--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Sleep score check</t>
+          <t>Morning sleep check</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -999,17 +999,17 @@
       </c>
       <c r="AG2" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH2" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
@@ -2995,17 +2995,17 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
@@ -4425,17 +4425,17 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
@@ -4749,17 +4749,17 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
@@ -4909,17 +4909,17 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
@@ -5229,17 +5229,17 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
@@ -5905,17 +5905,17 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
@@ -6407,17 +6407,17 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
@@ -6561,17 +6561,17 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
@@ -6719,17 +6719,17 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
@@ -7023,17 +7023,17 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
@@ -7491,17 +7491,17 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -7655,17 +7655,17 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
@@ -7981,17 +7981,17 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
@@ -8127,17 +8127,17 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
@@ -8431,17 +8431,17 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
@@ -8585,17 +8585,17 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ49" s="3" t="inlineStr">
@@ -8747,17 +8747,17 @@
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
@@ -8897,17 +8897,17 @@
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Ishan)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ51" s="3" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ52" s="3" t="inlineStr">
@@ -9213,17 +9213,17 @@
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ53" s="3" t="inlineStr">
@@ -9383,17 +9383,17 @@
       </c>
       <c r="AG54" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ54" s="3" t="inlineStr">
@@ -9533,17 +9533,17 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ55" s="3" t="inlineStr">
@@ -9691,17 +9691,17 @@
       </c>
       <c r="AG56" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
@@ -9853,17 +9853,17 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
@@ -10173,17 +10173,17 @@
       </c>
       <c r="AG59" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
@@ -10319,17 +10319,17 @@
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
@@ -10473,17 +10473,17 @@
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ61" s="3" t="inlineStr">
@@ -10615,17 +10615,17 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
@@ -10761,17 +10761,17 @@
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ63" s="3" t="inlineStr">
@@ -10911,17 +10911,17 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ64" s="3" t="inlineStr">
@@ -11065,17 +11065,17 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
@@ -11235,17 +11235,17 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ66" s="3" t="inlineStr">
@@ -11385,17 +11385,17 @@
       </c>
       <c r="AG67" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ67" s="3" t="inlineStr">
@@ -11531,17 +11531,17 @@
       </c>
       <c r="AG68" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ68" s="3" t="inlineStr">
@@ -11685,17 +11685,17 @@
       </c>
       <c r="AG69" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ69" s="3" t="inlineStr">
@@ -11839,17 +11839,17 @@
       </c>
       <c r="AG70" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ70" s="3" t="inlineStr">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="AG71" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ71" s="3" t="inlineStr">
@@ -12159,17 +12159,17 @@
       </c>
       <c r="AG72" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ72" s="3" t="inlineStr">
@@ -12313,17 +12313,17 @@
       </c>
       <c r="AG73" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ73" s="3" t="inlineStr">
@@ -12467,17 +12467,17 @@
       </c>
       <c r="AG74" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ74" s="3" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ75" s="3" t="inlineStr">
@@ -12793,17 +12793,17 @@
       </c>
       <c r="AG76" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ76" s="3" t="inlineStr">
@@ -12953,17 +12953,17 @@
       </c>
       <c r="AG77" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ77" s="3" t="inlineStr">
@@ -13121,17 +13121,17 @@
       </c>
       <c r="AG78" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ78" s="3" t="inlineStr">
@@ -13283,17 +13283,17 @@
       </c>
       <c r="AG79" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ79" s="3" t="inlineStr">
@@ -13447,17 +13447,17 @@
       </c>
       <c r="AG80" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ80" s="3" t="inlineStr">
@@ -13615,17 +13615,17 @@
       </c>
       <c r="AG81" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ81" s="3" t="inlineStr">
@@ -13773,17 +13773,17 @@
       </c>
       <c r="AG82" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ82" s="3" t="inlineStr">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="AG83" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ83" s="3" t="inlineStr">
@@ -14077,17 +14077,17 @@
       </c>
       <c r="AG84" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ84" s="3" t="inlineStr">
@@ -14227,17 +14227,17 @@
       </c>
       <c r="AG85" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ85" s="3" t="inlineStr">
@@ -14373,17 +14373,17 @@
       </c>
       <c r="AG86" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ86" s="3" t="inlineStr">
@@ -14523,17 +14523,17 @@
       </c>
       <c r="AG87" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ87" s="3" t="inlineStr">
@@ -14669,17 +14669,17 @@
       </c>
       <c r="AG88" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ88" s="3" t="inlineStr">
@@ -14823,17 +14823,17 @@
       </c>
       <c r="AG89" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ89" s="3" t="inlineStr">
@@ -14977,17 +14977,17 @@
       </c>
       <c r="AG90" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ90" s="3" t="inlineStr">
@@ -15131,17 +15131,17 @@
       </c>
       <c r="AG91" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ91" s="3" t="inlineStr">
@@ -15281,17 +15281,17 @@
       </c>
       <c r="AG92" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ92" s="3" t="inlineStr">
@@ -15439,17 +15439,17 @@
       </c>
       <c r="AG93" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ93" s="3" t="inlineStr">
@@ -15589,17 +15589,17 @@
       </c>
       <c r="AG94" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ94" s="3" t="inlineStr">
@@ -15755,17 +15755,17 @@
       </c>
       <c r="AG95" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ95" s="3" t="inlineStr">
@@ -15917,17 +15917,17 @@
       </c>
       <c r="AG96" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ96" s="3" t="inlineStr">
@@ -16083,17 +16083,17 @@
       </c>
       <c r="AG97" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ97" s="3" t="inlineStr">
@@ -16229,17 +16229,17 @@
       </c>
       <c r="AG98" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ98" s="3" t="inlineStr">
@@ -16387,17 +16387,17 @@
       </c>
       <c r="AG99" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH99" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI99" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ99" s="3" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="AG100" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH100" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI100" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ100" s="3" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="AG101" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH101" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI101" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ101" s="3" t="inlineStr">
@@ -16877,17 +16877,17 @@
       </c>
       <c r="AG102" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH102" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI102" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ102" s="3" t="inlineStr">
@@ -17035,17 +17035,17 @@
       </c>
       <c r="AG103" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH103" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI103" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ103" s="3" t="inlineStr">
@@ -17197,17 +17197,17 @@
       </c>
       <c r="AG104" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH104" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI104" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ104" s="3" t="inlineStr">
@@ -17359,17 +17359,17 @@
       </c>
       <c r="AG105" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH105" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI105" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ105" s="3" t="inlineStr">
@@ -17521,17 +17521,17 @@
       </c>
       <c r="AG106" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH106" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI106" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ106" s="3" t="inlineStr">
@@ -17685,17 +17685,17 @@
       </c>
       <c r="AG107" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH107" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI107" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ107" s="3" t="inlineStr">
@@ -17847,17 +17847,17 @@
       </c>
       <c r="AG108" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH108" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI108" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ108" s="3" t="inlineStr">
@@ -18007,17 +18007,17 @@
       </c>
       <c r="AG109" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH109" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI109" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ109" s="3" t="inlineStr">
@@ -18169,17 +18169,17 @@
       </c>
       <c r="AG110" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH110" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI110" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ110" s="3" t="inlineStr">
@@ -18331,17 +18331,17 @@
       </c>
       <c r="AG111" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH111" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ111" s="3" t="inlineStr">
@@ -18493,17 +18493,17 @@
       </c>
       <c r="AG112" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH112" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI112" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ112" s="3" t="inlineStr">
@@ -18655,17 +18655,17 @@
       </c>
       <c r="AG113" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH113" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI113" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ113" s="3" t="inlineStr">
@@ -18817,17 +18817,17 @@
       </c>
       <c r="AG114" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH114" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI114" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ114" s="3" t="inlineStr">
@@ -18979,17 +18979,17 @@
       </c>
       <c r="AG115" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH115" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI115" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ115" s="3" t="inlineStr">
@@ -19141,17 +19141,17 @@
       </c>
       <c r="AG116" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH116" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI116" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ116" s="3" t="inlineStr">
@@ -19311,17 +19311,17 @@
       </c>
       <c r="AG117" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH117" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI117" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ117" s="3" t="inlineStr">
@@ -19477,17 +19477,17 @@
       </c>
       <c r="AG118" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH118" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI118" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ118" s="3" t="inlineStr">
@@ -19639,17 +19639,17 @@
       </c>
       <c r="AG119" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH119" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI119" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ119" s="3" t="inlineStr">
@@ -19805,17 +19805,17 @@
       </c>
       <c r="AG120" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH120" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI120" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ120" s="3" t="inlineStr">
@@ -19971,17 +19971,17 @@
       </c>
       <c r="AG121" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH121" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI121" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ121" s="3" t="inlineStr">
@@ -20137,17 +20137,17 @@
       </c>
       <c r="AG122" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH122" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI122" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ122" s="3" t="inlineStr">
@@ -20291,17 +20291,17 @@
       </c>
       <c r="AG123" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH123" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI123" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ123" s="3" t="inlineStr">
@@ -20449,17 +20449,17 @@
       </c>
       <c r="AG124" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH124" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI124" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ124" s="3" t="inlineStr">
@@ -20603,17 +20603,17 @@
       </c>
       <c r="AG125" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH125" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI125" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ125" s="3" t="inlineStr">
@@ -20769,17 +20769,17 @@
       </c>
       <c r="AG126" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH126" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI126" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ126" s="3" t="inlineStr">
@@ -20931,17 +20931,17 @@
       </c>
       <c r="AG127" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH127" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI127" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ127" s="3" t="inlineStr">
@@ -21081,17 +21081,17 @@
       </c>
       <c r="AG128" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH128" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI128" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ128" s="3" t="inlineStr">
@@ -21235,17 +21235,17 @@
       </c>
       <c r="AG129" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH129" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI129" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ129" s="3" t="inlineStr">
@@ -21401,17 +21401,17 @@
       </c>
       <c r="AG130" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH130" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI130" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ130" s="3" t="inlineStr">
@@ -21547,17 +21547,17 @@
       </c>
       <c r="AG131" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH131" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI131" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ131" s="3" t="inlineStr">
@@ -21697,17 +21697,17 @@
       </c>
       <c r="AG132" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH132" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI132" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ132" s="3" t="inlineStr">
@@ -21851,17 +21851,17 @@
       </c>
       <c r="AG133" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH133" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI133" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ133" s="3" t="inlineStr">
@@ -22013,17 +22013,17 @@
       </c>
       <c r="AG134" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH134" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI134" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ134" s="3" t="inlineStr">
@@ -22167,17 +22167,17 @@
       </c>
       <c r="AG135" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH135" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI135" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ135" s="3" t="inlineStr">
@@ -22325,17 +22325,17 @@
       </c>
       <c r="AG136" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH136" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI136" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ136" s="3" t="inlineStr">
@@ -22487,17 +22487,17 @@
       </c>
       <c r="AG137" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH137" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI137" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ137" s="3" t="inlineStr">
@@ -22641,17 +22641,17 @@
       </c>
       <c r="AG138" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH138" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI138" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ138" s="3" t="inlineStr">
@@ -22803,17 +22803,17 @@
       </c>
       <c r="AG139" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH139" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI139" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ139" s="3" t="inlineStr">
@@ -22957,17 +22957,17 @@
       </c>
       <c r="AG140" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH140" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI140" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ140" s="3" t="inlineStr">
@@ -23111,17 +23111,17 @@
       </c>
       <c r="AG141" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH141" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI141" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ141" s="3" t="inlineStr">
@@ -23261,17 +23261,17 @@
       </c>
       <c r="AG142" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH142" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI142" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ142" s="3" t="inlineStr">
@@ -23423,17 +23423,17 @@
       </c>
       <c r="AG143" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH143" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI143" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ143" s="3" t="inlineStr">
@@ -23585,17 +23585,17 @@
       </c>
       <c r="AG144" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH144" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI144" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ144" s="3" t="inlineStr">
@@ -23751,17 +23751,17 @@
       </c>
       <c r="AG145" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH145" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI145" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ145" s="3" t="inlineStr">
@@ -23915,17 +23915,17 @@
       </c>
       <c r="AG146" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH146" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI146" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ146" s="3" t="inlineStr">
@@ -24085,17 +24085,17 @@
       </c>
       <c r="AG147" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH147" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI147" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ147" s="3" t="inlineStr">
@@ -24251,17 +24251,17 @@
       </c>
       <c r="AG148" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH148" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI148" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ148" s="3" t="inlineStr">
@@ -24421,17 +24421,17 @@
       </c>
       <c r="AG149" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH149" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI149" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ149" s="3" t="inlineStr">
@@ -24591,17 +24591,17 @@
       </c>
       <c r="AG150" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH150" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI150" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ150" s="3" t="inlineStr">
@@ -24757,17 +24757,17 @@
       </c>
       <c r="AG151" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH151" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI151" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ151" s="3" t="inlineStr">
@@ -24923,17 +24923,17 @@
       </c>
       <c r="AG152" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH152" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI152" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ152" s="3" t="inlineStr">
@@ -25085,17 +25085,17 @@
       </c>
       <c r="AG153" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH153" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI153" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ153" s="3" t="inlineStr">
@@ -25247,17 +25247,17 @@
       </c>
       <c r="AG154" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH154" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI154" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ154" s="3" t="inlineStr">
@@ -25413,17 +25413,17 @@
       </c>
       <c r="AG155" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH155" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI155" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ155" s="3" t="inlineStr">
@@ -25563,17 +25563,17 @@
       </c>
       <c r="AG156" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH156" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI156" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ156" s="3" t="inlineStr">
@@ -25721,17 +25721,17 @@
       </c>
       <c r="AG157" s="3" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>live</t>
         </is>
       </c>
       <c r="AH157" s="3" t="inlineStr">
         <is>
-          <t>Claude (sources opened; awaiting Veer)</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="AI157" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AJ157" s="3" t="inlineStr">

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>One of the best-studied supplements. For people who lift, it adds several kilos to strength gains over weeks of training; without training, gains are small. Monohydrate at 3 to 5 g a day is the studied form.</t>
+          <t>One of the best-studied supplements. For people who lift, it adds to strength gains over weeks of training, shown mostly in men; without training, gains are small. Monohydrate at 3 to 5 g a day is the studied form.</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>Plain unflavored monohydrate powder, often around $10 a month.</t>
+          <t>Plain unflavored monohydrate, the form the trials used.</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>Dose floor settled at 3 g/day. The ISSN 2017 position stand gives 3 g/day for 28 days as the low-dose route and says smaller amounts (e.g. 3-5 g/day) saturate muscle over 3-4 weeks; it never gives a 2 g human dose (it notes a normal diet already supplies 1-2 g/day). V3's ruleText cut-off of 2 g was wrong; the factCheck 3 g was right. Loading (~0.3 g/kg/day for 5-7 days, then 3-5 g/day) is optional; ISSN notes larger athletes may take 5-10 g/day. Female evidence is thin (Wang 2024: only 2 female-only trials, gains not significant). Wang co-author Candow advises creatine makers and most ISSN/Antonio authors disclose industry ties; Wang itself had no external funding and the strength effect is consistent (I2 = 0%), so A stands. FORM_NOT_ABSORBED: ISSN and Antonio find no form better than monohydrate and ISSN does not mention HCl, so for HCl or buffered the verdict should say monohydrate is the studied form, not that the other form fails; ethyl ester has the weakest case. tier_otherwise C: without training, gains are small and inconsistent (Antonio 2021, mostly older-adult data). V3's claim about thinking during sleep loss was not checked and is left out of person-facing text. Effect on sleep or HRV is not visible to wearables.</t>
+          <t>Dose floor settled at 3 g/day. The ISSN 2017 position stand gives 3 g/day for 28 days as the low-dose route and says smaller amounts (e.g. 3-5 g/day) saturate muscle over 3-4 weeks; it never gives a 2 g human dose (it notes a normal diet already supplies 1-2 g/day). V3's ruleText cut-off of 2 g was wrong; the factCheck 3 g was right. Loading (~0.3 g/kg/day for 5-7 days, then 3-5 g/day) is optional; ISSN notes larger athletes may take 5-10 g/day. Female evidence is thin (Wang 2024: only 2 female-only trials, gains not significant). Wang co-author Candow advises creatine makers and most ISSN/Antonio authors disclose industry ties; Wang itself had no external funding and the strength effect is consistent (I2 = 0%), so A stands. FORM_NOT_ABSORBED: ISSN and Antonio find no form better than monohydrate and ISSN does not mention HCl, so for HCl or buffered the verdict should say monohydrate is the studied form, not that the other form fails; ethyl ester has the weakest case. tier_otherwise C: without training, gains are small and inconsistent (Antonio 2021, mostly older-adult data). V3's claim about thinking during sleep loss was not checked and is left out of person-facing text. Effect on sleep or HRV is not visible to wearables. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>A plain tablet near 600 IU, often a couple of dollars a month.</t>
+          <t>A plain tablet near 600 IU, the usual daily amount advised for adults.</t>
         </is>
       </c>
       <c r="AC5" s="3" t="n"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>Outcome chosen: bone density and levels when low, the one area where benefit clearly depends on baseline (Macdonald 2018: bone density rose only when starting 25(OH)D was at or below 30 nmol/L; the IOM found evidence for bone health only). Most 22-35 buyers want immunity, mood or energy, and those grade lower: colds C at best (Martineau 2017 showed a strong effect below 25 nmol/L, but Jolliffe 2021 and 2025 found no modification by baseline status and the 2025 overall effect is no longer significant); mood null (VITAL-DEP). tier_otherwise D means trials in people with normal levels found no bone, fracture or mood benefit (VITAL); the scale has no 'tested and found little' grade. B rather than A because the deficiency evidence comes from subgroup analyses of a few trials plus the IOM consensus. V3 nudged a ~$30 blood test: the Endocrine Society 2024 guideline suggests against routine 25(OH)D testing in healthy adults and against doses above the DRI for ages 19-74, and the IOM notes many labs use cut-offs that overstate deficiency (20 ng/mL, 50 nmol/L, is adequate for nearly everyone). Drop the testing nudge; ask whether a clinician already said it runs low. V3 put harm above 10,000 IU: the upper limit is 4,000 IU/day; above 10,000 IU/day is where kidney and tissue damage is documented. If clinician-prescribed (e.g. weekly high-dose), treat as clinician-led and protect. dose_min 600 IU is the RDA; DOSE_BELOW_MIN left out because correcting a deficiency is a clinician call. AG1 Next Gen reportedly has no vitamin D, so D plus AG1 is not an overlap (see overlap proposals).</t>
+          <t>Outcome chosen: bone density and levels when low, the one area where benefit clearly depends on baseline (Macdonald 2018: bone density rose only when starting 25(OH)D was at or below 30 nmol/L; the IOM found evidence for bone health only). Most 22-35 buyers want immunity, mood or energy, and those grade lower: colds C at best (Martineau 2017 showed a strong effect below 25 nmol/L, but Jolliffe 2021 and 2025 found no modification by baseline status and the 2025 overall effect is no longer significant); mood null (VITAL-DEP). tier_otherwise D means trials in people with normal levels found no bone, fracture or mood benefit (VITAL); the scale has no 'tested and found little' grade. B rather than A because the deficiency evidence comes from subgroup analyses of a few trials plus the IOM consensus. V3 nudged a ~$30 blood test: the Endocrine Society 2024 guideline suggests against routine 25(OH)D testing in healthy adults and against doses above the DRI for ages 19-74, and the IOM notes many labs use cut-offs that overstate deficiency (20 ng/mL, 50 nmol/L, is adequate for nearly everyone). Drop the testing nudge; ask whether a clinician already said it runs low. V3 put harm above 10,000 IU: the upper limit is 4,000 IU/day; above 10,000 IU/day is where kidney and tissue damage is documented. If clinician-prescribed (e.g. weekly high-dose), treat as clinician-led and protect. dose_min 600 IU is the RDA; DOSE_BELOW_MIN left out because correcting a deficiency is a clinician call. AG1 Next Gen reportedly has no vitamin D, so D plus AG1 is not an overlap (see overlap proposals). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>A basic store-brand multivitamin, often a few dollars a month.</t>
+          <t>A basic multivitamin covers the same ground.</t>
         </is>
       </c>
       <c r="AC6" s="3" t="n"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>C because the trials disagree slightly: the USPSTF evidence review pooled a small drop in cancer incidence (OR 0.93, 4 RCTs, limitations noted) while COSMOS found no effect on cancer, CV events or mortality; USPSTF grade is I (insufficient). V3 said there was no effect on cancer, which is not quite right. The cognitive benefit is confirmed only in adults 60+ (COSMOS, about 2 years of cognitive aging slowed). No trials in 22-35-year-olds. V3 also said it does no harm: USPSTF recommends against beta-carotene, which raises lung cancer risk in people at high risk (e.g. smokers), and some multis contain it. The safety list has no smoking condition, so this needs a reviewer decision. Targeted needs (B12 for vegans, iron, folate before pregnancy) are separate items and often clinician-led. COSMOS funders include Pfizer per the record; whether pills were donated was not confirmed.</t>
+          <t>C because the trials disagree slightly: the USPSTF evidence review pooled a small drop in cancer incidence (OR 0.93, 4 RCTs, limitations noted) while COSMOS found no effect on cancer, CV events or mortality; USPSTF grade is I (insufficient). V3 said there was no effect on cancer, which is not quite right. The cognitive benefit is confirmed only in adults 60+ (COSMOS, about 2 years of cognitive aging slowed). No trials in 22-35-year-olds. V3 also said it does no harm: USPSTF recommends against beta-carotene, which raises lung cancer risk in people at high risk (e.g. smokers), and some multis contain it. The safety list has no smoking condition, so this needs a reviewer decision. Targeted needs (B12 for vegans, iron, folate before pregnancy) are separate items and often clinician-led. COSMOS funders include Pfizer per the record; whether pills were donated was not confirmed. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>A smoothie with frozen spinach and berries keeps the morning glass for less.</t>
+          <t>A smoothie with frozen spinach and berries keeps the morning glass.</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>Tier N per the brief's rule (brand-funded only counts as none). V3 said D. Every human study found was funded by the brand and/or written by its employees: AG1 (La Monica 2024: funded in part by AG1, two AG1 employees; Gonzalez 2026: AG1-funded, AG1 employees; Sapp 2026: five AG1-affiliated authors, no funding statement in the record) and Field of Greens (Robinson 2026: BrickHouse Nutrition paid for the trial and supplied the product). Kirby 2024 is a lab gut-simulator study by AG1 employees. Outcomes were surrogates (bacterial taxa, intake on paper, blood levels after one dose); none showed changes in health, energy or digestion, and microbiome diversity did not change. AG1 conference abstracts in JISSN 2025 supplements are also AG1-authored and were not opened. Price: AG1 is $79/month on subscription or $99 one-time per a Fortune review (Jan 2026, updated Jul 2026, affiliate-linked; https://www.fortune.com/article/ag1-review), so V3's $90 is updated to 79. The same review says AG1 Next Gen has no vitamin D or K (sold separately); the label could not be checked (drinkag1.com rate-limited). ritual_role is anchor because the morning glass often carries the habit, so fits_instead keeps the glass.</t>
+          <t>Tier N per the brief's rule (brand-funded only counts as none). V3 said D. Every human study found was funded by the brand and/or written by its employees: AG1 (La Monica 2024: funded in part by AG1, two AG1 employees; Gonzalez 2026: AG1-funded, AG1 employees; Sapp 2026: five AG1-affiliated authors, no funding statement in the record) and Field of Greens (Robinson 2026: BrickHouse Nutrition paid for the trial and supplied the product). Kirby 2024 is a lab gut-simulator study by AG1 employees. Outcomes were surrogates (bacterial taxa, intake on paper, blood levels after one dose); none showed changes in health, energy or digestion, and microbiome diversity did not change. AG1 conference abstracts in JISSN 2025 supplements are also AG1-authored and were not opened. Price: AG1 is $79/month on subscription or $99 one-time per a Fortune review (Jan 2026, updated Jul 2026, affiliate-linked; https://www.fortune.com/article/ag1-review), so V3's $90 is updated to 79. The same review says AG1 Next Gen has no vitamin D or K (sold separately); the label could not be checked (drinkag1.com rate-limited). ritual_role is anchor because the morning glass often carries the habit, so fits_instead keeps the glass. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>A large coffee about an hour before training covers the caffeine part for less.</t>
+          <t>A large coffee about an hour before training covers the caffeine part.</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>Tier A rests on the caffeine (ISSN 2021 stand; Grgic 2020 umbrella review of 21 meta-analyses, moderate-quality evidence, mostly young men), not on the blend: I found no meta-analysis of multi-ingredient pre-workouts, product trials are small and often brand-linked, and 44% of listed ingredients sit in proprietary blends with beta-alanine below its effective dose (Jagim 2019). 89% of regular users take it for energy and focus (Jagim 2019 survey), which is why evidence_for names energy as well as performance. V3 graded B and said the sleep cost starts 'after 2pm'; Gardiner 2023 modelled a standard 217.5 mg pre-workout needing about 13.2 h before bed to avoid lost sleep (before 8:50am for a 10pm bedtime), so afternoon and evening scoops cost more than V3 implied. dose_min 140 mg = 2 mg/kg at 70 kg, the ISSN 'may be as low as' figure; 3 to 6 mg/kg (about 200 to 400 mg) is the consistently effective range, so a stim-free tub fails DOSE_BELOW_MIN. tier_otherwise N: no studies of pre-workouts outside training; for alertness alone, coffee carries the same caffeine. Coffee as a substitute is my inference from caffeine being the shared active ingredient, not a head-to-head trial. Safety rows: pregnancy and breastfeeding from EFSA and FDA plus Jagim 2019's 254 mg average serving; heart from Bella 2025, Jagim 2019 (self-reported heart abnormalities) and the energy-drink ECG trials; under-18 extends AAP 2011's energy-drink guidance to stimulant pre-workouts; medicines from FDA and Gardiner 2023 (antidepressants and oral contraceptives change caffeine half-life).</t>
+          <t>Tier A rests on the caffeine (ISSN 2021 stand; Grgic 2020 umbrella review of 21 meta-analyses, moderate-quality evidence, mostly young men), not on the blend: I found no meta-analysis of multi-ingredient pre-workouts, product trials are small and often brand-linked, and 44% of listed ingredients sit in proprietary blends with beta-alanine below its effective dose (Jagim 2019). 89% of regular users take it for energy and focus (Jagim 2019 survey), which is why evidence_for names energy as well as performance. V3 graded B and said the sleep cost starts 'after 2pm'; Gardiner 2023 modelled a standard 217.5 mg pre-workout needing about 13.2 h before bed to avoid lost sleep (before 8:50am for a 10pm bedtime), so afternoon and evening scoops cost more than V3 implied. dose_min 140 mg = 2 mg/kg at 70 kg, the ISSN 'may be as low as' figure; 3 to 6 mg/kg (about 200 to 400 mg) is the consistently effective range, so a stim-free tub fails DOSE_BELOW_MIN. tier_otherwise N: no studies of pre-workouts outside training; for alertness alone, coffee carries the same caffeine. Coffee as a substitute is my inference from caffeine being the shared active ingredient, not a head-to-head trial. Safety rows: pregnancy and breastfeeding from EFSA and FDA plus Jagim 2019's 254 mg average serving; heart from Bella 2025, Jagim 2019 (self-reported heart abnormalities) and the energy-drink ECG trials; under-18 extends AAP 2011's energy-drink guidance to stimulant pre-workouts; medicines from FDA and Gardiner 2023 (antidepressants and oral contraceptives change caffeine half-life). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       <c r="Q16" s="3" t="n"/>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>Bright morning light nudges the body clock earlier; in one camping study, a week of natural light moved it about two hours. A review links brighter mornings with earlier, better-rated sleep. Ten minutes hasn't been tested directly.</t>
+          <t>Bright morning light nudges the body clock earlier; a week of natural light with no evening electric light moved it about two hours. Everyday studies are mixed, and ten minutes hasn't been tested directly.</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>V3 fact-check target confirmed: Wright 2013 (8 campers; clock about 2 h earlier after a week of natural light only; read in full text). Tier B is for clock timing only: lab bright-light experiments in healthy adults agree (Dautovich 2019 review, 32 experimental + 13 observational studies, no meta-analysis), but no trial tested 10 minutes outdoors, and everyday wrist-measured light shows weak or conflicting links (Bohmer 2021). Mood or energy claims would be tier C. V3 dayOne line ('about half of one night's normal swing') had no source and is dropped. clear_when empty: free, B tier, and the wake-up light rule keeps the free option. Area set to sleep (V3 batch was mind); reviewer may move it back. Never tell anyone to look at the sun.</t>
+          <t>V3 fact-check target confirmed: Wright 2013 (8 campers; clock about 2 h earlier after a week of natural light only; read in full text). Tier B is for clock timing only: lab bright-light experiments in healthy adults agree (Dautovich 2019 review, 32 experimental + 13 observational studies, no meta-analysis), but no trial tested 10 minutes outdoors, and everyday wrist-measured light shows weak or conflicting links (Bohmer 2021). Mood or energy claims would be tier C. V3 dayOne line ('about half of one night's normal swing') had no source and is dropped. clear_when empty: free, B tier, and the wake-up light rule keeps the free option. Area set to sleep (V3 batch was mind); reviewer may move it back. Never tell anyone to look at the sun. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -3450,11 +3450,7 @@
           <t>When did you last open it?</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>A free guided meditation app, for the same kind of practice without the subscription.</t>
-        </is>
-      </c>
+      <c r="AB17" s="3" t="n"/>
       <c r="AC17" s="3" t="n"/>
       <c r="AD17" s="3" t="inlineStr">
         <is>
@@ -3488,7 +3484,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>V3 tier B kept. A is arguable (Linardon 2024: 45 RCTs, effects held in lower-bias trials), but effects are small (g 0.24 to 0.28), measured only at post-test (10 days to 8 weeks), not better than active therapies, and the authors flag possible conflicts of interest in Headspace trials (k = 15; Calm k = 5). Gal 2021 stress effect (g 0.46) was heterogeneous (I2 68%). V3 line about sleep ('people say they sleep better; measured change smaller') was not checked here and is removed. Baumel 2019 backs the UNUSED path (median 30-day retention about 3%, meditation apps about 5%). V3 cost 15 reflects monthly billing; annual plans run about $70 a year, so 7 is a blended estimate (prices from third-party pages, not sourced). Safety note from Farias 2020.</t>
+          <t>V3 tier B kept. A is arguable (Linardon 2024: 45 RCTs, effects held in lower-bias trials), but effects are small (g 0.24 to 0.28), measured only at post-test (10 days to 8 weeks), not better than active therapies, and the authors flag possible conflicts of interest in Headspace trials (k = 15; Calm k = 5). Gal 2021 stress effect (g 0.46) was heterogeneous (I2 68%). V3 line about sleep ('people say they sleep better; measured change smaller') was not checked here and is removed. Baumel 2019 backs the UNUSED path (median 30-day retention about 3%, meditation apps about 5%). V3 cost 15 reflects monthly billing; annual plans run about $70 a year, so 7 is a blended estimate (prices from third-party pages, not sourced). Safety note from Farias 2020. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3732,7 @@
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>Studies from 28 countries, nearly 25,000 people, find a small average rise in well-being, clearest for positive mood. Other pleasant exercises do about as well, and how often it's done mattered little.</t>
+          <t>Studies from 28 countries, nearly 25,000 people, find a small average rise in well-being, clearest for positive mood. Other active exercises do about as well.</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -3778,7 +3774,7 @@
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>Once a week instead of nightly; in studies, how often mattered little.</t>
+          <t>Once a week instead of nightly, if nightly feels like a chore.</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
@@ -3818,7 +3814,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>V3 tier B raised to A: Choi 2025 (PNAS, preregistered, 145 papers, 24,804 people, g = 0.19, robust to publication bias). The effect is small and not specific to gratitude: Davis 2016 and Choi 2025 both find it matches other positive activities, and Davis found no effect on anxiety. Number of sessions did not moderate the effect (Choi), which supports the weekly fits_instead. Awe 'moral' is a judgment call: it fits when the practice dwells on other people's kindness (Keltner's moral beauty), much less for lists of pleasant things; blank it if the reviewer prefers. clear_when empty: free and A tier.</t>
+          <t>V3 tier B raised to A: Choi 2025 (PNAS, preregistered, 145 papers, 24,804 people, g = 0.19, robust to publication bias). The effect is small and not specific to gratitude: Davis 2016 and Choi 2025 both find it matches other positive activities, and Davis found no effect on anxiety. Number of sessions did not moderate the effect (Choi), which supports the weekly fits_instead. Awe 'moral' is a judgment call: it fits when the practice dwells on other people's kindness (Keltner's moral beauty), much less for lists of pleasant things; blank it if the reviewer prefers. clear_when empty: free and A tier. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4054,7 @@
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>Hundreds of trials find talk therapy, especially CBT, eases depression and anxiety symptoms, with gains still present 6 to 12 months later. It's clinician-led care, so Distill never suggests letting it go; changes belong with the therapist.</t>
+          <t>Hundreds of trials find talk therapy eases depression and anxiety, with CBT the most studied; for depression, gains held 6 to 12 months later. It's clinician-led care, so Distill never suggests letting it go.</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4128,7 +4124,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>Protected: never_clear yes and clear_when empty by design; no fits_instead offered for clinician-led care. Evidence population is people with depression or anxiety disorders, not healthy adults; no evidence_requires code fits, so it is set to none and the population sits in evidence_for. Keep the V3 behaviour of letting the person hide it from the cost total (hence the human_question). Cost: about $143 to $174 a session self-pay versus about $23 in-network copay (third-party 2026 figures, not sourced); 300 a month is a blended estimate for weekly sessions (V3 said 400). The safety row is a protection rule rather than a sourced interaction.</t>
+          <t>Protected: never_clear yes and clear_when empty by design; no fits_instead offered for clinician-led care. Evidence population is people with depression or anxiety disorders, not healthy adults; no evidence_requires code fits, so it is set to none and the population sits in evidence_for. Keep the V3 behaviour of letting the person hide it from the cost total (hence the human_question). Cost: about $143 to $174 a session self-pay versus about $23 in-network copay (third-party 2026 figures, not sourced); 300 a month is a blended estimate for weekly sessions (V3 said 400). The safety row is a protection rule rather than a sourced interaction. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4678,7 @@
       <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>Nicotine near bedtime makes sleep lighter and more broken, in lab trials and in people tracked at home. Vapes nudge heart rate up a little; strong pouches raise it sharply, a 6 mg pouch only slightly.</t>
+          <t>Nicotine near bedtime makes sleep lighter and more broken, in overnight patch trials and in people tracked at home. Vapes and pouches nudge heart rate up.</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -4764,7 +4760,7 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>V3 tier A lowered to B. Sleep: small placebo-controlled patch trials in healthy non-smokers agree (Jaehne 2014, n = 66; Choi 2017, n = 16; also opened Gillin 1994 and Davila 1994, not cited), backed by actigraphy cohort data (Spadola 2019: nicotine within 4 h of bed, lower efficiency, about 6 more minutes awake) and a cross-sectional meta-analysis of vape-only users (Gulati 2026, OR 1.38). No sleep trial used pouches or vapes directly. Heart rate: dose-dependent; the pouch study (n = 15 smokers) found 20 to 30 mg pouches raise it 12 to 25 bpm but 6 mg only slightly; vaping about +2 bpm in a meta-analysis of mostly non-randomized studies. V3's 'lowers HRV' is not confirmed (Choi 2017: no overnight HRV difference). Withdrawal can upset sleep for a while (Jaehne 2009), so an evening-off test may look worse at first. If the pouch or vape replaced cigarettes, Distill should not propose letting it go; no safety condition code fits this, so it is flagged here and asked in human_question. The engine still needs V3's timing question (daytime only, some after 6pm, mostly evening). EVIDENCE_REGULAR left out of keep_when because the tier grades harm, not benefit. kind 'food-drink' is the nearest allowed value (no substance kind). Keep V3's stance: test evening timing, never a quit programme. Cost: ZYN about $5.50 to $6.25 a can retail, several pouches a day, about $80 a month (third-party pricing, not sourced; V3 said 60).</t>
+          <t>V3 tier A lowered to B. Sleep: small placebo-controlled patch trials in healthy non-smokers agree (Jaehne 2014, n = 66; Choi 2017, n = 16; also opened Gillin 1994 and Davila 1994, not cited), backed by actigraphy cohort data (Spadola 2019: nicotine within 4 h of bed, lower efficiency, about 6 more minutes awake) and a cross-sectional meta-analysis of vape-only users (Gulati 2026, OR 1.38). No sleep trial used pouches or vapes directly. Heart rate: dose-dependent; the pouch study (n = 15 smokers) found 20 to 30 mg pouches raise it 12 to 25 bpm but 6 mg only slightly; vaping about +2 bpm in a meta-analysis of mostly non-randomized studies. V3's 'lowers HRV' is not confirmed (Choi 2017: no overnight HRV difference). Withdrawal can upset sleep for a while (Jaehne 2009), so an evening-off test may look worse at first. If the pouch or vape replaced cigarettes, Distill should not propose letting it go; no safety condition code fits this, so it is flagged here and asked in human_question. The engine still needs V3's timing question (daytime only, some after 6pm, mostly evening). EVIDENCE_REGULAR left out of keep_when because the tier grades harm, not benefit. kind 'food-drink' is the nearest allowed value (no substance kind). Keep V3's stance: test evening timing, never a quit programme. Cost: ZYN about $5.50 to $6.25 a can retail, several pouches a day, about $80 a month (third-party pricing, not sourced; V3 said 60). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5324,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>Regular training builds strength and fitness, and a gym makes that easier. The benefit lives in the visits: in one large study, monthly members averaged about four visits a month, paying more per visit than a pass.</t>
+          <t>Regular training builds strength and fitness, and a gym is one way to do it. The benefit lives in the visits: in one large study, monthly members paid more per visit than a pass would have cost.</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -5372,11 +5368,7 @@
           <t>How many times did you go in the last month?</t>
         </is>
       </c>
-      <c r="AB29" s="3" t="inlineStr">
-        <is>
-          <t>A pay-per-visit pass, which often costs less when visits are few.</t>
-        </is>
-      </c>
+      <c r="AB29" s="3" t="n"/>
       <c r="AC29" s="3" t="n"/>
       <c r="AD29" s="3" t="inlineStr">
         <is>
@@ -5410,7 +5402,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>V3 graded the membership itself A. Now the A belongs to the training it makes possible and holds only for people who use it (evidence_requires 'trains', tier_otherwise N). The main clear codes are UNUSED and OVERLAP. Usage evidence: DellaVigna and Malmendier 2006 (7,752 members of three US clubs; monthly members averaged about 4.3 visits, over $17 a visit, when a 10-visit pass cost $10 a visit). V3's visit thresholds (8+ a month keep; under 4 for two months running) are unsourced but line up with WHO's 2+ strength days a week, roughly 8 visits a month. cost_month_usd 50 is my estimate (budget gyms roughly $10 to $25, mid-tier $40 to $70), not sourced. wearable 'partial': workouts show up, the membership does not. Proposed 'gym floor access' group for two gyms doing the same job.</t>
+          <t>V3 graded the membership itself A. Now the A belongs to the training it makes possible and holds only for people who use it (evidence_requires 'trains', tier_otherwise N). The main clear codes are UNUSED and OVERLAP. Usage evidence: DellaVigna and Malmendier 2006 (7,752 members of three US clubs; monthly members averaged about 4.3 visits, over $17 a visit, when a 10-visit pass cost $10 a visit). V3's visit thresholds (8+ a month keep; under 4 for two months running) are unsourced but line up with WHO's 2+ strength days a week, roughly 8 visits a month. cost_month_usd 50 is my estimate (budget gyms roughly $10 to $25, mid-tier $40 to $70), not sourced. wearable 'partial': workouts show up, the membership does not. Proposed 'gym floor access' group for two gyms doing the same job. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5486,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>Training works the same in any gym, and no study we found shows pricier clubs bring better results. The extra money buys comfort, classes and spa rooms, which pay off only when used.</t>
+          <t>Training works wherever it happens. The club earns its place through the visits and the parts that get used: the classes, the calm, the spa.</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -5538,11 +5530,7 @@
           <t>Which parts of the club do you actually use?</t>
         </is>
       </c>
-      <c r="AB30" s="3" t="inlineStr">
-        <is>
-          <t>A standard gym with the same racks and machines, often for a fraction of the price.</t>
-        </is>
-      </c>
+      <c r="AB30" s="3" t="n"/>
       <c r="AC30" s="3" t="n"/>
       <c r="AD30" s="3" t="inlineStr">
         <is>
@@ -5576,7 +5564,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>No study found that compares outcomes by gym price, so the tier is the training's, applied only when the club gets used (otherwise N). Main clear codes: UNUSED and OVERLAP. V3's 'twice a week or more is worth almost any price' is opinion and is removed; V3's '$83 a visit' day-one copy is fine as arithmetic but not evidence. Premium clubs usually include a sauna or steam room, so proposed 'spa amenities' (with bathhouse or recovery-studio memberships) and 'gym floor access' (with a standard gym) groups. cost_month_usd 250 is my estimate (Equinox roughly $200 to $300+, Life Time roughly $100 to $250+), not sourced.</t>
+          <t>No study found that compares outcomes by gym price, so the tier is the training's, applied only when the club gets used (otherwise N). Main clear codes: UNUSED and OVERLAP. V3's 'twice a week or more is worth almost any price' is opinion and is removed; V3's '$83 a visit' day-one copy is fine as arithmetic but not evidence. Premium clubs usually include a sauna or steam room, so proposed 'spa amenities' (with bathhouse or recovery-studio memberships) and 'gym floor access' (with a standard gym) groups. cost_month_usd 250 is my estimate (Equinox roughly $200 to $300+, Life Time roughly $100 to $250+), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5648,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>Interval-style classes raise fitness at least as well as steady cardio in trials. A class format alone gives only a small edge over training solo; groups that feel like a team do better.</t>
+          <t>Interval training raises fitness at least as well as steady cardio in trials. A class format alone gives a small, uncertain edge over training solo; groups that feel like a team do better.</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -5704,11 +5692,7 @@
           <t>How many classes did you make it to last month?</t>
         </is>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
-        <is>
-          <t>A smaller class pack for the one or two classes booked most.</t>
-        </is>
-      </c>
+      <c r="AB31" s="3" t="n"/>
       <c r="AC31" s="3" t="inlineStr">
         <is>
           <t>collective</t>
@@ -5746,7 +5730,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>V3 said 'class formats have better attendance than open gyms, which is the honest case for paying more'. Not supported by what I opened: Burke 2006 found standard exercise classes did no better than home programs with some contact, while cohesion-building 'true groups' did best; Kritz 2026 (71 studies) found small, non-significant group edges for activity and health, and a significant edge for physical function only after removing outliers. Tier A is for the interval training itself (Milanovic 2015, healthy adults 18 to 45); no independent studies of the branded formats were looked for or found. Main clear codes: UNUSED and OVERLAP. Unflagged safety signal: spinning-induced rhabdomyolysis in healthy first-timers (Kim 2015, 11 cases); no schema condition fits, so suggest an item-level note such as 'ease into a first spin class'. awe 'collective' is for synchronized group classes; the row itself is a service. dose_typical 2 to 3 follows WHO-style weekly training, not a figure from the opened abstracts. cost_month_usd 200 is my estimate, not sourced.</t>
+          <t>V3 said 'class formats have better attendance than open gyms, which is the honest case for paying more'. Not supported by what I opened: Burke 2006 found standard exercise classes did no better than home programs with some contact, while cohesion-building 'true groups' did best; Kritz 2026 (71 studies) found small, non-significant group edges for activity and health, and a significant edge for physical function only after removing outliers. Tier A is for the interval training itself (Milanovic 2015, healthy adults 18 to 45); no independent studies of the branded formats were looked for or found. Main clear codes: UNUSED and OVERLAP. Unflagged safety signal: spinning-induced rhabdomyolysis in healthy first-timers (Kim 2015, 11 cases); no schema condition fits, so suggest an item-level note such as 'ease into a first spin class'. awe 'collective' is for synchronized group classes; the row itself is a service. dose_typical 2 to 3 follows WHO-style weekly training, not a figure from the opened abstracts. cost_month_usd 200 is my estimate, not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -5878,11 +5862,7 @@
           <t>Is the studio more about the workout or the calm?</t>
         </is>
       </c>
-      <c r="AB32" s="3" t="inlineStr">
-        <is>
-          <t>A smaller class pack plus free follow-along sessions at home.</t>
-        </is>
-      </c>
+      <c r="AB32" s="3" t="n"/>
       <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>collective</t>
@@ -5920,7 +5900,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>V3 tier B kept, outcome narrowed to stress and mood. V3 also claimed sleep benefits; not checked, so dropped. Support: Pascoe 2017 (42 RCTs against active controls, physiological stress markers, mixed populations), Pascoe and Bauer 2015 (25 RCTs, authors call it preliminary), Fleming and Herring 2018 (8 small pilates trials, inactive controls). Noetel 2024 ranks yoga among the stronger exercise types for clinical depression (very low certainty), internal only. Main clear codes: UNUSED and OVERLAP. The hot-yoga caution in pregnancy is in ACOG 804's full text, which I could not open (paywalled); the safety note rests on the NHS page (keep cool, stop if too hot, avoid lying flat on the back later). dose_typical 1 to 3 is common trial practice, not pulled from an opened abstract. awe 'collective' is for synchronized group practice; the row itself is a service. cost_month_usd 180 is my estimate (reformer pilates usually costs more), not sourced.</t>
+          <t>V3 tier B kept, outcome narrowed to stress and mood. V3 also claimed sleep benefits; not checked, so dropped. Support: Pascoe 2017 (42 RCTs against active controls, physiological stress markers, mixed populations), Pascoe and Bauer 2015 (25 RCTs, authors call it preliminary), Fleming and Herring 2018 (8 small pilates trials, inactive controls). Noetel 2024 ranks yoga among the stronger exercise types for clinical depression (very low certainty), internal only. Main clear codes: UNUSED and OVERLAP. The hot-yoga caution in pregnancy is in ACOG 804's full text, which I could not open (paywalled); the safety note rests on the NHS page (keep cool, stop if too hot, avoid lying flat on the back later). dose_typical 1 to 3 is common trial practice, not pulled from an opened abstract. awe 'collective' is for synchronized group practice; the row itself is a service. cost_month_usd 180 is my estimate (reformer pilates usually costs more), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5964,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -6048,11 +6028,7 @@
           <t>Would the workouts still happen without the trainer?</t>
         </is>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
-        <is>
-          <t>A few sessions to learn a plan, then monthly check-ins.</t>
-        </is>
-      </c>
+      <c r="AB33" s="3" t="n"/>
       <c r="AC33" s="3" t="n"/>
       <c r="AD33" s="3" t="inlineStr">
         <is>
@@ -6086,7 +6062,7 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>V3 graded A with 'strong evidence that this works, if you'd otherwise skip'. The supervision-specific evidence is small: Fisher 2022 (exploratory, 12 studies; strength SMD 0.40 with a wide CI; trivial body-composition effect) and Mazzetti 2000 (about 20 trained men, 12 weeks). Tier A is the training's; the coach adds a modest, uncertain extra. Nothing I opened shows that a trainer improves attendance; that V3 premise is untested here. V3 had no overlap group and treated low use as cost-per-session only; now UNUSED (unused or expiring session packs) is the main clear code, plus a proposed 'coaching' overlap with paid coaching apps. never_clear 'no': a trainer is not clinician-led care (a physical therapist would be a different row). cost_month_usd 400 assumes roughly $60 to $100 a session, 1 to 2 a week; not sourced.</t>
+          <t>V3 graded A with 'strong evidence that this works, if you'd otherwise skip'. The supervision-specific evidence is small: Fisher 2022 (exploratory, 12 studies; strength SMD 0.40 with a wide CI; trivial body-composition effect) and Mazzetti 2000 (about 20 trained men, 12 weeks). Tier A is the training's; the coach adds a modest, uncertain extra. Nothing I opened shows that a trainer improves attendance; that V3 premise is untested here. V3 had no overlap group and treated low use as cost-per-session only; now UNUSED (unused or expiring session packs) is the main clear code, plus a proposed 'coaching' overlap with paid coaching apps. never_clear 'no': a trainer is not clinician-led care (a physical therapist would be a different row). cost_month_usd 400 assumes roughly $60 to $100 a session, 1 to 2 a week; not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6196,7 @@
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>A 30 to 90 second cold finish to a shower, free and tested in a large trial.</t>
+          <t>A 30 to 90 second cold finish to a shower, though it was tested for sick days, not soreness.</t>
         </is>
       </c>
       <c r="AC34" s="3" t="n"/>
@@ -6256,7 +6232,7 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>V3 tier C changed: B for soreness in people who train (Machado 2016: small edge over passive rest, best near 10 to 15 C for 10 to 15 min; Moore 2022: soreness, perceived recovery and power better at 24 h after high-intensity work), C for everyone else (Cain 2025: 11 RCTs in healthy adults; stress lower only at 12 h; no mood change in the one mood study; sleep and quality of life each rest on a single study; inflammation up right after). Well supported: a small soreness benefit. Popular but thin: mood, dopamine, immunity, resilience. The dopamine figure that circulates traces to Sramek 2000, a one-hour head-out immersion at 14 C, not a 3-minute plunge. Buijze 2016: cold showers cut sick-leave days but not illness days. V3's 'an evening plunge can make it harder to fall asleep' is NOT supported: Robey 2013 and Chauvineau 2021 (small, trained men, lab sleep tests) found no change in sleep onset, and Chauvineau found fewer night arousals. V3's blunted-growth point is confirmed (Roberts 2015; Pinero 2024 applies to cold water within about 15 min after lifting). Popular 2 to 5 minute plunges are shorter than the 10 to 15 minutes best studied for soreness. Key mismatch: the overlap file lists 'cold-plunge-ice-bath-tub-owned', but the V3 row key is 'cold-plunge-ice-bath' and had no overlap group; see overlap_proposals. Safety: Shattock and Tipton 2012 for heart rhythm; the pregnancy, diabetes, blood pressure and medication rows rest on standard tub label warnings (read in a combined hot and cold tub manual, CSC Chill1000), which also flag alcohol and drowning risk. The schema has no alcohol or plunging-alone condition, so suggest an item-level caution: ease in, never alone, never after drinking. kind 'device' assumes an owned tub; a DIY ice bath would be 'practice'. cost_month_usd 100 is my estimate (tub amortized over a few years plus power), not sourced.</t>
+          <t>V3 tier C changed: B for soreness in people who train (Machado 2016: small edge over passive rest, best near 10 to 15 C for 10 to 15 min; Moore 2022: soreness, perceived recovery and power better at 24 h after high-intensity work), C for everyone else (Cain 2025: 11 RCTs in healthy adults; stress lower only at 12 h; no mood change in the one mood study; sleep and quality of life each rest on a single study; inflammation up right after). Well supported: a small soreness benefit. Popular but thin: mood, dopamine, immunity, resilience. The dopamine figure that circulates traces to Sramek 2000, a one-hour head-out immersion at 14 C, not a 3-minute plunge. Buijze 2016: cold showers cut sick-leave days but not illness days. V3's 'an evening plunge can make it harder to fall asleep' is NOT supported: Robey 2013 and Chauvineau 2021 (small, trained men, lab sleep tests) found no change in sleep onset, and Chauvineau found fewer night arousals. V3's blunted-growth point is confirmed (Roberts 2015; Pinero 2024 applies to cold water within about 15 min after lifting). Popular 2 to 5 minute plunges are shorter than the 10 to 15 minutes best studied for soreness. Key mismatch: the overlap file lists 'cold-plunge-ice-bath-tub-owned', but the V3 row key is 'cold-plunge-ice-bath' and had no overlap group; see overlap_proposals. Safety: Shattock and Tipton 2012 for heart rhythm; the pregnancy, diabetes, blood pressure and medication rows rest on standard tub label warnings (read in a combined hot and cold tub manual, CSC Chill1000), which also flag alcohol and drowning risk. The schema has no alcohol or plunging-alone condition, so suggest an item-level caution: ease in, never alone, never after drinking. kind 'device' assumes an owned tub; a DIY ice bath would be 'practice'. cost_month_usd 100 is my estimate (tub amortized over a few years plus power), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6462,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -6502,7 +6478,7 @@
       <c r="Q36" s="3" t="n"/>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>Daily sunscreen is one of the best-studied habits in skin care. In a 4.5-year trial of 903 adults, daily users showed no detectable rise in skin aging, and about a quarter less aging than occasional users.</t>
+          <t>In a 4.5-year Australian trial of 903 adults, daily sunscreen users showed no detectable rise in skin aging, and about a quarter less than occasional users.</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -6576,7 +6552,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>Tier A rests on one large independent RCT (Hughes 2013: n=903, 4.5 years, government-funded) plus a systematic review (Ronsch &amp; Bauer 2021) in which both photoaging trials favored sunscreen. That review calls the overall evidence base limited and notes guidelines put shade and clothing first, so a strict reading of 'several RCTs' could argue B. Both A and B keep it via EVIDENCE_REGULAR. The trial abstract gives no SPF; SPF 30+ and 1 teaspoon for the face are AAD advice. Skin-cancer outcomes are left out of person-facing text because they would be a medical claim. V3 overstated two things: 'nothing else on the shelf comes close' (retinoids have more photoaging RCTs) and 'the evidence is as strong as evidence gets'. kind=practice because the kind list has no topical-product option; propose adding one. UNUSED is included per its definition (a bottle can sit unused); drop it if sunscreen should never be proposed for letting go. No overlap group: if the table has an SPF moisturizer, SPF makeup or oral sun pills, propose a 'sun protection' group with keep-best-evidence. dose_unit is blank because the unit list has no % or teaspoon. how_common and cost are estimates.</t>
+          <t>Tier A rests on one large independent RCT (Hughes 2013: n=903, 4.5 years, government-funded) plus a systematic review (Ronsch &amp; Bauer 2021) in which both photoaging trials favored sunscreen. That review calls the overall evidence base limited and notes guidelines put shade and clothing first, so a strict reading of 'several RCTs' could argue B. Both A and B keep it via EVIDENCE_REGULAR. The trial abstract gives no SPF; SPF 30+ and 1 teaspoon for the face are AAD advice. Skin-cancer outcomes are left out of person-facing text because they would be a medical claim. V3 overstated two things: 'nothing else on the shelf comes close' (retinoids have more photoaging RCTs) and 'the evidence is as strong as evidence gets'. kind=practice because the kind list has no topical-product option; propose adding one. UNUSED is included per its definition (a bottle can sit unused); drop it if sunscreen should never be proposed for letting go. No overlap group: if the table has an SPF moisturizer, SPF makeup or oral sun pills, propose a 'sun protection' group with keep-best-evidence. dose_unit is blank because the unit list has no % or teaspoon. how_common and cost are estimates. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6616,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -6656,7 +6632,7 @@
       <c r="Q37" s="3" t="n"/>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>Retinoids are the best-studied ingredients for fine lines. Trial reviews show tretinoin and over-the-counter retinol both smooth fine lines over months, and in a 48-week trial a milder tretinoin worked as well with less irritation.</t>
+          <t>Retinoids are the best-studied ingredients for fine lines. Tretinoin smooths them over months, and a milder strength works as well with less irritation; over-the-counter retinol has thinner but similar evidence.</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -6698,7 +6674,7 @@
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>A drugstore retinol on two or three nights a week, at a fraction of a premium serum's price.</t>
+          <t>Two or three retinoid nights a week, building up as the skin adjusts.</t>
         </is>
       </c>
       <c r="AC37" s="3" t="n"/>
@@ -6734,7 +6710,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>Tier A is for the class. Tretinoin has two systematic reviews (Sitohang 2022: 7 RCTs; Siddiqui 2024: 25 comparison studies), and both tretinoin and retinol were significant for fine wrinkles in a 23-RCT network meta-analysis (Lin 2025, which has internal inconsistencies and one co-author company affiliation). Over-the-counter retinol alone is closer to B (Kafi 2007: n=36, mean age 87, up to 3 times a week). The 2005 Cochrane photodamage review was withdrawn in 2015 over a sponsorship conflict, so it is not cited. Adapalene was not significant for fine wrinkles in Lin 2025 (very wide CI), so fits_instead points to drugstore retinol, not adapalene. never_clear=no because the row mixes OTC and prescription products; prescribed use is caught by the on-medication safety row, but splitting it into 'OTC retinol' and 'prescription retinoid' (never_clear yes) would be cleaner. V3 contradicted itself: goalNotes named overlap 'exfoliants' but overlapGroups was empty. A retinoid is not an exfoliant and should never be the step dropped, hence the proposed 'retinoid nights' group (keep-best-evidence). Pregnancy: the data show no clear harm but are underpowered (Kaplan 2015). The AAD says stop tazarotene, and most experts stop tretinoin and adapalene; the AAD does not address retinol, which is treated the same way as a precaution. The breastfeeding row rests on e-lactancia (APILAM, updated 2023-02-09, opened this session); LactMed was blocked by a captcha, so it is not cited. Concentrations need a % unit, which the list lacks. Lowest studied doses that worked: tretinoin 0.025% (Griffiths 1995), retinol 0.4% (Kafi 2007). Cost $25 (V3 had $40) is an estimate: drugstore retinol is about $10 a month, telehealth tretinoin $20 to 40, premium serums $30 to 45.</t>
+          <t>Tier A is for the class. Tretinoin has two systematic reviews (Sitohang 2022: 7 RCTs; Siddiqui 2024: 25 comparison studies), and both tretinoin and retinol were significant for fine wrinkles in a 23-RCT network meta-analysis (Lin 2025, which has internal inconsistencies and one co-author company affiliation). Over-the-counter retinol alone is closer to B (Kafi 2007: n=36, mean age 87, up to 3 times a week). The 2005 Cochrane photodamage review was withdrawn in 2015 over a sponsorship conflict, so it is not cited. Adapalene was not significant for fine wrinkles in Lin 2025 (very wide CI), so fits_instead points to drugstore retinol, not adapalene. never_clear=no because the row mixes OTC and prescription products; prescribed use is caught by the on-medication safety row, but splitting it into 'OTC retinol' and 'prescription retinoid' (never_clear yes) would be cleaner. V3 contradicted itself: goalNotes named overlap 'exfoliants' but overlapGroups was empty. A retinoid is not an exfoliant and should never be the step dropped, hence the proposed 'retinoid nights' group (keep-best-evidence). Pregnancy: the data show no clear harm but are underpowered (Kaplan 2015). The AAD says stop tazarotene, and most experts stop tretinoin and adapalene; the AAD does not address retinol, which is treated the same way as a precaution. The breastfeeding row rests on e-lactancia (APILAM, updated 2023-02-09, opened this session); LactMed was blocked by a captcha, so it is not cited. Concentrations need a % unit, which the list lacks. Lowest studied doses that worked: tretinoin 0.025% (Griffiths 1995), retinol 0.4% (Kafi 2007). Cost $25 (V3 had $40) is an estimate: drugstore retinol is about $10 a month, telehealth tretinoin $20 to 40, premium serums $30 to 45. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6832,7 @@
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>A budget serum with 10 to 20% L-ascorbic acid, the best-studied form.</t>
+          <t>A serum with 10 to 20% L-ascorbic acid, the best-studied form.</t>
         </is>
       </c>
       <c r="AC38" s="3" t="n"/>
@@ -6888,7 +6864,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>Tier C (V3 had B). The only RCT-only review found 7 trials with 139 people in total (Correia 2023). A 2026 review of 44 studies says many were small, short, open-label or industry-sponsored. Reported effects: objective lightening and smoother skin; hydration was no better than placebo. V3 had stability backwards: L-ascorbic acid is the unstable form, while derivatives are stable but less studied, and in pig skin magnesium ascorbyl phosphate, ascorbyl palmitate and dehydroascorbic acid did not raise skin vitamin C (Pinnell 2001). FORM_NOT_ABSORBED therefore fits derivative-only or oxidized products. Derivatives do have small newer trials (Boghosian 2026), so present that code gently. V3's 'turned orange' check and 'opaque, airtight packaging' are common advice, but I found no independent source this session, so both stay out of person-facing text. Concentration needs a % unit: if one is added, set dose_min 10 (studied L-ascorbic acid serums ran 10 to 15%; Al-Niaimi 2017 says above 8% is needed and above 20% adds nothing) and add DOSE_BELOW_MIN. kind=practice because there is no topical-product kind; if the engine only applies FORM_NOT_ABSORBED to kind=supplement, this row needs an exception. Cost $30 (V3 had $60) is an estimate: budget serums are about $15 a month, premium ones $60 to 90.</t>
+          <t>Tier C (V3 had B). The only RCT-only review found 7 trials with 139 people in total (Correia 2023). A 2026 review of 44 studies says many were small, short, open-label or industry-sponsored. Reported effects: objective lightening and smoother skin; hydration was no better than placebo. V3 had stability backwards: L-ascorbic acid is the unstable form, while derivatives are stable but less studied, and in pig skin magnesium ascorbyl phosphate, ascorbyl palmitate and dehydroascorbic acid did not raise skin vitamin C (Pinnell 2001). FORM_NOT_ABSORBED therefore fits derivative-only or oxidized products. Derivatives do have small newer trials (Boghosian 2026), so present that code gently. V3's 'turned orange' check and 'opaque, airtight packaging' are common advice, but I found no independent source this session, so both stay out of person-facing text. Concentration needs a % unit: if one is added, set dose_min 10 (studied L-ascorbic acid serums ran 10 to 15%; Al-Niaimi 2017 says above 8% is needed and above 20% adds nothing) and add DOSE_BELOW_MIN. kind=practice because there is no topical-product kind; if the engine only applies FORM_NOT_ABSORBED to kind=supplement, this row needs an exception. Cost $30 (V3 had $60) is an estimate: budget serums are about $15 a month, premium ones $60 to 90. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7546,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -7586,7 +7562,7 @@
       <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>Pooled trials show it helps people fall asleep about 7 minutes sooner, and it eases jet lag well. Sleep doctors don't back it for ongoing insomnia, and more than 5 mg adds nothing measurable.</t>
+          <t>Pooled trials, mostly in people with sleep problems, show falling asleep about 7 minutes sooner, and it eases jet lag well. For good sleepers the gain is unclear, and sleep doctors don't back it for ongoing insomnia.</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -7614,7 +7590,7 @@
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -7670,7 +7646,7 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>V3's 7 and 8 minute figures confirmed (Ferracioli-Oda 2013: 19 RCTs, 1,683 people). V3's line 'more than 1 mg adds grogginess, not effect' is not supported: pooled effects rise with dose up to about 4 mg (Cruz-Sanabria 2024) and higher doses gave larger total-sleep gains (Ferracioli-Oda). The defensible 'less is more' line is that over 5 mg adds nothing measurable (Cochrane jet lag review; Cruz-Sanabria). AASM 2017 suggests clinicians not use melatonin for chronic insomnia (weak, very low quality, based on 2 mg prolonged-release in over-55s); the summary reflects this. Tier B because the effect is consistent but small and mostly measured in people with sleep disorders; the jet lag evidence in healthy travellers is stronger. dose_min 0.1 mg = lowest dose that improved sleep (Zhdanova 2001, insomniacs over 50; 0.3 mg restored normal night levels; normal sleepers unaffected); 0.5 mg works for jet lag. UNUSED left off because occasional travel use is a normal pattern. Cadence set to daily, though many people use it only some nights. Erland 2017 (supplement content survey) not opened; NCCIH page summarizes it. Cost is an estimate.</t>
+          <t>V3's 7 and 8 minute figures confirmed (Ferracioli-Oda 2013: 19 RCTs, 1,683 people). V3's line 'more than 1 mg adds grogginess, not effect' is not supported: pooled effects rise with dose up to about 4 mg (Cruz-Sanabria 2024) and higher doses gave larger total-sleep gains (Ferracioli-Oda). The defensible 'less is more' line is that over 5 mg adds nothing measurable (Cochrane jet lag review; Cruz-Sanabria). AASM 2017 suggests clinicians not use melatonin for chronic insomnia (weak, very low quality, based on 2 mg prolonged-release in over-55s); the summary reflects this. Tier B because the effect is consistent but small and mostly measured in people with sleep disorders; the jet lag evidence in healthy travellers is stronger. dose_min 0.1 mg = lowest dose that improved sleep (Zhdanova 2001, insomniacs over 50; 0.3 mg restored normal night levels; normal sleepers unaffected); 0.5 mg works for jet lag. UNUSED left off because occasional travel use is a normal pattern. Cadence set to daily, though many people use it only some nights. Erland 2017 (supplement content survey) not opened; NCCIH page summarizes it. Cost is an estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7726,7 @@
       <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>The melatonin inside is the only ingredient with consistent trial support, and it buys a few minutes. When 25 gummy brands were lab-tested, 22 were mislabeled, one had no melatonin, and one held about 3.5 times the label.</t>
+          <t>Melatonin is the ingredient with trial support: a few minutes sooner to sleep, in people with sleep problems. Lab tests of 25 gummy brands found 22 mislabeled and one without melatonin.</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -7796,7 +7772,7 @@
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>A low dose of plain melatonin, 0.5 to 3 mg, for about a third of the price.</t>
+          <t>Plain melatonin on travel nights, where it helps most.</t>
         </is>
       </c>
       <c r="AC44" s="3" t="n"/>
@@ -7832,7 +7808,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>V3 graded B; regraded C, which reflects indirect evidence. No independent trials of blended sleep gummies were found. The working ingredient is melatonin (tier B on its own), but gummy doses are unreliable (Cohen 2023: 22 of 25 mislabeled, 74% to 347% of label, one product with no melatonin but 31 mg CBD). Valerian, common in blends, got a weak recommendation against for insomnia from AASM 2017; the other herbs were not graded here. The router could lift this to melatonin's tier only when a melatonin dose is confirmed; a melatonin-free gummy should route with herb blends (C or D). The 'third of the price' line rests on my cost estimates (about 18 vs 5 USD a month), not a source.</t>
+          <t>V3 graded B; regraded C, which reflects indirect evidence. No independent trials of blended sleep gummies were found. The working ingredient is melatonin (tier B on its own), but gummy doses are unreliable (Cohen 2023: 22 of 25 mislabeled, 74% to 347% of label, one product with no melatonin but 31 mg CBD). Valerian, common in blends, got a weak recommendation against for insomnia from AASM 2017; the other herbs were not graded here. The router could lift this to melatonin's tier only when a melatonin dose is confirmed; a melatonin-free gummy should route with herb blends (C or D). The 'third of the price' line rests on my cost estimates (about 18 vs 5 USD a month), not a source. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8340,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -8380,7 +8356,7 @@
       <c r="Q48" s="3" t="n"/>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>Large studies link steady sleep and wake times, weekends included, to better health and longer life. A small trial in students found keeping regular times lifted daytime alertness, and sleep experts agree regularity matters.</t>
+          <t>Large observational studies link steady sleep times to better health. One small student trial found regular times lifted daytime alertness. When weekday sleep runs short, some weekend catch-up can help.</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -8394,7 +8370,7 @@
       <c r="W48" s="3" t="inlineStr"/>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr"/>
@@ -8446,7 +8422,7 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>V3 graded A from one cohort; regraded B, since the brief's A needs meta-analyses or several RCTs in healthy adults. Evidence: large observational cohorts (Windred 2024: 60,977 people, mean age 63, so not the 22 to 35 group; it measured overall sleep regularity, not wake time alone), a systematic review of mostly observational studies (Chaput 2020, very low to moderate certainty), an expert consensus (Sletten 2023, National Sleep Foundation), one small controlled trial in students (Manber 1996; the abstract does not say whether groups were randomized), and stimulus control, which includes waking at the same time daily, for chronic insomnia (Edinger 2021, conditional, low-quality evidence). No trial isolates wake time alone in healthy adults. V3's '60,000 people' figure is confirmed (60,977). V3's 'single strongest sleep habit we know of' is not something these sources establish.</t>
+          <t>V3 graded A from one cohort; regraded B, since the brief's A needs meta-analyses or several RCTs in healthy adults. Evidence: large observational cohorts (Windred 2024: 60,977 people, mean age 63, so not the 22 to 35 group; it measured overall sleep regularity, not wake time alone), a systematic review of mostly observational studies (Chaput 2020, very low to moderate certainty), an expert consensus (Sletten 2023, National Sleep Foundation), one small controlled trial in students (Manber 1996; the abstract does not say whether groups were randomized), and stimulus control, which includes waking at the same time daily, for chronic insomnia (Edinger 2021, conditional, low-quality evidence). No trial isolates wake time alone in healthy adults. V3's '60,000 people' figure is confirmed (60,977). V3's 'single strongest sleep habit we know of' is not something these sources establish. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8644,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -8684,7 +8660,7 @@
       <c r="Q50" s="3" t="n"/>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>In an online trial of nearly 1,000 adults, a week of reading in bed left 42% reporting better sleep, versus 28% without. A small lab study found paper books, unlike a bright tablet, left melatonin untouched.</t>
+          <t>In an online trial of nearly 1,000 adults, a week of reading in bed left 42% reporting better sleep, versus 28% without; sleep was self-rated. A bright tablet disturbed sleep more than paper.</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -8710,7 +8686,7 @@
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr"/>
@@ -8762,7 +8738,7 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>V3 graded C ('small trials versus screens favour paper'); regraded B because two randomized studies agree, though both are short. Finucane 2021 is large (991 randomized) but one week long, unblinded, with a single-item self-reported outcome and more dropouts among readers; e-readers were not excluded and paper was not required. Its secondary sleep-disturbance gain was small. Chang 2015 (12 people, inpatient) compared a printed book with a tablet at full brightness for 4 hours, not with no reading. So the support is for reading in general and for print over bright screens; paper versus e-ink has not been tested. Cost set to 0 because the habit is free; books are optional.</t>
+          <t>V3 graded C ('small trials versus screens favour paper'); regraded B because two randomized studies agree, though both are short. Finucane 2021 is large (991 randomized) but one week long, unblinded, with a single-item self-reported outcome and more dropouts among readers; e-readers were not excluded and paper was not required. Its secondary sleep-disturbance gain was small. Chang 2015 (12 people, inpatient) compared a printed book with a tablet at full brightness for 4 hours, not with no reading. So the support is for reading in general and for print over bright screens; paper versus e-ink has not been tested. Cost set to 0 because the habit is free; books are optional. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9122,7 @@
       <c r="Q53" s="3" t="n"/>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>One large Dutch trial found 29% fewer sick days, though people got ill just as often. Many reported more energy, but it wasn't measured.</t>
+          <t>One large Dutch trial found 29% fewer self-reported sick days, though people got ill just as often. Energy wasn't measured.</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -9228,7 +9204,7 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>Tier C: a single pragmatic RCT (Buijze 2016, PLoS One, n=3018 Dutch workers, opened full text): sickness absence IRR 0.71 at 90 days, illness days unchanged, no difference between 30, 60 and 90 s. Unblinded, all self-report, 20% attrition. Energy was not measured formally; authors only report it as the most common perceived benefit. Cain 2025 meta-analysis (11 studies, mostly baths, only 1 shower) found stress lower at 12 h and an acute inflammation spike, and cites the Buijze sick-day result narratively. Safety row: Buijze excluded people with serious cardiac comorbidity; cold shock is better described for immersion (Shattock 2012) than for showers, so I set clinician-first rather than never-suggest. Free, so no UNUSED.</t>
+          <t>Tier C: a single pragmatic RCT (Buijze 2016, PLoS One, n=3018 Dutch workers, opened full text): sickness absence IRR 0.71 at 90 days, illness days unchanged, no difference between 30, 60 and 90 s. Unblinded, all self-report, 20% attrition. Energy was not measured formally; authors only report it as the most common perceived benefit. Cain 2025 meta-analysis (11 studies, mostly baths, only 1 shower) found stress lower at 12 h and an acute inflammation spike, and cites the Buijze sick-day result narratively. Safety row: Buijze excluded people with serious cardiac comorbidity; cold shock is better described for immersion (Shattock 2012) than for showers, so I set clinician-first rather than never-suggest. Free, so no UNUSED. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -9360,11 +9336,7 @@
           <t>When did you last press play on a workout?</t>
         </is>
       </c>
-      <c r="AB54" s="3" t="inlineStr">
-        <is>
-          <t>Free workout videos or a saved routine keep the same sessions.</t>
-        </is>
-      </c>
+      <c r="AB54" s="3" t="n"/>
       <c r="AC54" s="3" t="n"/>
       <c r="AD54" s="3" t="inlineStr">
         <is>
@@ -9398,7 +9370,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>Structured like a training row: A for the exercise when it happens (WHO 2020 guidelines, Bull et al., opened abstract: 150-300 min/week moderate plus muscle strengthening), requires trains. tier_otherwise C from Romeo 2019 JMIR (9 RCTs, 1740 adults, objective activity): apps produced a nonsignificant +477 steps/day (P=.19); short programmes under 3 months did better. dose_min 150 min is per week (WHO), not per day; the unit list has no min/week. Price: Apple Fitness+ $9.99/month or $79.99/year (apple.com, opened). Peloton's pricing page rendered $0 (display error), and Ladder wasn't opened, so 15 is an estimate across the three. V3 said B; the 'outlive the habit' line isn't tested for fitness apps specifically (DellaVigna 2006 is gyms).</t>
+          <t>Structured like a training row: A for the exercise when it happens (WHO 2020 guidelines, Bull et al., opened abstract: 150-300 min/week moderate plus muscle strengthening), requires trains. tier_otherwise C from Romeo 2019 JMIR (9 RCTs, 1740 adults, objective activity): apps produced a nonsignificant +477 steps/day (P=.19); short programmes under 3 months did better. dose_min 150 min is per week (WHO), not per day; the unit list has no min/week. Price: Apple Fitness+ $9.99/month or $79.99/year (apple.com, opened). Peloton's pricing page rendered $0 (display error), and Ladder wasn't opened, so 15 is an estimate across the three. V3 said B; the 'outlive the habit' line isn't tested for fitness apps specifically (DellaVigna 2006 is gyms). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9434,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -9478,7 +9450,7 @@
       <c r="Q55" s="3" t="n"/>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>Across 41 studies, food-logging apps brought small gains in eating habits and weight. The gains come from logging, which the free tier also allows.</t>
+          <t>Across 41 studies, app programs that pair logging with coaching brought small gains in eating habits and weight. Logging alone showed no diet change in one trial, and premium tiers are untested.</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -9496,7 +9468,7 @@
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -9514,11 +9486,7 @@
           <t>Do you still log, or just pay?</t>
         </is>
       </c>
-      <c r="AB55" s="3" t="inlineStr">
-        <is>
-          <t>The free version still does the logging.</t>
-        </is>
-      </c>
+      <c r="AB55" s="3" t="n"/>
       <c r="AC55" s="3" t="n"/>
       <c r="AD55" s="3" t="inlineStr">
         <is>
@@ -9548,7 +9516,7 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>Tier B: Villinger 2019 Obes Rev meta-analysis (41 studies, 27 RCTs, 6348 people): g=0.19 for nutrition behaviours, g=0.30 for obesity indices; commercial vs research app made no difference. Effects are small and the premium tier specifically isn't tested; I wrote the free-tier line from my own knowledge that MyFitnessPal's free tier logs food (not from an opened source) so Veer may want to check. Kept clear_when to UNUSED only so a used app is protected. Safety: Simpson &amp; Mazzeo 2017 (n=493 students, cross-sectional) linked calorie trackers with more eating concern and restraint; Hahn 2021 RCT (200 low-risk undergraduate women, 1 month MyFitnessPal) found no change in eating disorder risk. So the risk sits with people with an eating disorder history; clinician-first. Price: MyFitnessPal Premium $19.99/month or $79.99/year (myfitnesspal.com/premium, opened); annual works out near $7/month.</t>
+          <t>Tier B: Villinger 2019 Obes Rev meta-analysis (41 studies, 27 RCTs, 6348 people): g=0.19 for nutrition behaviours, g=0.30 for obesity indices; commercial vs research app made no difference. Effects are small and the premium tier specifically isn't tested; I wrote the free-tier line from my own knowledge that MyFitnessPal's free tier logs food (not from an opened source) so Veer may want to check. Kept clear_when to UNUSED only so a used app is protected. Safety: Simpson &amp; Mazzeo 2017 (n=493 students, cross-sectional) linked calorie trackers with more eating concern and restraint; Hahn 2021 RCT (200 low-risk undergraduate women, 1 month MyFitnessPal) found no change in eating disorder risk. So the risk sits with people with an eating disorder history; clinician-first. Price: MyFitnessPal Premium $19.99/month or $79.99/year (myfitnesspal.com/premium, opened); annual works out near $7/month. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9916,7 @@
       <c r="Q58" s="3" t="n"/>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>A 2024 review of 17 small studies found a small drop in soreness. Muscle strength and damage markers barely changed.</t>
+          <t>A 2024 review of 17 small studies found a small to moderate drop in felt soreness. Effects on strength and damage markers were inconsistent.</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -9992,11 +9960,7 @@
           <t>Is it the soreness, or the half hour lying still?</t>
         </is>
       </c>
-      <c r="AB58" s="3" t="inlineStr">
-        <is>
-          <t>Legs up the wall for ten minutes after a hard day.</t>
-        </is>
-      </c>
+      <c r="AB58" s="3" t="n"/>
       <c r="AC58" s="3" t="n"/>
       <c r="AD58" s="3" t="inlineStr">
         <is>
@@ -10030,7 +9994,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>Tier C: Maia 2024 Biol Sport meta-analysis (opened full text, public grant funding, no COI): 17 studies, 319 athletes and healthy adults. Soreness g=0.49 at 0-2 h and 0.37 at 96 h, nonsignificant at 24-72 h; muscle function trivial and nonsignificant; creatine kinase unclear; lactate and heart rate unaffected. Authors call the evidence preliminary. No safety row added: pneumatic compression is usually avoided with a suspected clot, but neither the review nor the Hyperice page I opened says so, so I left it out; worth Veer adding with a source. Price: Normatec 3 Legs $899 (hyperice.com, opened), /24 = about $37; Normatec Go $379, Elite Legs $1,099. Legs-up swap is my suggestion, untested.</t>
+          <t>Tier C: Maia 2024 Biol Sport meta-analysis (opened full text, public grant funding, no COI): 17 studies, 319 athletes and healthy adults. Soreness g=0.49 at 0-2 h and 0.37 at 96 h, nonsignificant at 24-72 h; muscle function trivial and nonsignificant; creatine kinase unclear; lactate and heart rate unaffected. Authors call the evidence preliminary. No safety row added: pneumatic compression is usually avoided with a suspected clot, but neither the review nor the Hyperice page I opened says so, so I left it out; worth Veer adding with a source. Price: Normatec 3 Legs $899 (hyperice.com, opened), /24 = about $37; Normatec Go $379, Elite Legs $1,099. Legs-up swap is my suggestion, untested. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10532,7 @@
       <c r="Q62" s="3" t="n"/>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>A subscription only helps when it gets used. Research on gym members shows people often keep paying long after the visits stop.</t>
+          <t>A subscription only helps when it gets used. A large gym study found members often paid for far more than got used.</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -10630,7 +10594,7 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>Catch-all row for any subscription a person forgot about; kept general as asked: tier N, clear_when UNUSED only (no BORROWED_WEAK, since the engine shouldn't judge an unknown product's evidence). Area 'mind' is a placeholder; the schema needs one, and Veer may want a neutral option. Cost 0 because the real amount comes from the person's own statement. DellaVigna 2006 AER (opened abstract): monthly gym members paid over $70 for 4.3 visits a month, over $17 a visit vs $10 on a pass, overestimated future attendance and delayed cancelling. It's gyms only, so I used it for the general pattern, not a tier. V3's '30 days unused' threshold has no source I found; it's a product rule.</t>
+          <t>Catch-all row for any subscription a person forgot about; kept general as asked: tier N, clear_when UNUSED only (no BORROWED_WEAK, since the engine shouldn't judge an unknown product's evidence). Area 'mind' is a placeholder; the schema needs one, and Veer may want a neutral option. Cost 0 because the real amount comes from the person's own statement. DellaVigna 2006 AER (opened abstract): monthly gym members paid over $70 for 4.3 visits a month, over $17 a visit vs $10 on a pass, overestimated future attendance and delayed cancelling. It's gyms only, so I used it for the general pattern, not a tier. V3's '30 days unused' threshold has no source I found; it's a product rule. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10804,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -10856,7 +10820,7 @@
       <c r="Q64" s="3" t="n"/>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>In loud recorded hospital noise, earplugs with a mask gave more dream sleep and fewer brief wakings. Hospital studies of earplugs alone are mixed but mostly favourable.</t>
+          <t>In a lab night of loud recorded hospital noise, earplugs with a mask gave more dream sleep and fewer brief wakings. Most other studies are in hospital patients.</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -10874,7 +10838,7 @@
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -10926,7 +10890,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>Tier B kept from V3 but scoped to noisy rooms. Hu 2010 (Crit Care, n=14 healthy volunteers, randomised night order, about 66 dB(A) playback): plugs plus mask raised REM 9.3% to 12.9%, cut arousal index 15.1 to 12.2, better perceived sleep; total sleep time and sleep latency not significant; plugs and mask combined. Karimi 2021 meta: earplug-only ICU studies mixed (Litton 2017, Baghaie Lakeh 2018 null). No good trial in quiet bedrooms or of healthy people at home, so evidence_for is limited to noise. I did not find a review of earplugs in healthy adults at home. Price: estimate, foam plugs about $0.10-0.20 a pair, reusable silicone/Loop-style a one-off $25-35. In noise-masking group with white noise (show-together, not redundancy, so no OVERLAP clear code here).</t>
+          <t>Tier B kept from V3 but scoped to noisy rooms. Hu 2010 (Crit Care, n=14 healthy volunteers, randomised night order, about 66 dB(A) playback): plugs plus mask raised REM 9.3% to 12.9%, cut arousal index 15.1 to 12.2, better perceived sleep; total sleep time and sleep latency not significant; plugs and mask combined. Karimi 2021 meta: earplug-only ICU studies mixed (Litton 2017, Baghaie Lakeh 2018 null). No good trial in quiet bedrooms or of healthy people at home, so evidence_for is limited to noise. I did not find a review of earplugs in healthy adults at home. Price: estimate, foam plugs about $0.10-0.20 a pair, reusable silicone/Loop-style a one-off $25-35. In noise-masking group with white noise (show-together, not redundancy, so no OVERLAP clear code here). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11008,7 @@
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>A free sound app or a fan gives the same steady sound.</t>
+          <t>A sound app or a fan gives the same steady sound.</t>
         </is>
       </c>
       <c r="AC65" s="3" t="n"/>
@@ -11080,7 +11044,7 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>Riedy 2021 (Sleep Med Rev 55:101385, PROSPERO-registered, 38 studies): GRADE very low for continuous noise improving sleep; findings ranged from improved to disrupted; authors warn about possible harm to sleep and hearing and call for objective measures. Read abstract via Europe PMC only (PubMed blocked). C not D because there are many human studies, just inconsistent. The V3 line about masking real noise is plausible but I did not find a trial isolating it. Price: estimate, $30-60 machine over 24 months, apps often free. OVERLAP code is there for people who use both earplugs and a machine; Veer may prefer to drop it.</t>
+          <t>Riedy 2021 (Sleep Med Rev 55:101385, PROSPERO-registered, 38 studies): GRADE very low for continuous noise improving sleep; findings ranged from improved to disrupted; authors warn about possible harm to sleep and hearing and call for objective measures. Read abstract via Europe PMC only (PubMed blocked). C not D because there are many human studies, just inconsistent. The V3 line about masking real noise is plausible but I did not find a trial isolating it. Price: estimate, $30-60 machine over 24 months, apps often free. OVERLAP code is there for people who use both earplugs and a machine; Veer may prefer to drop it. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11444,7 @@
       <c r="Q68" s="3" t="n"/>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>Strips and dilators open the nose a little. A 2016 review found no measurable drop in snoring or sleep apnea, though some bed partners heard less snoring.</t>
+          <t>Strips and dilators open the nose a little. A 2016 review of people with sleep apnea found no measurable drop in snoring or apnea.</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -11546,7 +11510,7 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>Camacho 2016 (Pulm Med, 14 studies, 294 patients, mostly small non-randomised, people with snoring/OSA): snore index change not significant (-2.5/hr overall; strips -3.1/hr), AHI unchanged, lowest O2 sat +1% (abstract and results disagree on significance). One included study found bed partners reported mildly less snoring. Improved nasal airflow is accepted. A consumer site claimed two GSK-sponsored RCTs found no sleep-quality benefit vs placebo strips; I could not verify, not used. C rather than D because human trials exist with mixed subjective vs objective results. Price: estimate, about $0.40-0.50 per strip nightly. Safety row added for sleep apnea.</t>
+          <t>Camacho 2016 (Pulm Med, 14 studies, 294 patients, mostly small non-randomised, people with snoring/OSA): snore index change not significant (-2.5/hr overall; strips -3.1/hr), AHI unchanged, lowest O2 sat +1% (abstract and results disagree on significance). One included study found bed partners reported mildly less snoring. Improved nasal airflow is accepted. A consumer site claimed two GSK-sponsored RCTs found no sleep-quality benefit vs placebo strips; I could not verify, not used. C rather than D because human trials exist with mixed subjective vs objective results. Price: estimate, about $0.40-0.50 per strip nightly. Safety row added for sleep apnea. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11632,7 @@
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>A satin pillowcase gives the same smooth feel for less.</t>
+          <t>A satin pillowcase gives the same smooth feel.</t>
         </is>
       </c>
       <c r="AC69" s="3" t="n"/>
@@ -11700,7 +11664,7 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>D: for hair the only support is friction reasoning and a seller's own lab test (Mulberry Park Silks, not opened, brand). The one registered trial (NCT00767104, Wake Forest, collaborator Precision Fabrics Group, n=40, 12 weeks, results posted 2017) used a silk-like synthetic, not silk, and found 13% vs 22% lesion reduction for silk-like vs cotton with overlapping CIs - no benefit. Healthline's claim that this trial showed fewer pimples contradicts the posted results. Marked brand_funded yes because a fabric maker collaborated (funding split not stated). Price: estimate, $25-90 pillowcase over 24 months.</t>
+          <t>D: for hair the only support is friction reasoning and a seller's own lab test (Mulberry Park Silks, not opened, brand). The one registered trial (NCT00767104, Wake Forest, collaborator Precision Fabrics Group, n=40, 12 weeks, results posted 2017) used a silk-like synthetic, not silk, and found 13% vs 22% lesion reduction for silk-like vs cotton with overlapping CIs - no benefit. Healthline's claim that this trial showed fewer pimples contradicts the posted results. Marked brand_funded yes because a fabric maker collaborated (funding split not stated). Price: estimate, $25-90 pillowcase over 24 months. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11886,7 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -11938,7 +11902,7 @@
       <c r="Q71" s="3" t="n"/>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>A 2020 review of 19 trials found bright light eased winter low mood more than dim light. The trials were small to medium and varied in quality.</t>
+          <t>In people diagnosed with seasonal depression, a 2020 review of 19 trials found bright light eased winter low mood more than dim light. For ordinary winter blues it is untested.</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -11964,7 +11928,7 @@
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -11984,7 +11948,7 @@
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>A morning walk outside brings bright light for free.</t>
+          <t>A morning walk outside brings bright light too, though it hasn't been tested the same way.</t>
         </is>
       </c>
       <c r="AC71" s="3" t="n"/>
@@ -12020,7 +11984,7 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>B: Pjrek 2020 (Psychother Psychosom, 19 RCTs vs dim light or sham ion generators): depression SMD -0.37, response RR 1.42, no publication bias, but moderate heterogeneity and moderate-high risk of bias (abstract). Golden 2005 meta: bright light ES 0.84 for seasonal depression, 0.53 non-seasonal (abstract). Not A: population is people with SAD, not healthy adults; evidence_requires has no 'seasonal low mood' option, so it is in evidence_for. For people without winter low mood the benefit is unproven; the engine may want a seasonal flag. Dose: 20-30 min at 10,000 lux each morning is the standard clinical protocol, but I did not open a dosing source, so dose_min is blank. Safety: Takeshima 2020 meta (6 RCTs, bipolar depression) found switch rate 4.7%, similar to control, mostly with mood stabilisers; authors suspect higher risk without one - kept clinician-first for bipolar. Price: estimate, $40-100 box over 24 months.</t>
+          <t>B: Pjrek 2020 (Psychother Psychosom, 19 RCTs vs dim light or sham ion generators): depression SMD -0.37, response RR 1.42, no publication bias, but moderate heterogeneity and moderate-high risk of bias (abstract). Golden 2005 meta: bright light ES 0.84 for seasonal depression, 0.53 non-seasonal (abstract). Not A: population is people with SAD, not healthy adults; evidence_requires has no 'seasonal low mood' option, so it is in evidence_for. For people without winter low mood the benefit is unproven; the engine may want a seasonal flag. Dose: 20-30 min at 10,000 lux each morning is the standard clinical protocol, but I did not open a dosing source, so dose_min is blank. Safety: Takeshima 2020 meta (6 RCTs, bipolar depression) found switch rate 4.7%, similar to control, mostly with mood stabilisers; authors suspect higher risk without one - kept clinician-first for bipolar. Price: estimate, $40-100 box over 24 months. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12102,7 @@
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>Barefoot time on grass or sand keeps the outdoor part for free.</t>
+          <t>Barefoot time on grass or sand keeps the outdoor part.</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
@@ -12174,7 +12138,7 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>Chevalier 2012 review: three of five authors are contractors for and shareholders in the earthing company; the sleep study (Ghaly and Teplitz 2004, n=12) had no control group. That evidence counts as brand. Lin 2022 (Healthcare, n=22 randomised, 15 completed, mild Alzheimer's, age about 78, no funding, no COI declared, used an Earthing-brand mat): PSQI better vs sham at week 12 (p=0.006) but GEE model p=0.053; later corrected. A Korean pilot (n=60) surfaced in search but I did not open it. Grade D not N because one independent pilot exists, but it is tiny and in a very different population; no plausible mechanism shown. Price: estimate, $50-150 over 24 months; V3 had 30, which looks high.</t>
+          <t>Chevalier 2012 review: three of five authors are contractors for and shareholders in the earthing company; the sleep study (Ghaly and Teplitz 2004, n=12) had no control group. That evidence counts as brand. Lin 2022 (Healthcare, n=22 randomised, 15 completed, mild Alzheimer's, age about 78, no funding, no COI declared, used an Earthing-brand mat): PSQI better vs sham at week 12 (p=0.006) but GEE model p=0.053; later corrected. A Korean pilot (n=60) surfaced in search but I did not open it. Grade D not N because one independent pilot exists, but it is tiny and in a very different population; no plausible mechanism shown. Price: estimate, $50-150 over 24 months; V3 had 30, which looks high. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12414,7 @@
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>Yogurt or kefir with breakfast keeps the habit for less.</t>
+          <t>Yogurt or kefir with breakfast keeps the habit.</t>
         </is>
       </c>
       <c r="AC74" s="3" t="n"/>
@@ -12482,7 +12446,7 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>Tier C, kept from V3. Khalesi 2019 (45 trials, healthy adults) found transient colonisation and some support for stool consistency, bowel movements and immune markers; no persistent microbiome change. Rauch 2022 found no improvement in gut symptoms or permeability in healthy or active adults. Strain-specific evidence (e.g. antibiotic-associated diarrhoea) does not transfer to a generic daily capsule; I could not open the AGA 2020 guideline full text (403), so it is not cited. If someone was prescribed a strain for a diagnosed condition, that falls outside this row. Price: $30/month is the V3 estimate, not checked against a pricing page.</t>
+          <t>Tier C, kept from V3. Khalesi 2019 (45 trials, healthy adults) found transient colonisation and some support for stool consistency, bowel movements and immune markers; no persistent microbiome change. Rauch 2022 found no improvement in gut symptoms or permeability in healthy or active adults. Strain-specific evidence (e.g. antibiotic-associated diarrhoea) does not transfer to a generic daily capsule; I could not open the AGA 2020 guideline full text (403), so it is not cited. If someone was prescribed a strain for a diagnosed condition, that falls outside this row. Price: $30/month is the V3 estimate, not checked against a pricing page. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12736,7 @@
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>An orange or kiwi each morning keeps the ritual for less.</t>
+          <t>An orange or kiwi keeps the morning habit, though at less than the 200 mg studied.</t>
         </is>
       </c>
       <c r="AC76" s="3" t="n"/>
@@ -12808,7 +12772,7 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>Tier A for the narrow claim only: Cochrane 2013, 31 comparisons, 9,745 episodes; duration down 8% (3 to 12%) in adults, 14% in children. Incidence RR 0.97 in the general community; RR 0.48 in marathon runners, skiers and soldiers under heavy physical stress (could justify a stronger keep for heavy endurance trainers). Starting vitamin C once a cold begins showed no consistent effect, so the benefit needs regular daily use. dose_min 200 mg is the review's inclusion floor. LPI: full absorption up to 200 mg per dose, plasma plateaus at 200 to 400 mg/day, so 1,000 mg adds little. The effect is small; the A is about how solid the evidence is, not its size. Price is the V3 estimate.</t>
+          <t>Tier A for the narrow claim only: Cochrane 2013, 31 comparisons, 9,745 episodes; duration down 8% (3 to 12%) in adults, 14% in children. Incidence RR 0.97 in the general community; RR 0.48 in marathon runners, skiers and soldiers under heavy physical stress (could justify a stronger keep for heavy endurance trainers). Starting vitamin C once a cold begins showed no consistent effect, so the benefit needs regular daily use. dose_min 200 mg is the review's inclusion floor. LPI: full absorption up to 200 mg per dose, plasma plateaus at 200 to 400 mg/day, so 1,000 mg adds little. The effect is small; the A is about how solid the evidence is, not its size. Price is the V3 estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -14010,7 +13974,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -14026,7 +13990,7 @@
       <c r="Q84" s="3" t="n"/>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>Across 39 trials and 20,000 people, acupuncture eased chronic pain more than sham needling or none, and the effect mostly lasted a year. The gain over sham is small.</t>
+          <t>In people with chronic pain, 39 trials found acupuncture eased pain more than sham needling or none, mostly lasting a year. The gain over sham is small, and other uses are untested.</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -14044,7 +14008,7 @@
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
@@ -14092,7 +14056,7 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>Tier B for chronic pain only: Vickers 2018 IPD meta-analysis (39 high-quality trials, 20,827 patients) beat sham (~0.2 SD) and no acupuncture (~0.5 SD); NCCIH 2022 agrees, cites ACP 2017 and ACR 2019 guidelines. Effect over sham is small, so B not A. Area set to mind because most 22-35 users go for stress/calm; for stress, sleep or general wellness without pain I did not open trials and V3 called sleep trials weak, so treat non-pain use as C/D in conversation (human_question separates the two). B keep applies on paper to everyone; if the engine can key on purpose, only protect for pain. Safety: NCCIH says serious harms are rare and tied to non-sterile needles or untrained practitioners; no specific condition row sourced (bleeding-risk caution is common practice but I did not open a source, so no row). Cost: estimate, about $100-130 a session, roughly one a week or less; no pricing page opened.</t>
+          <t>Tier B for chronic pain only: Vickers 2018 IPD meta-analysis (39 high-quality trials, 20,827 patients) beat sham (~0.2 SD) and no acupuncture (~0.5 SD); NCCIH 2022 agrees, cites ACP 2017 and ACR 2019 guidelines. Effect over sham is small, so B not A. Area set to mind because most 22-35 users go for stress/calm; for stress, sleep or general wellness without pain I did not open trials and V3 called sleep trials weak, so treat non-pain use as C/D in conversation (human_question separates the two). B keep applies on paper to everyone; if the engine can key on purpose, only protect for pain. Safety: NCCIH says serious harms are rare and tied to non-sterile needles or untrained practitioners; no specific condition row sourced (bleeding-risk caution is common practice but I did not open a source, so no row). Cost: estimate, about $100-130 a session, roughly one a week or less; no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14290,7 @@
       <c r="Q86" s="3" t="n"/>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>GLP-1 drugs lower weight well in adults with obesity, semaglutide most. Testosterone helps men with confirmed low levels. Injectable wellness peptides have little human safety data.</t>
+          <t>For adults with obesity, prescribed GLP-1 drugs lower weight well; testosterone helps men with confirmed low levels. Injectable wellness peptides and compounded copies have little safety data.</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -14388,7 +14352,7 @@
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>never_clear yes per brief: prescribing care is the clinician's call, Distill only adds safety framing. Tier A applies to the GLP-1 part: Shi 2024 Lancet NMA (republished after 2022 retraction; 132 RCTs, 48,209 adults; independent funding) GLP-1 RAs ~5.8% extra weight loss, semaglutide ~11.4%; STEP 1 (Novo-funded) -14.9% vs -2.4%. TRT: Endocrine Society 2018 says diagnose only with symptoms plus repeatedly low morning T, and lists contraindications (planning fertility, prostate/breast cancer, high hematocrit, untreated severe OSA, uncontrolled heart failure, recent MI/stroke). Peptides (BPC-157, TB-500, CJC-1295, ipamorelin etc.): FDA compounding page (current 2026-04-22) lists them as withdrawn nominations or Category 2 with little or no human safety data: effectively tier N/D. FDA GLP-1 page (current 2026-10-01): compounded semaglutide/tirzepatide not FDA-reviewed, dosing-error hospitalisations, salt forms unlawful, counterfeit risk, 990+ and 730+ adverse event reports. Cadence weekly = typical weekly injection; moments any. Cost $300 is V3 estimate (telehealth GLP-1 programmes and TRT clinics vary roughly $150-1,300); no pricing page opened. area eat chosen since GLP-1 weight programmes dominate in this age group; TRT is move/energy. wearable_sees partial: resting HR and weight trends only.</t>
+          <t>never_clear yes per brief: prescribing care is the clinician's call, Distill only adds safety framing. Tier A applies to the GLP-1 part: Shi 2024 Lancet NMA (republished after 2022 retraction; 132 RCTs, 48,209 adults; independent funding) GLP-1 RAs ~5.8% extra weight loss, semaglutide ~11.4%; STEP 1 (Novo-funded) -14.9% vs -2.4%. TRT: Endocrine Society 2018 says diagnose only with symptoms plus repeatedly low morning T, and lists contraindications (planning fertility, prostate/breast cancer, high hematocrit, untreated severe OSA, uncontrolled heart failure, recent MI/stroke). Peptides (BPC-157, TB-500, CJC-1295, ipamorelin etc.): FDA compounding page (current 2026-04-22) lists them as withdrawn nominations or Category 2 with little or no human safety data: effectively tier N/D. FDA GLP-1 page (current 2026-10-01): compounded semaglutide/tirzepatide not FDA-reviewed, dosing-error hospitalisations, salt forms unlawful, counterfeit risk, 990+ and 730+ adverse event reports. Cadence weekly = typical weekly injection; moments any. Cost $300 is V3 estimate (telehealth GLP-1 programmes and TRT clinics vary roughly $150-1,300); no pricing page opened. area eat chosen since GLP-1 weight programmes dominate in this age group; TRT is move/energy. wearable_sees partial: resting HR and weight trends only. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14436,7 @@
       <c r="Q87" s="3" t="n"/>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>CBT-I is the first-choice approach for chronic insomnia. In 20 trials, people fell asleep about 19 minutes sooner and lay awake 26 fewer minutes at night, and it lasted.</t>
+          <t>CBT-I is the first-choice approach for chronic insomnia. In 20 trials of people with insomnia, sleep came about 19 minutes sooner with 26 fewer minutes awake, and the gains seemed to last.</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -14538,7 +14502,7 @@
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>Tier A: Trauer 2015 Ann Intern Med meta-analysis (20 RCTs, 1,162 adults with chronic insomnia, no funding): SOL -19 min, WASO -26 min, SE +9.9%, sustained; TST only +7.6 min (CI crosses 0). AASM 2021 guideline: STRONG recommendation for multicomponent CBT-I. Population is people with chronic insomnia, not all healthy adults, but evidence_for names that group. never_clear yes because a trained CBT-I clinician is sleep care; caution: 'sleep coach' is unregulated and many coaches do not deliver CBT-I (stimulus control plus sleep restriction plus cognitive work). Name says 'trained coach' to signal that; if Veer wants untrained sleep coaching as a separate row it should be C/N and clearable. I left fits_instead empty to avoid steering people away from clinician care; a possible line is the free VA 'CBT-i Coach' app, but I did not open a source for it. dose_typical from common practice (Trauer required &gt;=3 components but I did not read session counts in the abstract), so dose_min left blank. Cost $200/month is V3 estimate; no pricing page opened. wearable_sees partial: bed and wake times are visible.</t>
+          <t>Tier A: Trauer 2015 Ann Intern Med meta-analysis (20 RCTs, 1,162 adults with chronic insomnia, no funding): SOL -19 min, WASO -26 min, SE +9.9%, sustained; TST only +7.6 min (CI crosses 0). AASM 2021 guideline: STRONG recommendation for multicomponent CBT-I. Population is people with chronic insomnia, not all healthy adults, but evidence_for names that group. never_clear yes because a trained CBT-I clinician is sleep care; caution: 'sleep coach' is unregulated and many coaches do not deliver CBT-I (stimulus control plus sleep restriction plus cognitive work). Name says 'trained coach' to signal that; if Veer wants untrained sleep coaching as a separate row it should be C/N and clearable. I left fits_instead empty to avoid steering people away from clinician care; a possible line is the free VA 'CBT-i Coach' app, but I did not open a source for it. dose_typical from common practice (Trauer required &gt;=3 components but I did not read session counts in the abstract), so dose_min left blank. Cost $200/month is V3 estimate; no pricing page opened. wearable_sees partial: bed and wake times are visible. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14566,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -14618,7 +14582,7 @@
       <c r="Q88" s="3" t="n"/>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>In 26 trials, one-to-one dietitian visits improved diet quality, blood sugar and weight more than usual care. Weight changes were modest, about 1 kg extra.</t>
+          <t>In primary-care patients, one-to-one dietitian visits improved diet quality and, for people with diabetes, blood sugar. Extra weight loss was modest, about 1 kg.</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -14636,7 +14600,7 @@
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>THEIRS, LOVED, EVIDENCE_REGULAR</t>
+          <t>THEIRS, LOVED</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
@@ -14684,7 +14648,7 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>Tier B: Mitchell 2017 J Acad Nutr Diet systematic review (26 RCTs, 5,500 adults) favoured dietitian consults for glycaemic control (4/4), dietary change (4/4) and anthropometry; not lipids or BP. Williams 2019 meta-analysis (5 RCTs, n=1,598): -1.03 kg extra weight, risk of bias unclear to high, so B not A. Evidence is for registered dietitians; 'nutritionist' is not a protected title in most US states, so a non-credentialed nutritionist or health coach is closer to C/N. Not never_clear (not prescribing care) but if it is for diabetes, kidney disease or an eating disorder it is part of medical care: the engine should not suggest letting go then (no safety row because I did not open a source specific to that). Cost: estimate ~$150 for a monthly follow-up visit (V3 had 200); no pricing page opened.</t>
+          <t>Tier B: Mitchell 2017 J Acad Nutr Diet systematic review (26 RCTs, 5,500 adults) favoured dietitian consults for glycaemic control (4/4), dietary change (4/4) and anthropometry; not lipids or BP. Williams 2019 meta-analysis (5 RCTs, n=1,598): -1.03 kg extra weight, risk of bias unclear to high, so B not A. Evidence is for registered dietitians; 'nutritionist' is not a protected title in most US states, so a non-credentialed nutritionist or health coach is closer to C/N. Not never_clear (not prescribing care) but if it is for diabetes, kidney disease or an eating disorder it is part of medical care: the engine should not suggest letting go then (no safety row because I did not open a source specific to that). Cost: estimate ~$150 for a monthly follow-up visit (V3 had 200); no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15036,7 @@
       <c r="Q91" s="3" t="n"/>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>Two large trials tested diet advice matched to genes. It did no better than advice based on what people already ate, and gene type did not predict weight loss.</t>
+          <t>One large trial found gene-matched diet advice did no better than advice based on current eating. Another, in overweight adults, found gene type didn't predict weight loss.</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -15146,7 +15110,7 @@
       </c>
       <c r="AJ91" s="3" t="inlineStr">
         <is>
-          <t>Tier D chosen because the benefit claim rests on mechanism only, while well-run independent RCTs tested it and found no added benefit: Food4Me 2017 (n=1,269 completers, 7 countries) personalised advice beat generic advice, but adding genotype (5 variants) did not improve it further; DIETFITS 2018 JAMA (n=609) no diet x genotype interaction for 12-month weight loss. The tier scale has no 'tested and null' grade; flag for Veer whether this should read N or D. One-off purchase so UNUSED left out. Cost: estimate, ~$100-200 one-off spread over 24 months (V3 typical) ≈ $5; no pricing page opened. Ancestry and raw data are a fair reason to keep; the question focuses on the wellness reports.</t>
+          <t>Tier D chosen because the benefit claim rests on mechanism only, while well-run independent RCTs tested it and found no added benefit: Food4Me 2017 (n=1,269 completers, 7 countries) personalised advice beat generic advice, but adding genotype (5 variants) did not improve it further; DIETFITS 2018 JAMA (n=609) no diet x genotype interaction for 12-month weight loss. The tier scale has no 'tested and null' grade; flag for Veer whether this should read N or D. One-off purchase so UNUSED left out. Cost: estimate, ~$100-200 one-off spread over 24 months (V3 typical) ≈ $5; no pricing page opened. Ancestry and raw data are a fair reason to keep; the question focuses on the wellness reports. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15194,7 @@
       <c r="Q92" s="3" t="n"/>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>Hyperbaric oxygen is real medicine for diving injuries, carbon monoxide and some wounds. The wellness studies in healthy adults came from a clinic chain that sells it.</t>
+          <t>Hyperbaric oxygen is real medicine for diving injuries, carbon monoxide and some wounds. The wellness studies, in adults over 64, came from a clinic chain that sells it.</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -15296,7 +15260,7 @@
       </c>
       <c r="AJ92" s="3" t="inlineStr">
         <is>
-          <t>Tier N: the only healthy-adult studies I found (Hadanny 2020 RCT n=63 cognition; Hachmo 2020 single-arm n=35 telomeres) are by Efrati's group, authors employed by or shareholders in Aviv Scientific, which sells HBOT longevity programmes, so brand-funded counts as none. Both in adults over 64, not 22-35. Harvard Health 2024 (Catanese, reviewed by Shmerling) lists FDA-cleared uses (decompression sickness, CO poisoning, gas embolism, hard-to-heal wounds, burns, sudden hearing loss etc.), says claims for Alzheimer's, autism, cancer, Lyme are not FDA-approved; risks ear/sinus pain, eardrum rupture, vision change, rarely lung collapse, fire risk; FDA advises accredited facility. FDA's own consumer page returned 404 (moved), so I cite Harvard's summary. Wellness 'mild' soft chambers (~1.3 ATA) were not studied in anything I opened. Cost: estimate, sessions ~$100-250, a few a month; no pricing page opened.</t>
+          <t>Tier N: the only healthy-adult studies I found (Hadanny 2020 RCT n=63 cognition; Hachmo 2020 single-arm n=35 telomeres) are by Efrati's group, authors employed by or shareholders in Aviv Scientific, which sells HBOT longevity programmes, so brand-funded counts as none. Both in adults over 64, not 22-35. Harvard Health 2024 (Catanese, reviewed by Shmerling) lists FDA-cleared uses (decompression sickness, CO poisoning, gas embolism, hard-to-heal wounds, burns, sudden hearing loss etc.), says claims for Alzheimer's, autism, cancer, Lyme are not FDA-approved; risks ear/sinus pain, eardrum rupture, vision change, rarely lung collapse, fire risk; FDA advises accredited facility. FDA's own consumer page returned 404 (moved), so I cite Harvard's summary. Wellness 'mild' soft chambers (~1.3 ATA) were not studied in anything I opened. Cost: estimate, sessions ~$100-250, a few a month; no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15344,7 @@
       <c r="Q93" s="3" t="n"/>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>The medical version is for lymphedema, and even there it adds only a little to compression. For people without swelling, studies are tiny and measure the nervous system, not looks.</t>
+          <t>The medical version is for lymphedema, and even there it adds only a little to compression. There's no good evidence it de-puffs people without swelling.</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr">
@@ -15454,7 +15418,7 @@
       </c>
       <c r="AJ93" s="3" t="inlineStr">
         <is>
-          <t>Tier D: Ezzo 2015 Cochrane (6 RCTs, breast-cancer lymphedema) MLD added ~7% volume reduction to compression bandaging in 2 small trials; other comparisons not significant or too varied. PubMed search for healthy-subject trials found only small physiology studies (e.g. autonomic/H-reflex changes in J Bodyw Mov Ther 2021, neck MLD in students J Clin Med 2020) with no outcome on puffiness, skin or wellbeing; I read titles/results snippets only, not cited. 'Draining toxins' framing has no support. Area skin because the TikTok draw is de-puffing/face; also mind for the calm. Put in existing massage group (show-together) via overlaps; the group's member list in existing-overlaps.json does not yet include this key, so Veer/Ishan add it there. No safety row: heart failure and active clot are standard contraindications in MLD practice but I did not open a source. Cost: estimate ~$120 a session, about monthly (V3); no pricing page opened.</t>
+          <t>Tier D: Ezzo 2015 Cochrane (6 RCTs, breast-cancer lymphedema) MLD added ~7% volume reduction to compression bandaging in 2 small trials; other comparisons not significant or too varied. PubMed search for healthy-subject trials found only small physiology studies (e.g. autonomic/H-reflex changes in J Bodyw Mov Ther 2021, neck MLD in students J Clin Med 2020) with no outcome on puffiness, skin or wellbeing; I read titles/results snippets only, not cited. 'Draining toxins' framing has no support. Area skin because the TikTok draw is de-puffing/face; also mind for the calm. Put in existing massage group (show-together) via overlaps; the group's member list in existing-overlaps.json does not yet include this key, so Veer/Ishan add it there. No safety row: heart failure and active clot are standard contraindications in MLD practice but I did not open a source. Cost: estimate ~$120 a session, about monthly (V3); no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16142,7 @@
       <c r="Q98" s="3" t="n"/>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>Tribulus and D-aspartic acid didn't raise testosterone in trials. Four small fenugreek trials, pooled, showed a rise. Most blends hold untested ingredients, some above safe vitamin limits.</t>
+          <t>Tribulus and D-aspartic acid didn't raise testosterone in trials. Four fenugreek trials, pooled, showed a rise. Most blends hold untested ingredients, some above safe vitamin and mineral limits.</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -16244,7 +16208,7 @@
       </c>
       <c r="AJ98" s="3" t="inlineStr">
         <is>
-          <t>V3 graded N and said fenugreek has 'none on testosterone'; that part is contradicted: Mansoori 2020 (Phytother Res meta-analysis, 4 RCTs) found a significant rise in total testosterone. I only read the abstract, which gives no effect size or funding; fenugreek trials are commonly run with branded extracts, so check before upgrading. Tribulus: Qureshi 2014 systematic review (11 studies) found it ineffective in humans except within combined supplements. D-AA: Willoughby &amp; Leutholtz 2013 (3 g, 28 days, trained men) and Melville 2017 (6 g, 12 weeks, 22 trained men aged 18 to 36) both found no change in testosterone or training outcomes. Clemesha 2020 (50 products): 61.5% of 109 components had no testosterone data, 10.1% had data showing a decrease, and 13 products exceeded the UL for zinc, B3 or magnesium. Tier C because the ingredients disagree (fenugreek positive, tribulus and D-AA null) and no blend has been tested. No dose fields: blends vary too much. fits_instead left empty: I found no source for a lifestyle swap that raises testosterone in healthy young men. Price: V3's $40, my estimate; no pricing page opened. Area move because the purchase is about training and physique. Name and short_name avoid 'booster' because 'boost' is on the banned word list.</t>
+          <t>V3 graded N and said fenugreek has 'none on testosterone'; that part is contradicted: Mansoori 2020 (Phytother Res meta-analysis, 4 RCTs) found a significant rise in total testosterone. I only read the abstract, which gives no effect size or funding; fenugreek trials are commonly run with branded extracts, so check before upgrading. Tribulus: Qureshi 2014 systematic review (11 studies) found it ineffective in humans except within combined supplements. D-AA: Willoughby &amp; Leutholtz 2013 (3 g, 28 days, trained men) and Melville 2017 (6 g, 12 weeks, 22 trained men aged 18 to 36) both found no change in testosterone or training outcomes. Clemesha 2020 (50 products): 61.5% of 109 components had no testosterone data, 10.1% had data showing a decrease, and 13 products exceeded the UL for zinc, B3 or magnesium. Tier C because the ingredients disagree (fenugreek positive, tribulus and D-AA null) and no blend has been tested. No dose fields: blends vary too much. fits_instead left empty: I found no source for a lifestyle swap that raises testosterone in healthy young men. Price: V3's $40, my estimate; no pricing page opened. Area move because the purchase is about training and physique. Name and short_name avoid 'booster' because 'boost' is on the banned word list. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16330,7 @@
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>A morning coffee gives the same caffeine lift for less.</t>
+          <t>A morning coffee gives the same caffeine lift.</t>
         </is>
       </c>
       <c r="AC99" s="3" t="n"/>
@@ -16402,7 +16366,7 @@
       </c>
       <c r="AJ99" s="3" t="inlineStr">
         <is>
-          <t>V3 graded N; I graded C because caffeine and green tea do have trial data, just small effects. Jeukendrup &amp; Randell 2011 (Obes Rev review): only caffeine and green tea have data backing fat-metabolism effects; evidence lacking for carnitine, CLA, forskolin, chromium and others. Tabrizi 2019 (13 RCTs, 606 people, I2 above 90%): caffeine might promote weight, BMI and fat reduction; very heterogeneous. Jurgens 2012 Cochrane: green tea outside Japan, -0.04 kg over 12 weeks, not meaningful. Batsis 2021 (Obesity, 315 RCTs of supplements and alternative therapies): only 52 low-risk and sufficient, of which 16 showed weight differences of 0.3 to 4.93 kg. Geller 2015 (NEJM, ED surveillance 2004 to 2013, HHS-funded): weight-loss or energy products caused 71.8% of supplement adverse events with palpitations, chest pain or tachycardia, 58% in people aged 20 to 34. V3 said they 'disturb your sleep': true by way of caffeine, but I did not open a fat-burner sleep study, so the summary leaves it out; added to the evening-stimulants overlap group instead. Coffee swap is my inference from shared caffeine. Under-18 safety row not added because I did not open a pediatric source this round (AAP 2011 exists in the table for energy drinks; Ishan may want it extended). Price: V3's $40, my estimate.</t>
+          <t>V3 graded N; I graded C because caffeine and green tea do have trial data, just small effects. Jeukendrup &amp; Randell 2011 (Obes Rev review): only caffeine and green tea have data backing fat-metabolism effects; evidence lacking for carnitine, CLA, forskolin, chromium and others. Tabrizi 2019 (13 RCTs, 606 people, I2 above 90%): caffeine might promote weight, BMI and fat reduction; very heterogeneous. Jurgens 2012 Cochrane: green tea outside Japan, -0.04 kg over 12 weeks, not meaningful. Batsis 2021 (Obesity, 315 RCTs of supplements and alternative therapies): only 52 low-risk and sufficient, of which 16 showed weight differences of 0.3 to 4.93 kg. Geller 2015 (NEJM, ED surveillance 2004 to 2013, HHS-funded): weight-loss or energy products caused 71.8% of supplement adverse events with palpitations, chest pain or tachycardia, 58% in people aged 20 to 34. V3 said they 'disturb your sleep': true by way of caffeine, but I did not open a fat-burner sleep study, so the summary leaves it out; added to the evening-stimulants overlap group instead. Coffee swap is my inference from shared caffeine. Under-18 safety row not added because I did not open a pediatric source this round (AAP 2011 exists in the table for energy drinks; Ishan may want it extended). Price: V3's $40, my estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16940,7 @@
       <c r="Q103" s="3" t="n"/>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>No human trials of sea moss itself. Its iodine swings widely between products, and lab tests found arsenic, mercury and bacteria in some.</t>
+          <t>No human trials of sea moss itself. Seaweed products' iodine swings widely, and lab tests found arsenic, mercury and bacteria in some sea moss.</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr">
@@ -17050,7 +17014,7 @@
       </c>
       <c r="AJ103" s="3" t="inlineStr">
         <is>
-          <t>Tier D: searched Europe PMC for human trials of Chondrus crispus / sea moss / Irish moss and found none (only cow and hen feeding studies). Claims rest on mineral content, i.e. mechanism and anecdote. Safety evidence is real: Aakre 2021 (Norwegian market, not sea moss specifically, mostly kelps) shows seaweed iodine per serving often exceeds the UL; Rejuso 2026 is the first US sea moss product survey (66 products) with arsenic/cobalt/mercury in dried product and Salmonella/Cronobacter isolates. I could NOT open the NIH ODS iodine fact sheet (Cloudflare 403), so the adult UL (1,100 mcg) is not cited here; worth adding nih-ods iodine if another agent has it. Did not find a sea moss-specific iodine assay paper. Could arguably join daily-multivitamin overlap ('92 minerals' marketing) but I left overlaps empty since that group's members list doesn't include it. Price is an estimate (gels often $25 to $40 a jar), no pricing page opened. Rewrote fits_instead to avoid a claim I can't source about health benefit.</t>
+          <t>Tier D: searched Europe PMC for human trials of Chondrus crispus / sea moss / Irish moss and found none (only cow and hen feeding studies). Claims rest on mineral content, i.e. mechanism and anecdote. Safety evidence is real: Aakre 2021 (Norwegian market, not sea moss specifically, mostly kelps) shows seaweed iodine per serving often exceeds the UL; Rejuso 2026 is the first US sea moss product survey (66 products) with arsenic/cobalt/mercury in dried product and Salmonella/Cronobacter isolates. I could NOT open the NIH ODS iodine fact sheet (Cloudflare 403), so the adult UL (1,100 mcg) is not cited here; worth adding nih-ods iodine if another agent has it. Did not find a sea moss-specific iodine assay paper. Could arguably join daily-multivitamin overlap ('92 minerals' marketing) but I left overlaps empty since that group's members list doesn't include it. Price is an estimate (gels often $25 to $40 a jar), no pricing page opened. Rewrote fits_instead to avoid a claim I can't source about health benefit. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18552,7 @@
       <c r="Q113" s="3" t="n"/>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>Outside Japan, trials found almost no weight change. High-dose extracts have raised liver enzymes, more so when taken on an empty stomach.</t>
+          <t>Outside Japan, trials found almost no weight change. Extracts have been linked to liver injury, and fasting raises how much gets absorbed.</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr">
@@ -18670,7 +18634,7 @@
       </c>
       <c r="AJ113" s="3" t="inlineStr">
         <is>
-          <t>Tier C on weight: Cochrane 2012 (Jurgens) found -0.04 kg outside Japan (6 RCTs, n=532), Japanese trials -0.2 to -3.5 kg but unpoolable; authors judge it not clinically important. Could be argued D-for-effect but trials exist and disagree by region, so C. Liver: EFSA 2018 says &gt;=800 mg EGCG/day as supplement raised transaminases in trials; USP 2020 review: liver injury case reports at 140 to ~1,000 mg EGCG/day, fasting bolus dosing raises EGCG bioavailability; USP label requires 'take with food, do not use with liver problems'. Brewed tea is generally safe per EFSA (rare idiosyncratic cases). V3 referenced Hu 2018 hepatotoxicity review; I used the USP 2020 review (Oketch-Rabah) instead, which I opened. Price estimate.</t>
+          <t>Tier C on weight: Cochrane 2012 (Jurgens) found -0.04 kg outside Japan (6 RCTs, n=532), Japanese trials -0.2 to -3.5 kg but unpoolable; authors judge it not clinically important. Could be argued D-for-effect but trials exist and disagree by region, so C. Liver: EFSA 2018 says &gt;=800 mg EGCG/day as supplement raised transaminases in trials; USP 2020 review: liver injury case reports at 140 to ~1,000 mg EGCG/day, fasting bolus dosing raises EGCG bioavailability; USP label requires 'take with food, do not use with liver problems'. Brewed tea is generally safe per EFSA (rare idiosyncratic cases). V3 referenced Hu 2018 hepatotoxicity review; I used the USP 2020 review (Oketch-Rabah) instead, which I opened. Price estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18718,7 @@
       <c r="Q114" s="3" t="n"/>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>A 2025 review of 19 trials found small gains in self-rated sleep and next-day feel. Few tested L-theanine alone, and measured sleep was rarely checked.</t>
+          <t>A 2025 review of 19 trials found small gains in self-rated sleep and next-day feel. Few tested L-theanine alone.</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr">
@@ -18832,7 +18796,7 @@
       </c>
       <c r="AJ114" s="3" t="inlineStr">
         <is>
-          <t>Tier C. Bulman/D'Cunha 2025 Sleep Med Rev meta-analysis (abstract via Bond portal): 19 RCTs, n=897, 18 pooled. Significant but small subjective effects: sleep onset latency SMD 0.15 (CI 0.01-0.29), daytime dysfunction 0.33, overall sleep quality 0.43 (CI 0.04-0.83). Authors flag few pure L-theanine studies and unsettled dose. No objective outcomes in abstract. Borderline B for self-rated sleep; kept C because effects are small, subjective, and confounded by blends. Dose 200-400 mg from V3 and Cotter 2025 review (search snippet only, not opened). Moment 'morning' added because many take it with coffee; caffeine-pairing evidence not reviewed here. Price is an estimate (~$12-18/month for 200 mg daily at mainstream brands); no pricing page opened. No safety row: nothing serious found in opened sources.</t>
+          <t>Tier C. Bulman/D'Cunha 2025 Sleep Med Rev meta-analysis (abstract via Bond portal): 19 RCTs, n=897, 18 pooled. Significant but small subjective effects: sleep onset latency SMD 0.15 (CI 0.01-0.29), daytime dysfunction 0.33, overall sleep quality 0.43 (CI 0.04-0.83). Authors flag few pure L-theanine studies and unsettled dose. No objective outcomes in abstract. Borderline B for self-rated sleep; kept C because effects are small, subjective, and confounded by blends. Dose 200-400 mg from V3 and Cotter 2025 review (search snippet only, not opened). Moment 'morning' added because many take it with coffee; caffeine-pairing evidence not reviewed here. Price is an estimate (~$12-18/month for 200 mg daily at mainstream brands); no pricing page opened. No safety row: nothing serious found in opened sources. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19204,7 @@
       <c r="Q117" s="3" t="n"/>
       <c r="R117" s="3" t="inlineStr">
         <is>
-          <t>Sleep trials used 150 to 300 mg, far above most gummies, and still mostly matched placebo. In one test of online products, only 31% matched the label.</t>
+          <t>Sleep trials used high doses, far above most gummies, and still mostly matched placebo. In one test of online products, only 31% matched the label.</t>
         </is>
       </c>
       <c r="S117" s="3" t="inlineStr">
@@ -19326,7 +19290,7 @@
       </c>
       <c r="AJ117" s="3" t="inlineStr">
         <is>
-          <t>Tier C. Suraev 2020 Sleep Med Rev systematic review: insufficient evidence for any sleep disorder, moderate-high risk of bias. Narayan 2024 JCSM RCT (n=30 insomnia, 150 mg nightly x2 weeks): no difference on ISI, self-reported SOL, SE, WASO; objective SE higher at 2 weeks; well-being higher. Wang 2025 JCSM (n=125, 300 mg CBD+terpenes, crossover) found a small rise in % deep+REM on a wrist tracker, no change in total sleep; funding not visible in the record, so not cited. Suraev CANSLEEP (200 mg CBD + 10 mg THC) cut total sleep and REM (conference abstract, not cited). dose_min 150 = lowest pure-CBD dose in an opened sleep RCT, used so DOSE_BELOW_MIN can flag 10-25 mg gummies; it is not a recommendation to take more. Bonn-Miller 2017 JAMA: 84 online products, 31% accurate within 10%, 43% under-labelled, 26% over-labelled, 21% had THC. Safety from NCCIH (interactions, liver injury) and FDA 2019 (avoid in pregnancy/breastfeeding). Price estimate (~$40-60/month for a 25 mg daily gummy).</t>
+          <t>Tier C. Suraev 2020 Sleep Med Rev systematic review: insufficient evidence for any sleep disorder, moderate-high risk of bias. Narayan 2024 JCSM RCT (n=30 insomnia, 150 mg nightly x2 weeks): no difference on ISI, self-reported SOL, SE, WASO; objective SE higher at 2 weeks; well-being higher. Wang 2025 JCSM (n=125, 300 mg CBD+terpenes, crossover) found a small rise in % deep+REM on a wrist tracker, no change in total sleep; funding not visible in the record, so not cited. Suraev CANSLEEP (200 mg CBD + 10 mg THC) cut total sleep and REM (conference abstract, not cited). dose_min 150 = lowest pure-CBD dose in an opened sleep RCT, used so DOSE_BELOW_MIN can flag 10-25 mg gummies; it is not a recommendation to take more. Bonn-Miller 2017 JAMA: 84 online products, 31% accurate within 10%, 43% under-labelled, 26% over-labelled, 21% had THC. Safety from NCCIH (interactions, liver injury) and FDA 2019 (avoid in pregnancy/breastfeeding). Price estimate (~$40-60/month for a 25 mg daily gummy). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -19410,7 +19374,7 @@
       <c r="Q118" s="3" t="n"/>
       <c r="R118" s="3" t="inlineStr">
         <is>
-          <t>Early trials found kava eased anxiety short term, but a 16-week trial of 171 adults found no benefit over placebo. Sleep was rarely studied. Rare liver injury is reported.</t>
+          <t>Early trials in anxious patients found short-term relief, but a 16-week trial of 171 adults with diagnosed anxiety found no benefit over placebo. Rare liver injury is reported.</t>
         </is>
       </c>
       <c r="S118" s="3" t="inlineStr">
@@ -19492,7 +19456,7 @@
       </c>
       <c r="AJ118" s="3" t="inlineStr">
         <is>
-          <t>V3 had B; downgraded to C because studies now disagree. Pittler &amp; Ernst 2003 Cochrane (Europe PMC record; Cochrane site returned 403): 11 RCTs, n=645, HAM-A WMD 5.0 (CI 1.1-8.8) for kava, short-term use relatively safe; the review is old and Cochrane marks its CAM summaries outdated. Sarris 2013 (n=58 analysed, 120-240 mg, d=0.62) was positive, but the larger phase III Sarris 2020 (n=171 GAD, 240 mg/day, 16 weeks) found no benefit (placebo slightly better), with more liver-test abnormalities on kava. NCCIH 2025: may help anxiety, not GAD; rare serious liver injury; avoid with alcohol or sedatives; pregnancy/breastfeeding risks. Teschke 2008: of 26 suspected liver cases, 8 possible/probable, mostly with overdose, long use or co-medication. Sleep: found no solid kava sleep trials. Area set to mind (anxiety is the evidence outcome), also_serves sleep. Cadence 'occasional' and why_loved 'connection' reflect kava-bar culture; capsule users may be daily. Price estimate (~$25-35/month capsules; kava bar shells cost more).</t>
+          <t>V3 had B; downgraded to C because studies now disagree. Pittler &amp; Ernst 2003 Cochrane (Europe PMC record; Cochrane site returned 403): 11 RCTs, n=645, HAM-A WMD 5.0 (CI 1.1-8.8) for kava, short-term use relatively safe; the review is old and Cochrane marks its CAM summaries outdated. Sarris 2013 (n=58 analysed, 120-240 mg, d=0.62) was positive, but the larger phase III Sarris 2020 (n=171 GAD, 240 mg/day, 16 weeks) found no benefit (placebo slightly better), with more liver-test abnormalities on kava. NCCIH 2025: may help anxiety, not GAD; rare serious liver injury; avoid with alcohol or sedatives; pregnancy/breastfeeding risks. Teschke 2008: of 26 suspected liver cases, 8 possible/probable, mostly with overdose, long use or co-medication. Sleep: found no solid kava sleep trials. Area set to mind (anxiety is the evidence outcome), also_serves sleep. Cadence 'occasional' and why_loved 'connection' reflect kava-bar culture; capsule users may be daily. Price estimate (~$25-35/month capsules; kava bar shells cost more). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -19618,7 +19582,7 @@
       </c>
       <c r="AB119" s="3" t="inlineStr">
         <is>
-          <t>Chamomile tea is the food source of apigenin, for a few dollars.</t>
+          <t>Chamomile tea is the everyday source of apigenin.</t>
         </is>
       </c>
       <c r="AC119" s="3" t="n"/>
@@ -19654,7 +19618,7 @@
       </c>
       <c r="AJ119" s="3" t="inlineStr">
         <is>
-          <t>Tier D. Europe PMC search (apigenin + sleep + human) found no RCT of apigenin alone. Viola 1995: apigenin isolated from chamomile binds the benzodiazepine receptor, anxiolytic in mice, sedative only at 10x dose. Mastrofini 2026 JISSN RCT (n=103 active adults): evening blend had 50 mg apigenin plus magnesium L-threonate and L-theanine, so apigenin's own effect can't be separated; funding not visible in the record. Wong 2026 mouse study: apigenin + magnesium synergy (animal). Popularity traces to a podcast sleep protocol (not sourced, from V3). Price estimate (~$15-25/month for 50 mg). No safety row: no specific harm found in opened sources.</t>
+          <t>Tier D. Europe PMC search (apigenin + sleep + human) found no RCT of apigenin alone. Viola 1995: apigenin isolated from chamomile binds the benzodiazepine receptor, anxiolytic in mice, sedative only at 10x dose. Mastrofini 2026 JISSN RCT (n=103 active adults): evening blend had 50 mg apigenin plus magnesium L-threonate and L-theanine, so apigenin's own effect can't be separated; funding not visible in the record. Wong 2026 mouse study: apigenin + magnesium synergy (animal). Popularity traces to a podcast sleep protocol (not sourced, from V3). Price estimate (~$15-25/month for 50 mg). No safety row: no specific harm found in opened sources. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19748,7 @@
       </c>
       <c r="AB120" s="3" t="inlineStr">
         <is>
-          <t>Chamomile tea keeps the bedtime ritual for less.</t>
+          <t>Chamomile tea keeps the bedtime ritual.</t>
         </is>
       </c>
       <c r="AC120" s="3" t="n"/>
@@ -19820,7 +19784,7 @@
       </c>
       <c r="AJ120" s="3" t="inlineStr">
         <is>
-          <t>Tier C (V3 had D): human placebo-controlled trials exist but are small and disagree. Hepsomali 2020 Front Neurosci systematic review: 14 placebo-controlled trials, 'limited' evidence for stress and 'very limited' for sleep (first author's affiliation Unilever, not a GABA seller). Boonstra 2015 Front Psychol: blood-brain barrier crossing long assumed impossible, studies contradictory; much calming evidence from researchers with potential conflicts. FORM_NOT_ABSORBED not used because the barrier question is unresolved, not disproven. Could be argued N if every sleep trial is seller-funded; I did not verify funding trial by trial. Dose range from V3 plus common product labels (not opened). Overlap: gaba-oral is NOT yet in sleep-aids in existing-overlaps.json; needs adding or drop OVERLAP. Price estimate.</t>
+          <t>Tier C (V3 had D): human placebo-controlled trials exist but are small and disagree. Hepsomali 2020 Front Neurosci systematic review: 14 placebo-controlled trials, 'limited' evidence for stress and 'very limited' for sleep (first author's affiliation Unilever, not a GABA seller). Boonstra 2015 Front Psychol: blood-brain barrier crossing long assumed impossible, studies contradictory; much calming evidence from researchers with potential conflicts. FORM_NOT_ABSORBED not used because the barrier question is unresolved, not disproven. Could be argued N if every sleep trial is seller-funded; I did not verify funding trial by trial. Dose range from V3 plus common product labels (not opened). Overlap: gaba-oral is NOT yet in sleep-aids in existing-overlaps.json; needs adding or drop OVERLAP. Price estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -20116,7 +20080,7 @@
       </c>
       <c r="AB122" s="3" t="inlineStr">
         <is>
-          <t>Magnesium glycinate at bedtime, for a fraction of the price.</t>
+          <t>If magnesium is the goal, plain glycinate at bedtime, though its sleep evidence is thin too.</t>
         </is>
       </c>
       <c r="AC122" s="3" t="n"/>
@@ -20152,7 +20116,7 @@
       </c>
       <c r="AJ122" s="3" t="inlineStr">
         <is>
-          <t>Tier N by the brand-funding rule. Hausenblas 2024 Sleep Med X (full text): n=80, 1 g/day Magtein x21 days; funded by AIDP Inc. (3 authors are AIDP; product from Threotech); ISI interaction not significant (p=0.39); Oura deep/REM scores and some self-reports better. Europe PMC lists the grant as 'CNY Arts' - conflicts with the paper's own funding line; the paper says AIDP. There is a 2025 erratum. Lopresti 2025 Front Nutr (full text): n=100, 2 g/day (145 mg elemental) x6 weeks, funded by Threotech, which also co-designed the study; only PROMIS sleep-related impairment improved (p=0.043), Oura sleep unchanged; cognition composite improved. V3's 'Neurocentria' funding claim was not confirmed: funders are AIDP and Threotech. Plain magnesium has its own C-level sleep evidence (existing sources arab-2023, mah-2021, schuster-2025 - not re-opened here). Kidney safety row added from general magnesium knowledge plus MedlinePlus magnesium oxide precaution; NIH ODS page returned 403, so no fact-sheet citation. Price estimate (~$30-45/month for 2 g/day); vendor pages returned 403.</t>
+          <t>Tier N by the brand-funding rule. Hausenblas 2024 Sleep Med X (full text): n=80, 1 g/day Magtein x21 days; funded by AIDP Inc. (3 authors are AIDP; product from Threotech); ISI interaction not significant (p=0.39); Oura deep/REM scores and some self-reports better. Europe PMC lists the grant as 'CNY Arts' - conflicts with the paper's own funding line; the paper says AIDP. There is a 2025 erratum. Lopresti 2025 Front Nutr (full text): n=100, 2 g/day (145 mg elemental) x6 weeks, funded by Threotech, which also co-designed the study; only PROMIS sleep-related impairment improved (p=0.043), Oura sleep unchanged; cognition composite improved. V3's 'Neurocentria' funding claim was not confirmed: funders are AIDP and Threotech. Plain magnesium has its own C-level sleep evidence (existing sources arab-2023, mah-2021, schuster-2025 - not re-opened here). Kidney safety row added from general magnesium knowledge plus MedlinePlus magnesium oxide precaution; NIH ODS page returned 403, so no fact-sheet citation. Price estimate (~$30-45/month for 2 g/day); vendor pages returned 403. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20550,7 @@
       </c>
       <c r="AB125" s="3" t="inlineStr">
         <is>
-          <t>Sparkling water with a splash of juice keeps the fizz for less.</t>
+          <t>Sparkling water with a splash of juice keeps the fizz.</t>
         </is>
       </c>
       <c r="AC125" s="3" t="n"/>
@@ -20618,7 +20582,7 @@
       </c>
       <c r="AJ125" s="3" t="inlineStr">
         <is>
-          <t>Tier C, up from V3's D: Kapp &amp; Sumner 2019 systematic review (Ann Epidemiol) found only one human study as of 2018, but small RCTs have appeared since: Arce-Lopez 2025 (n=58 healthy, 6 wk, fiber-enriched kombucha; triglycerides and Bifidobacterium shifted vs unfermented tea), Bonifacio 2026 (n=90 healthy beginner runners, 12 wk; primary outcome FRAP unchanged, other changes exploratory after FDR), Bonifacio 2026 second trial (n=59 overweight on calorie restriction; no between-group differences overall). Small, short, mixed = C. No kombucha-company funding disclosed in these records (public Brazilian/Spanish funders). 'Probiotic drinks' with named strains (e.g. Yakult-type for antibiotic diarrhoea) were not assessed here; if Veer wants them separate, they need their own row. Price: estimate. Search-result listings (ShopRite) showed GT's Synergy 16 oz at $3.99 to $4.49 regular; about 3 bottles a week is roughly $50/month. Safety row from TTB page: kombucha can ferment in the bottle to 0.5% ABV or more.</t>
+          <t>Tier C, up from V3's D: Kapp &amp; Sumner 2019 systematic review (Ann Epidemiol) found only one human study as of 2018, but small RCTs have appeared since: Arce-Lopez 2025 (n=58 healthy, 6 wk, fiber-enriched kombucha; triglycerides and Bifidobacterium shifted vs unfermented tea), Bonifacio 2026 (n=90 healthy beginner runners, 12 wk; primary outcome FRAP unchanged, other changes exploratory after FDR), Bonifacio 2026 second trial (n=59 overweight on calorie restriction; no between-group differences overall). Small, short, mixed = C. No kombucha-company funding disclosed in these records (public Brazilian/Spanish funders). 'Probiotic drinks' with named strains (e.g. Yakult-type for antibiotic diarrhoea) were not assessed here; if Veer wants them separate, they need their own row. Price: estimate. Search-result listings (ShopRite) showed GT's Synergy 16 oz at $3.99 to $4.49 regular; about 3 bottles a week is roughly $50/month. Safety row from TTB page: kombucha can ferment in the bottle to 0.5% ABV or more. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20874,7 @@
       </c>
       <c r="AB127" s="3" t="inlineStr">
         <is>
-          <t>A mug of miso or homemade stock keeps the warmth for less.</t>
+          <t>A mug of miso or homemade stock keeps the warmth.</t>
         </is>
       </c>
       <c r="AC127" s="3" t="n"/>
@@ -20946,7 +20910,7 @@
       </c>
       <c r="AJ127" s="3" t="inlineStr">
         <is>
-          <t>Tier D: no human trials of bone broth for skin, joints or gut turned up in Europe PMC searches (bone broth + randomized/clinical trial/crossover). Alcock 2019 (IJSNEM, lab analysis): standardized-recipe broths had significantly lower glycine, proline, hydroxyproline etc. than a 20 g collagen supplement dose, with large variation across recipes; cafe broths highest. Alcock 2019 Front Nutr (300 mL broth in a plasma amino acid study) exists but I did not open it fully. Matar 2025 (Dig Dis Sci) is a narrative review arguing gut-barrier benefits from broth's components (glutamine, glycine), i.e. mechanism, not broth trials. Myung 2025 (existing source): collagen effects on skin vanish in non-industry-funded and high-quality RCTs, which undercuts the collagen rationale. It is a real food with some protein, so it is not harmful; D is about the borrowed claims. Price: estimate from search-result listings (Walmart $6.58, Thrive $7.99 for a 16.9 oz carton, about 2 mugs); a few mugs a week is about $50/month.</t>
+          <t>Tier D: no human trials of bone broth for skin, joints or gut turned up in Europe PMC searches (bone broth + randomized/clinical trial/crossover). Alcock 2019 (IJSNEM, lab analysis): standardized-recipe broths had significantly lower glycine, proline, hydroxyproline etc. than a 20 g collagen supplement dose, with large variation across recipes; cafe broths highest. Alcock 2019 Front Nutr (300 mL broth in a plasma amino acid study) exists but I did not open it fully. Matar 2025 (Dig Dis Sci) is a narrative review arguing gut-barrier benefits from broth's components (glutamine, glycine), i.e. mechanism, not broth trials. Myung 2025 (existing source): collagen effects on skin vanish in non-industry-funded and high-quality RCTs, which undercuts the collagen rationale. It is a real food with some protein, so it is not harmful; D is about the borrowed claims. Price: estimate from search-result listings (Walmart $6.58, Thrive $7.99 for a 16.9 oz carton, about 2 mugs); a few mugs a week is about $50/month. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -21334,7 +21298,7 @@
       <c r="Q130" s="3" t="n"/>
       <c r="R130" s="3" t="inlineStr">
         <is>
-          <t>Across 24 studies, caffeine cut about 45 minutes of sleep, and a 107 mg coffee needed about nine hours before bed. FDA calls 400 mg a day generally fine.</t>
+          <t>Across 24 studies, caffeine cut about 45 minutes of sleep, and a 107 mg coffee needed about nine hours before bed. FDA calls up to 400 mg a day generally fine for healthy adults.</t>
         </is>
       </c>
       <c r="S130" s="3" t="inlineStr">
@@ -21416,7 +21380,7 @@
       </c>
       <c r="AJ130" s="3" t="inlineStr">
         <is>
-          <t>Cost habit, so UNLOVED_HABIT and no EVIDENCE_REGULAR. Tier A describes the cost of late caffeine: Gardiner 2023 meta-analysis (24 studies): TST -45 min, sleep efficiency -7%, SOL +9 min, WASO +12 min, less deep sleep; coffee (107 mg/250 mL) &gt;=8.8 h before bed to avoid TST loss. Drake 2013 RCT: 400 mg at 0, 3 or 6 h before bed all disrupted sleep. FDA consumer page: 400 mg/day (about two to three 12 oz cups) generally not linked to negative effects in most adults; 12 oz brewed coffee is 113 to 247 mg. So a second cup at 10am is usually fine; the cost is timing or a total well past 400 mg. V3's HRV claim was not checked here and is left out. Cost $40 is an estimate (mix of home brew and some cafe cups); timing rows otherwise have no product cost.</t>
+          <t>Cost habit, so UNLOVED_HABIT and no EVIDENCE_REGULAR. Tier A describes the cost of late caffeine: Gardiner 2023 meta-analysis (24 studies): TST -45 min, sleep efficiency -7%, SOL +9 min, WASO +12 min, less deep sleep; coffee (107 mg/250 mL) &gt;=8.8 h before bed to avoid TST loss. Drake 2013 RCT: 400 mg at 0, 3 or 6 h before bed all disrupted sleep. FDA consumer page: 400 mg/day (about two to three 12 oz cups) generally not linked to negative effects in most adults; 12 oz brewed coffee is 113 to 247 mg. So a second cup at 10am is usually fine; the cost is timing or a total well past 400 mg. V3's HRV claim was not checked here and is left out. Cost $40 is an estimate (mix of home brew and some cafe cups); timing rows otherwise have no product cost. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21644,7 @@
       </c>
       <c r="AB132" s="3" t="inlineStr">
         <is>
-          <t>Your utility's yearly water report shows whether a filter earns its place.</t>
+          <t>Testing your own tap first, since lead often comes from home pipes.</t>
         </is>
       </c>
       <c r="AC132" s="3" t="n"/>
@@ -21712,7 +21676,7 @@
       </c>
       <c r="AJ132" s="3" t="inlineStr">
         <is>
-          <t>Tier C, and deliberately no BORROWED_WEAK even though C allows it: whether a filter matters depends on the home's water (lead service lines, old buildings, private wells, PFAS), which Distill can't see, so a 'let it go' could be wrong in exactly the homes where it matters. Only UNUSED (a filter that isn't changed or used). Evidence: CDC 2024 page: test first; if water has no harmful germs/chemicals a filter may not be needed; pitcher filters are mainly for taste and smell, may remove lead; check NSF standard on label. Purchase 2025 field test: lead-certified faucet filters brought occupied-home lead below 1 ug/L; a disturbed lead line overwhelmed them; iron clogged them. Hazzazi 2025: nine popular pitchers varied widely in mineral changes; none fully removed fluoride despite three makers' claims. No health-outcome trials of filtering already-compliant water exist that I found. Price: brita.com lists Elite replacement $19.99 and Original 1-pack $7.99; filter life not shown on the page I opened, so $5/month is an estimate.</t>
+          <t>Tier C, and deliberately no BORROWED_WEAK even though C allows it: whether a filter matters depends on the home's water (lead service lines, old buildings, private wells, PFAS), which Distill can't see, so a 'let it go' could be wrong in exactly the homes where it matters. Only UNUSED (a filter that isn't changed or used). Evidence: CDC 2024 page: test first; if water has no harmful germs/chemicals a filter may not be needed; pitcher filters are mainly for taste and smell, may remove lead; check NSF standard on label. Purchase 2025 field test: lead-certified faucet filters brought occupied-home lead below 1 ug/L; a disturbed lead line overwhelmed them; iron clogged them. Hazzazi 2025: nine popular pitchers varied widely in mineral changes; none fully removed fluoride despite three makers' claims. No health-outcome trials of filtering already-compliant water exist that I found. Price: brita.com lists Elite replacement $19.99 and Original 1-pack $7.99; filter life not shown on the page I opened, so $5/month is an estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -23400,11 +23364,7 @@
           <t>Is it mostly for skin, or for recovery?</t>
         </is>
       </c>
-      <c r="AB143" s="3" t="inlineStr">
-        <is>
-          <t>Ten minutes of morning daylight outdoors keeps a light ritual for free.</t>
-        </is>
-      </c>
+      <c r="AB143" s="3" t="n"/>
       <c r="AC143" s="3" t="n"/>
       <c r="AD143" s="3" t="inlineStr">
         <is>
@@ -23438,7 +23398,7 @@
       </c>
       <c r="AJ143" s="3" t="inlineStr">
         <is>
-          <t>Tier C for skin (V3 C). Wunsch 2014 (full text) is the closest match to a panel (full-body units) and found gains vs untreated controls, but was fully sponsor-funded with non-randomized, sponsor-employee controls and no sham. AAD 2024 (full text) supports subtle-to-noticeable results for aging skin but says home devices are hard to judge. Recovery: Dutra 2022 meta-analysis (abstract) found small gains in single-joint endurance and cycling time to exhaustion, none in strength or running; trials used lasers/LED clusters on muscles pre-exercise, not panels, so the move claim is C at best. Sleep: Zhao 2012 (abstract) is 20 athletes, not blinded; D for sleep. V3 testosterone claim rests on rat data; not searched further and left out. Price: Mito panels $249 to $749 for most home sizes (brand page, opened), over 24 months about $10 to $31; used $20. fits_instead points to morning-sunlight-10-min-outdoors (a different benefit, circadian, not skin); Veer may prefer "".</t>
+          <t>Tier C for skin (V3 C). Wunsch 2014 (full text) is the closest match to a panel (full-body units) and found gains vs untreated controls, but was fully sponsor-funded with non-randomized, sponsor-employee controls and no sham. AAD 2024 (full text) supports subtle-to-noticeable results for aging skin but says home devices are hard to judge. Recovery: Dutra 2022 meta-analysis (abstract) found small gains in single-joint endurance and cycling time to exhaustion, none in strength or running; trials used lasers/LED clusters on muscles pre-exercise, not panels, so the move claim is C at best. Sleep: Zhao 2012 (abstract) is 20 athletes, not blinded; D for sleep. V3 testosterone claim rests on rat data; not searched further and left out. Price: Mito panels $249 to $749 for most home sizes (brand page, opened), over 24 months about $10 to $31; used $20. fits_instead points to morning-sunlight-10-min-outdoors (a different benefit, circadian, not skin); Veer may prefer "". Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -24014,7 +23974,7 @@
       </c>
       <c r="R147" s="3" t="inlineStr">
         <is>
-          <t>Regular classes build fitness like any training. The benefit lives in the classes taken: in one large gym study, members paid more per visit than a pass.</t>
+          <t>Regular classes build fitness like any training. The benefit lives in the classes taken.</t>
         </is>
       </c>
       <c r="S147" s="3" t="inlineStr">
@@ -24058,11 +24018,7 @@
           <t>How many credits are left before the pack expires?</t>
         </is>
       </c>
-      <c r="AB147" s="3" t="inlineStr">
-        <is>
-          <t>A smaller pack sized to the classes you actually book.</t>
-        </is>
-      </c>
+      <c r="AB147" s="3" t="n"/>
       <c r="AC147" s="3" t="inlineStr">
         <is>
           <t>collective</t>
@@ -24100,7 +24056,7 @@
       </c>
       <c r="AJ147" s="3" t="inlineStr">
         <is>
-          <t>V3 graded A off an unsourced claim that unused credits are the most common wellness purchase that does nothing; I found no study of class-pack or ClassPass breakage, so that claim is dropped. The A now belongs to the training (HIIT trials, WHO activity guidance), held only for people who use it (trains, otherwise N), matching gym-membership and boutique rows. Usage evidence is DellaVigna and Malmendier 2006 (gym memberships, not packs). Expiry matters: SoulCycle's opened series page (San Francisco) lists 5 classes $185 (45-day expiry), 10 for $365 (3 months), 20 for $710 (9 months). cost_month_usd 120 = a 10-pack spread over its 3-month expiry. ClassPass official pricing page returned 403; third-party summaries show $19 for 8 credits up to about $139 to $159, with rollover capped, so not used for the price. Clear codes follow the gym rows (UNUSED, OVERLAP), not BORROWED_WEAK.</t>
+          <t>V3 graded A off an unsourced claim that unused credits are the most common wellness purchase that does nothing; I found no study of class-pack or ClassPass breakage, so that claim is dropped. The A now belongs to the training (HIIT trials, WHO activity guidance), held only for people who use it (trains, otherwise N), matching gym-membership and boutique rows. Usage evidence is DellaVigna and Malmendier 2006 (gym memberships, not packs). Expiry matters: SoulCycle's opened series page (San Francisco) lists 5 classes $185 (45-day expiry), 10 for $365 (3 months), 20 for $710 (9 months). cost_month_usd 120 = a 10-pack spread over its 3-month expiry. ClassPass official pricing page returned 403; third-party summaries show $19 for 8 credits up to about $139 to $159, with rollover capped, so not used for the price. Clear codes follow the gym rows (UNUSED, OVERLAP), not BORROWED_WEAK. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24646,7 @@
       </c>
       <c r="R151" s="3" t="inlineStr">
         <is>
-          <t>Training builds strength and fitness wherever it happens. Two memberships help only if both get used: in one large gym study, members paid more per visit than a pass.</t>
+          <t>Training builds strength and fitness wherever it happens. A second membership adds something only when both get used.</t>
         </is>
       </c>
       <c r="S151" s="3" t="inlineStr">
@@ -24772,7 +24728,7 @@
       </c>
       <c r="AJ151" s="3" t="inlineStr">
         <is>
-          <t>V3 graded A off 'nobody needs two', which is not a research finding. As with gym-membership, the A belongs to the training and holds only with use (trains, otherwise N); OVERLAP via gym-floor-access (keep-most-used) is the real lever. DellaVigna and Malmendier 2006 is the usage evidence. Price is an estimate: a second membership is often a studio or climbing gym. Opened data points: Time Out (2025) VITAL Climbing Harlem $155 a month; SoulCycle 10-pack $365 over 3 months (about $120 a month). Budget gyms run far less (Planet Fitness page returned 403, not used). cost 120 sits between.</t>
+          <t>V3 graded A off 'nobody needs two', which is not a research finding. As with gym-membership, the A belongs to the training and holds only with use (trains, otherwise N); OVERLAP via gym-floor-access (keep-most-used) is the real lever. DellaVigna and Malmendier 2006 is the usage evidence. Price is an estimate: a second membership is often a studio or climbing gym. Opened data points: Time Out (2025) VITAL Climbing Harlem $155 a month; SoulCycle 10-pack $365 over 3 months (about $120 a month). Budget gyms run far less (Planet Fitness page returned 403, not used). cost 120 sits between. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -24856,7 +24812,7 @@
       <c r="Q152" s="3" t="n"/>
       <c r="R152" s="3" t="inlineStr">
         <is>
-          <t>Trials pooled in a 2004 review show one massage eases anxiety, heart rate and blood pressure, and a course eases lasting anxiety. A 2018 review ranked massage top for soreness.</t>
+          <t>Trials pooled in a 2004 review show one massage eases anxiety, heart rate and blood pressure, and a 2018 review ranked massage top for soreness after exercise.</t>
         </is>
       </c>
       <c r="S152" s="3" t="inlineStr">
@@ -24938,7 +24894,7 @@
       </c>
       <c r="AJ152" s="3" t="inlineStr">
         <is>
-          <t>V3 B kept; same evidence as the massage membership row (Moyer 2004, Dupuy 2018). V3's 'HRV goes up for a while' and 'no lasting physical effect' not verified; Moyer found course effects on trait anxiety and depression, so 'no lasting effect' was dropped. NCCIH (2019) notes rare serious harms (blood clot, nerve injury, fracture), mostly with vigorous deep tissue work. Price opened: ThePricer (Aug 2026) non-member 60-min Massage Envy prices $125 (Mount Dora), $145 (Freehold), $155 (Concord), $160 (Gramercy NYC); Squeeze $129 for 50 min. cost 130 excludes tip. UNUSED included per the rule for paid items (a prepaid package or gift card).</t>
+          <t>V3 B kept; same evidence as the massage membership row (Moyer 2004, Dupuy 2018). V3's 'HRV goes up for a while' and 'no lasting physical effect' not verified; Moyer found course effects on trait anxiety and depression, so 'no lasting effect' was dropped. NCCIH (2019) notes rare serious harms (blood clot, nerve injury, fracture), mostly with vigorous deep tissue work. Price opened: ThePricer (Aug 2026) non-member 60-min Massage Envy prices $125 (Mount Dora), $145 (Freehold), $155 (Concord), $160 (Gramercy NYC); Squeeze $129 for 50 min. cost 130 excludes tip. UNUSED included per the rule for paid items (a prepaid package or gift card). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>
@@ -25392,7 +25348,7 @@
       </c>
       <c r="AB155" s="3" t="inlineStr">
         <is>
-          <t>A cold plunge or cold shower, cheaper and better studied.</t>
+          <t>A cold-water plunge, which has more evidence behind it.</t>
         </is>
       </c>
       <c r="AC155" s="3" t="n"/>
@@ -25428,7 +25384,7 @@
       </c>
       <c r="AJ155" s="3" t="inlineStr">
         <is>
-          <t>V3 C kept. Costello 2015 Cochrane (CD010789): 4 lab RCTs, 64 active, mostly young men; very low-quality evidence, insufficient to say whether WBC reduces soreness or improves recovery vs rest; no adverse events reported. Dupuy 2018 pooled 'cryotherapy' broadly (not WBC alone) and found smaller DOMS drops than massage. Legrand 2023 consortium scoping review: 16 adverse events in 7 reports (4 serious: amnesia, brain bleed, moyamoya, aortic dissection); hypertension is an absolute contraindication in the Bad Voslau consensus. An FDA MAUDE report I opened states FDA has not cleared or approved any WBC device and describes a worker found dead in a chamber; the 2016 FDA consumer update URL now 404s, so not cited. Could argue D; kept C because RCTs exist, just tiny. Price opened: Cryo Lab (El Dorado Hills, CA) $45 a session, 2 to 3.5 minutes. cost 180 = 4 sessions a month; unlimited plans run about $59 to $249 elsewhere (search snippets, not opened).</t>
+          <t>V3 C kept. Costello 2015 Cochrane (CD010789): 4 lab RCTs, 64 active, mostly young men; very low-quality evidence, insufficient to say whether WBC reduces soreness or improves recovery vs rest; no adverse events reported. Dupuy 2018 pooled 'cryotherapy' broadly (not WBC alone) and found smaller DOMS drops than massage. Legrand 2023 consortium scoping review: 16 adverse events in 7 reports (4 serious: amnesia, brain bleed, moyamoya, aortic dissection); hypertension is an absolute contraindication in the Bad Voslau consensus. An FDA MAUDE report I opened states FDA has not cleared or approved any WBC device and describes a worker found dead in a chamber; the 2016 FDA consumer update URL now 404s, so not cited. Could argue D; kept C because RCTs exist, just tiny. Price opened: Cryo Lab (El Dorado Hills, CA) $45 a session, 2 to 3.5 minutes. cost 180 = 4 sessions a month; unlimited plans run about $59 to $249 elsewhere (search snippets, not opened). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
     </row>

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ157"/>
+  <dimension ref="A1:AK157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -845,6 +845,11 @@
           <t>notes_internal</t>
         </is>
       </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>origin_question</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1843,6 +1848,11 @@
       <c r="AJ7" s="3" t="inlineStr">
         <is>
           <t>Tier N per the brief's rule (brand-funded only counts as none). V3 said D. Every human study found was funded by the brand and/or written by its employees: AG1 (La Monica 2024: funded in part by AG1, two AG1 employees; Gonzalez 2026: AG1-funded, AG1 employees; Sapp 2026: five AG1-affiliated authors, no funding statement in the record) and Field of Greens (Robinson 2026: BrickHouse Nutrition paid for the trial and supplied the product). Kirby 2024 is a lab gut-simulator study by AG1 employees. Outcomes were surrogates (bacterial taxa, intake on paper, blood levels after one dose); none showed changes in health, energy or digestion, and microbiome diversity did not change. AG1 conference abstracts in JISSN 2025 supplements are also AG1-authored and were not opened. Price: AG1 is $79/month on subscription or $99 one-time per a Fortune review (Jan 2026, updated Jul 2026, affiliate-linked; https://www.fortune.com/article/ag1-review), so V3's $90 is updated to 79. The same review says AG1 Next Gen has no vitamin D or K (sold separately); the label could not be checked (drinkag1.com rate-limited). ritual_role is anchor because the morning glass often carries the habit, so fits_instead keeps the glass. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>How did greens powder find its way into your mornings?</t>
         </is>
       </c>
     </row>
@@ -4595,6 +4605,11 @@
       <c r="AJ24" s="3" t="inlineStr">
         <is>
           <t>V3 tier N kept and now sourced: no study tests the added value of a second device. Miller 2022 (n = 53, one lab night, six devices worn at once; the lab receives WHOOP support, though WHOOP had no role in the study) found all valid for total sleep and weaker on stages, each with its own HRV bias, so two devices can disagree with no way to tell which is right; that can feed score worry (see the sleep-score row). V3's 'they measure the same things' is right for sleep timing and heart rate, less so for stages and HRV. Ryan 2019: wearables mostly feel positive; anxiety shows up when unable to wear one. Rosman 2024 (atrial fibrillation patients) supports the heart-condition safety row. Cost: WHOOP about $199 to $359 a year, or Oura $5.99 a month plus the ring (third-party pricing, not sourced); 20 a month set as the typical extra cost (V3 said 30).</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>What got you wearing a second tracker?</t>
         </is>
       </c>
     </row>
@@ -7017,6 +7032,11 @@
           <t>Tier D for the practice. V3's B graded the warning, not the practice. No trial compares same-night layering with alternate nights, so the founder's 'adds irritation, not results' is reasonable guidance but not proven. Support: AAD says exfoliating alongside retinoids may worsen dryness and that starting several anti-aging products close together irritates; Lin 2025 links glycolic acid to more adverse events and finds it not significant for fine wrinkles (only for roughness); Griffiths 1995 shows a stronger tretinoin adds irritation without adding benefit. Counterpoint, brand data only: a J&amp;J patent (US5646186, opened this session) claims 5 to 10% glycolic acid in the same formula cut irritation from low-dose retinol in 14-day patch tests, with no effect at 0.3% retinol. V3's 'alternating nights gives the same benefit' is also untested, so the summary avoids it. Cost $15 covers the extra acid only; the retinoid's cost sits in its own row. Cadence 'weekly' means several nights a week; the cadence list has no such option. how_common is an estimate.</t>
         </is>
       </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Who suggested a retinoid and an acid on the same nights?</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -7167,6 +7187,11 @@
           <t>Tier D (V3 had B with no source). No study compares one exfoliant with two; the evidence that one acid works comes from Lin 2025 (glycolic acid eased roughness in RCTs). The harms are guidance-backed: AAD on over-exfoliating, scrubbing flaring acne and darker skin; FDA on AHA sun sensitivity (fades within a week of stopping). V3 overstated with 'one of these is doing the job and the other is doing damage', and its blanket 'keep the acid, drop the scrub' goes too far: the AAD suggests a mild chemical exfoliant for dry, sensitive or acne-prone skin, but says oily, thicker skin can take stronger methods. The darker-skin pigmentation risk has no condition code; consider adding 'darker skin tone' as a note condition. The FDA page reports the industry panel's view that AHA products are safe at 10% or less and pH 3.5 or higher. Cost $15 (V3 had $25) is an estimate for the second product. Cadence 'weekly' means a few times a week.</t>
         </is>
       </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Where did the idea of two exfoliants come from?</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -7317,6 +7342,11 @@
           <t>Tier N for the doubled practice: no study tests a second hyaluronic acid product, and there is no mechanism by which a second dose of the same humectant would add much. The evidence for a single HA product is itself thin and industry-linked. Pavicic 2011 had co-authors from Evonik and Novozymes (both ingredient makers). The Bravo 2022 review was L'Oreal-funded, so it is not cited. A single HA serum would sit around tier C. V3 graded this B with no source. Cost $20 (V3 had $50) is an estimate: budget HA serums cost $10 to 20 a month. The proposed keep-most-used rule gives the existing 'hydrating layers' group a tiebreak.</t>
         </is>
       </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>How did a second hyaluronic serum end up on your shelf?</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -8119,6 +8149,11 @@
       <c r="AJ46" s="3" t="inlineStr">
         <is>
           <t>V3 graded C off one small uncontrolled study in mild apnea (Lee 2022: 20 people, no control group). Rhee 2025 (systematic review) found ten poor-quality studies, none testing normal sleepers, and concluded the data do not support taping. Graded D for better sleep in people without sleep apnea (mechanism and anecdote only); the snoring signal in mild apnea is C at best. The main risks (blocked nose, moderate or severe apnea, regurgitation while taped) have no matching condition in the brief's safety list. Suggest adding a 'sleep-apnea-or-blocked-nose' condition with never-suggest, and a gate that routes loud snoring, gasping or witnessed breathing pauses to a clinician. Cost is an estimate (branded strips cost more, plain surgical tape far less).</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Where did you first hear about mouth tape?</t>
         </is>
       </c>
     </row>
@@ -8579,6 +8614,11 @@
           <t>The tier grades the benefit people use it for (winding down), which only anecdote supports, so D; the harm evidence lives in the summary. V3 graded the harm as B, which under V4 would add EVIDENCE_REGULAR and protect the habit. Harm evidence is mostly observational (Brautsch 2023: 42 studies, causal direction unclear; Hjetland 2025: cross-sectional, 35% response rate) plus one small pilot RCT with diary-only outcomes (He 2020: 38 students, latency 31 to 18 min vs 29 to 27 min). V3's '20 to 30 minutes later for social media in bed' figure was not confirmed (Levenson 2017 and Exelmans 2016 not opened). Hjetland found no difference between social media and other screen activities, which cuts against V3's 'what you look at matters more than blue light' line; time in bed on the screen seems to matter most.</t>
         </is>
       </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>How did the phone become part of bedtime?</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -9677,6 +9717,11 @@
           <t>Tier N for the second app's added value, not for meditation apps generally. Linardon 2024 (45 RCTs) found small effects of one mindfulness app on depression (g=0.24) and anxiety (g=0.28); that protects the first app (separate row). Nothing tests a second app on top. Baumel 2019 (93 Android mental-health apps, independent panel data): median 30-day retention 3.3% overall, 4.7% for mindfulness apps, with morning and night peaks for meditation use (used for moments). Overlap rule keep-most-used handles which one stays. Price is an estimate (Headspace and Calm list roughly $13 to $17/month from my knowledge; their pricing pages failed to load).</t>
         </is>
       </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>What got you a second meditation or sleep app?</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -10301,6 +10346,11 @@
           <t>Tier N: no controlled studies. Verma 2024 Cureus (opened full text, no funding) is a two-case report where the subjects were also authors: about 3 months, 10-min sessions 1-3x/week, no change in jawline or double chin; complaints were gagging and suction, no TMJ pain reported. Its literature section says masticatory muscles don't act on submental fat. For TMJ risk I found no dental-association statement on jaw exercisers; nearest is Alam 2025 systematic review on gum chewing (8 studies, mixed: some show dose-related muscle discomfort, others no link). So the safety row is a gentle note, not never-suggest. Area set to skin since it is bought for looks. Price: about $10 per Verma; spread to $3/month as an estimate (cheap, often replaced).</t>
         </is>
       </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Where did you first see the jaw exerciser?</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10453,6 +10503,11 @@
       <c r="AJ61" s="3" t="inlineStr">
         <is>
           <t>Tier N. FTC press release 20 Feb 2002 (opened): charged SV1 and Comstar (WaveShield) over claims of blocking 97-99% of radiation; quotes Good Housekeeping Institute tests showing no reduction and an FTC consumer alert saying no proof shields reduce exposure; also notes most emission comes from the antenna, not the earpiece. FDA page (current as of 13 May 2021, opened): weight of evidence has not linked phone RF with health problems; page says nothing about shields. Newer wearable 'EMF' pendants weren't checked separately. Price: one-off purchase, roughly $20 to $40 (estimate), spread to about $2/month. Phone-across-the-room swap is my own suggestion.</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Where did you hear about EMF stickers?</t>
         </is>
       </c>
     </row>
@@ -10597,6 +10652,11 @@
           <t>Catch-all row for any subscription a person forgot about; kept general as asked: tier N, clear_when UNUSED only (no BORROWED_WEAK, since the engine shouldn't judge an unknown product's evidence). Area 'mind' is a placeholder; the schema needs one, and Veer may want a neutral option. Cost 0 because the real amount comes from the person's own statement. DellaVigna 2006 AER (opened abstract): monthly gym members paid over $70 for 4.3 visits a month, over $17 a visit vs $10 on a pass, overestimated future attendance and delayed cancelling. It's gyms only, so I used it for the general pattern, not a tier. V3's '30 days unused' threshold has no source I found; it's a product rule. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Do you remember how this subscription started?</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -11667,6 +11727,11 @@
           <t>D: for hair the only support is friction reasoning and a seller's own lab test (Mulberry Park Silks, not opened, brand). The one registered trial (NCT00767104, Wake Forest, collaborator Precision Fabrics Group, n=40, 12 weeks, results posted 2017) used a silk-like synthetic, not silk, and found 13% vs 22% lesion reduction for silk-like vs cotton with overlapping CIs - no benefit. Healthline's claim that this trial showed fewer pimples contradicts the posted results. Marked brand_funded yes because a fabric maker collaborated (funding split not stated). Price: estimate, $25-90 pillowcase over 24 months. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>What first sold you on a silk pillowcase?</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -12141,6 +12206,11 @@
           <t>Chevalier 2012 review: three of five authors are contractors for and shareholders in the earthing company; the sleep study (Ghaly and Teplitz 2004, n=12) had no control group. That evidence counts as brand. Lin 2022 (Healthcare, n=22 randomised, 15 completed, mild Alzheimer's, age about 78, no funding, no COI declared, used an Earthing-brand mat): PSQI better vs sham at week 12 (p=0.006) but GEE model p=0.053; later corrected. A Korean pilot (n=60) surfaced in search but I did not open it. Grade D not N because one independent pilot exists, but it is tiny and in a very different population; no plausible mechanism shown. Price: estimate, $50-150 over 24 months; V3 had 30, which looks high. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Where did you come across grounding?</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -12295,6 +12365,11 @@
           <t>N: no peer-reviewed study of salt lamps on air, mood or sleep found. Cleveland Clinic (2021, Neha Vyas MD) says output is too low to matter and benefits are anecdotal. Healthline cites a Negative Ion Information Center test showing barely measurable ions; not opened or verified. Note: 'treat' in why_loved is the allowed code, not person-facing text. Price: estimate, $15-30 lamp over 24 months; V3 had 0. Kind set to environment since it is room decor.</t>
         </is>
       </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>How did the salt lamp end up in your room?</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -13907,6 +13982,11 @@
       <c r="AJ83" s="3" t="inlineStr">
         <is>
           <t>V3 graded N, but independent trials exist and found no benefit, so D fits the table's practice for tested-and-null items (as with phone-in-bed). Bamford 2013 Cochrane (19 EPO trials) found no improvement in eczema and called further trials hard to justify; the lead author had past Efamol trial support, but the review was independent. PMS: Budeiri 1996 (7 trials) found the two best-controlled showed no benefit; NCCIH 2024 calls PMS and menopause evidence insufficient and breast pain probably no better than placebo. V3's 'Whelan 2009' was not found; not cited. Area set to skin because eczema is the main claim. dose_typical 1 to 3 g is a common label range, not checked against trials. Bamford notes a possible bleeding interaction with warfarin. Price is the V3 estimate.</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Who first suggested evening primrose oil?</t>
         </is>
       </c>
     </row>
@@ -15113,6 +15193,11 @@
           <t>Tier D chosen because the benefit claim rests on mechanism only, while well-run independent RCTs tested it and found no added benefit: Food4Me 2017 (n=1,269 completers, 7 countries) personalised advice beat generic advice, but adding genotype (5 variants) did not improve it further; DIETFITS 2018 JAMA (n=609) no diet x genotype interaction for 12-month weight loss. The tier scale has no 'tested and null' grade; flag for Veer whether this should read N or D. One-off purchase so UNUSED left out. Cost: estimate, ~$100-200 one-off spread over 24 months (V3 typical) ≈ $5; no pricing page opened. Ancestry and raw data are a fair reason to keep; the question focuses on the wellness reports. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>What got you to order the DNA test?</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -15263,6 +15348,11 @@
           <t>Tier N: the only healthy-adult studies I found (Hadanny 2020 RCT n=63 cognition; Hachmo 2020 single-arm n=35 telomeres) are by Efrati's group, authors employed by or shareholders in Aviv Scientific, which sells HBOT longevity programmes, so brand-funded counts as none. Both in adults over 64, not 22-35. Harvard Health 2024 (Catanese, reviewed by Shmerling) lists FDA-cleared uses (decompression sickness, CO poisoning, gas embolism, hard-to-heal wounds, burns, sudden hearing loss etc.), says claims for Alzheimer's, autism, cancer, Lyme are not FDA-approved; risks ear/sinus pain, eardrum rupture, vision change, rarely lung collapse, fire risk; FDA advises accredited facility. FDA's own consumer page returned 404 (moved), so I cite Harvard's summary. Wellness 'mild' soft chambers (~1.3 ATA) were not studied in anything I opened. Cost: estimate, sessions ~$100-250, a few a month; no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>How did you first hear about hyperbaric sessions?</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -15421,6 +15511,11 @@
           <t>Tier D: Ezzo 2015 Cochrane (6 RCTs, breast-cancer lymphedema) MLD added ~7% volume reduction to compression bandaging in 2 small trials; other comparisons not significant or too varied. PubMed search for healthy-subject trials found only small physiology studies (e.g. autonomic/H-reflex changes in J Bodyw Mov Ther 2021, neck MLD in students J Clin Med 2020) with no outcome on puffiness, skin or wellbeing; I read titles/results snippets only, not cited. 'Draining toxins' framing has no support. Area skin because the TikTok draw is de-puffing/face; also mind for the calm. Put in existing massage group (show-together) via overlaps; the group's member list in existing-overlaps.json does not yet include this key, so Veer/Ishan add it there. No safety row: heart failure and active clot are standard contraindications in MLD practice but I did not open a source. Cost: estimate ~$120 a session, about monthly (V3); no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Where did lymphatic drainage first come up for you?</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -15571,6 +15666,11 @@
           <t>Tier N: Acosta &amp; Cash 2009 Am J Gastroenterol systematic review found no methodologically rigorous controlled trials for general health, multiple case reports/series of harms. NCCIH 2025: limited evidence for colonic irrigation; serious side effects; harm more likely with GI disease, colon surgery, severe haemorrhoids, kidney disease or heart disease; laxatives cause dehydration; long fasts can upset electrolytes; people with diabetes check with care team; 2017 review: juice/cleanse weight loss mostly regained. Mishori 2011 J Fam Pract (V3 pointer) has no abstract in PubMed and I did not open full text, so not cited. Name avoids the banned word; key kept as given. Cost: estimate ~$100 a session, occasional; no pricing page opened. Safety rows: kidney and heart (clinician-first), diabetes for fasting cleanses, plus a general note.</t>
         </is>
       </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Who first suggested a colon cleanse?</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -15899,6 +15999,11 @@
           <t>V3 N, kept the substance but graded D: trials do exist, and they agree on no benefit, so the only support for the claim is mechanism (plasma glutamine dips after hard exercise). Gleeson 2008 (J Nutr review, abstract): claimed immune, glycogen and anticatabolic benefits have little support in healthy, well-nourished people; 20 to 30 g acutely and 28 g/day for 14 days without ill effect. Ramezani Ahmadi 2019 (Clin Nutr meta-analysis, 25 trials in athletes): no effect on immune system, aerobic performance or body composition; a small weight-reduction signal (-1.36 kg) that the authors note but which is not the reason people buy it. Candow 2001 (RCT, 31 adults 18 to 24, 6 weeks lifting, high dose): no difference in strength, lean mass or protein breakdown. V3's 'gut evidence is from hospital patients only' was not checked here and is left out of the summary. Some small studies report less soreness after eccentric exercise; I found them only via fitness-site summaries, not opened, so not used. Price is my estimate (about $20 for a month of 5 g); no pricing page opened. Moment set to evening (post-workout or bedtime use is common), a judgment call.</t>
         </is>
       </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Who put glutamine on your list?</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -16063,6 +16168,11 @@
       <c r="AJ97" s="3" t="inlineStr">
         <is>
           <t>V3 N; graded D. The testosterone claim traces to Brilla &amp; Conte 2000 (not opened here; reported by Wilborn as finding higher free testosterone, IGF-1 and strength in football players). Replications: Wilborn 2004 (JISSN RCT, 42 trained men, 8 weeks, funded by Cytodyne, which made the product tested; null for hormones, body composition and strength) and Koehler 2009 (EJCN, 14 exercising men with adequate zinc intake; no change in total or free testosterone). Edwards 2024 (Nutrients, 19 recreationally trained men with adequate intake, two nights, actigraphy) found no sleep effect. I chose D over C because the independent trials agree on no benefit; the claim rests on one unreplicated trial plus mechanism. Dose from Wilborn's product (30 mg zinc, 450 mg magnesium, 11 mg B6), a standard ZMA label. Overlap: already in the magnesium keep-one group. Safety: 30 mg zinc plus a zinc-containing multivitamin pushes intake high; I could not open the NIH ODS zinc sheet (Cloudflare block) to cite the 40 mg adult UL, so the safety note avoids the number and leans on a 2025 case report of zinc-induced copper deficiency. Price is my estimate (about $15 to $20 a month); no pricing page opened. Wearable partial: sleep tracking would show any change.</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Where did you first hear about ZMA?</t>
         </is>
       </c>
     </row>
@@ -16859,6 +16969,11 @@
           <t>V3 D, kept. No trial of any mushroom coffee product found. Ingredient evidence: Docherty 2023 (Nutrients pilot RCT, 41 healthy adults 18 to 45, 1.8 g lion's mane): faster Stroop at 60 min after one dose, a non-significant trend to less stress at 28 days, plus null and some negative findings. Mori 2009 (older adults with MCI, 3 g/day) is not the target group, so not cited. Menon 2025 systematic review: 5 RCTs, mostly cognition in people with and without dementia; side effects include stomach upset, headache, allergy. Ryze holds about 2 g of a six-mushroom blend and 48 mg caffeine per serving (company figures via a nutritionist's review updated March 2024; per-mushroom amounts undisclosed; the 0.33 g each figure would be an equal-split assumption, so the summary avoids it). D rather than C because no study tested these amounts; the lion's mane pilot used close to a whole cup's blend of one mushroom. Price: Ryze product page, $45 list for 30 servings ($27 on a sale when opened). Caffeine is roughly half a cup, so this row's real sleep effect is gentler than coffee; it stays in evening-stimulants. A 2026 case report of shiitake dermatitis from mushroom coffee exists (abstract unavailable), so no safety row.</t>
         </is>
       </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Where did mushroom coffee first catch your eye?</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -17015,6 +17130,11 @@
       <c r="AJ103" s="3" t="inlineStr">
         <is>
           <t>Tier D: searched Europe PMC for human trials of Chondrus crispus / sea moss / Irish moss and found none (only cow and hen feeding studies). Claims rest on mineral content, i.e. mechanism and anecdote. Safety evidence is real: Aakre 2021 (Norwegian market, not sea moss specifically, mostly kelps) shows seaweed iodine per serving often exceeds the UL; Rejuso 2026 is the first US sea moss product survey (66 products) with arsenic/cobalt/mercury in dried product and Salmonella/Cronobacter isolates. I could NOT open the NIH ODS iodine fact sheet (Cloudflare 403), so the adult UL (1,100 mcg) is not cited here; worth adding nih-ods iodine if another agent has it. Did not find a sea moss-specific iodine assay paper. Could arguably join daily-multivitamin overlap ('92 minerals' marketing) but I left overlaps empty since that group's members list doesn't include it. Price is an estimate (gels often $25 to $40 a jar), no pricing page opened. Rewrote fits_instead to avoid a claim I can't source about health benefit. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Who got you onto sea moss?</t>
         </is>
       </c>
     </row>
@@ -17179,6 +17299,11 @@
           <t>Tier N. Pandit 2016 (Andrologia, PrimaVie) lists Natreon Inc as funder in Europe PMC grant data, so it counts as none. Yadav 2026 (TruBlk resin) is open-label, single-arm, and 4 of 6 authors are at Amaara Botanicals (the brand). A 2026 TruBlk RCT is a preprint by the same group (not opened). Martinez 2025 RCT tested chromium + amla + shilajit together (not opened, combination, can't isolate). Morgado 2024 rates PrimaVie 'possibly effective' in low-T men, but that rests on brand trials. V3 claimed raw shilajit 'repeatedly' contains lead and arsenic: I could not verify that for shilajit specifically; I did find Kamgar 2025 (thallium in raw and supplement shilajit). Safety row is a note to buy tested product. Price estimate (resin jars roughly $30 to $60 for a month); vendor page I opened showed no price.</t>
         </is>
       </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>What first put shilajit on your radar?</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -18961,6 +19086,11 @@
           <t>Tier N by the brief's rule (brand-affiliated only counts as none), but this is a judgement call: V3 had C. The human sleep trials (Inagawa 2006, Yamadera 2007, Bannai 2012) all include Ajinomoto researchers; Ajinomoto sells glycine. Bannai 2012 full text: single-blind crossover, 7 analysed, all Ajinomoto employees, 3 g 30 min before bed after sleep restriction; day-1 fatigue and PVT improved, most other measures not. Yamadera 2007 (Sleep Biol Rhythms 5:126-131, co-authors Inagawa and Bannai of Ajinomoto): only Crossref metadata opened, no abstract, so not cited as a source. Soh 2024 GeroScience systematic review (abstract, independent): sleep gains in healthy adults came from small, high-risk-of-bias studies. If Veer prefers to count academic first authors as independent, regrade to C and drop BORROWED_WEAK rationale accordingly (BORROWED_WEAK still allowed at C). Price estimate (~$10/month for 3 g/day powder); no page opened.</t>
         </is>
       </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Where did glycine at bedtime come from?</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -19621,6 +19751,11 @@
           <t>Tier D. Europe PMC search (apigenin + sleep + human) found no RCT of apigenin alone. Viola 1995: apigenin isolated from chamomile binds the benzodiazepine receptor, anxiolytic in mice, sedative only at 10x dose. Mastrofini 2026 JISSN RCT (n=103 active adults): evening blend had 50 mg apigenin plus magnesium L-threonate and L-theanine, so apigenin's own effect can't be separated; funding not visible in the record. Wong 2026 mouse study: apigenin + magnesium synergy (animal). Popularity traces to a podcast sleep protocol (not sourced, from V3). Price estimate (~$15-25/month for 50 mg). No safety row: no specific harm found in opened sources. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Did apigenin come from a podcast sleep stack, or somewhere else?</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -19953,6 +20088,11 @@
           <t>Tier D for adult sleep. MSK About Herbs (updated 2022, full page): 'studies evaluating 5-HTP for insomnia are lacking'; avoid with SSRIs, MAOIs, tricyclics without physician; case reports of serotonin syndrome (with linezolid), mania (with MAOI), scleroderma-like illness (with carbidopa), and eosinophilia-myalgia from a contaminated product. Europe PMC: adult sleep work is cat/rat studies plus a 1981 case letter; the only sleep RCT is Bruni 2004 in children with sleep terrors (2 mg/kg, positive) - different population and outcome. Mood: Shaw 2002 Cochrane, 108 trials found, only 2 (n=64) met quality, inconclusive; Javelle 2020 Nutr Rev meta (13 studies, weak, few placebo-controlled) seen in listing. Sertraline + 5-HTP serotonin syndrome case (Am J Case Rep 2017) seen in search only. Safety: never-suggest on antidepressants. Price estimate (~$10-20/month).</t>
         </is>
       </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Who suggested 5-HTP to you?</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -20117,6 +20257,11 @@
       <c r="AJ122" s="3" t="inlineStr">
         <is>
           <t>Tier N by the brand-funding rule. Hausenblas 2024 Sleep Med X (full text): n=80, 1 g/day Magtein x21 days; funded by AIDP Inc. (3 authors are AIDP; product from Threotech); ISI interaction not significant (p=0.39); Oura deep/REM scores and some self-reports better. Europe PMC lists the grant as 'CNY Arts' - conflicts with the paper's own funding line; the paper says AIDP. There is a 2025 erratum. Lopresti 2025 Front Nutr (full text): n=100, 2 g/day (145 mg elemental) x6 weeks, funded by Threotech, which also co-designed the study; only PROMIS sleep-related impairment improved (p=0.043), Oura sleep unchanged; cognition composite improved. V3's 'Neurocentria' funding claim was not confirmed: funders are AIDP and Threotech. Plain magnesium has its own C-level sleep evidence (existing sources arab-2023, mah-2021, schuster-2025 - not re-opened here). Kidney safety row added from general magnesium knowledge plus MedlinePlus magnesium oxide precaution; NIH ODS page returned 403, so no fact-sheet citation. Price estimate (~$30-45/month for 2 g/day); vendor pages returned 403. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>What drew you to this form of magnesium?</t>
         </is>
       </c>
     </row>
@@ -20273,6 +20418,11 @@
           <t>Tier N. Groeber 2017 Nutrients review (abstract via Europe PMC): claims that transdermal magnesium beats oral are not supported by scientific evidence; oral magnesium's benefits for deficiency are documented. Note: Groeber/Vormann are linked to magnesium-industry bodies, but the conclusion runs against the transdermal products. Found no sleep trial of magnesium spray. kind set to 'topical' (V3 said supplement). FORM_NOT_ABSORBED fits the core claim. Overlap: this key is NOT yet in the 'magnesium' group in existing-overlaps.json; needs adding or drop OVERLAP. fits_instead mentions a warm bath (evening warm bath has its own evidence row, haghayegh-2019). Price estimate (~$10-15 a bottle lasting about a month).</t>
         </is>
       </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Where did you pick up the magnesium spray?</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -20911,6 +21061,11 @@
       <c r="AJ127" s="3" t="inlineStr">
         <is>
           <t>Tier D: no human trials of bone broth for skin, joints or gut turned up in Europe PMC searches (bone broth + randomized/clinical trial/crossover). Alcock 2019 (IJSNEM, lab analysis): standardized-recipe broths had significantly lower glycine, proline, hydroxyproline etc. than a 20 g collagen supplement dose, with large variation across recipes; cafe broths highest. Alcock 2019 Front Nutr (300 mL broth in a plasma amino acid study) exists but I did not open it fully. Matar 2025 (Dig Dis Sci) is a narrative review arguing gut-barrier benefits from broth's components (glutamine, glycine), i.e. mechanism, not broth trials. Myung 2025 (existing source): collagen effects on skin vanish in non-industry-funded and high-quality RCTs, which undercuts the collagen rationale. It is a real food with some protein, so it is not harmful; D is about the borrowed claims. Price: estimate from search-result listings (Walmart $6.58, Thrive $7.99 for a 16.9 oz carton, about 2 mugs); a few mugs a week is about $50/month. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>What got bone broth into your day?</t>
         </is>
       </c>
     </row>
@@ -21995,6 +22150,11 @@
           <t>Tier D: Linus Pauling Institute (Oregon State) chlorophyll/chlorophyllin page (updated 2021, reviewed 2022): most OTC 'chlorophyll' is sodium copper chlorophyllin; skin evidence is two 10-person topical gel pilots (acne, photodamage) plus case reports; odor-control evidence mixed (one placebo-controlled colostomy trial null); the aflatoxin-adduct RCT (n=180, China) is in a high-exposure population and irrelevant here. No oral trials for skin, energy or bloating turned up in Europe PMC searches. LPI: not tested in pregnancy or lactation; green stools, tongue discoloration, false-positive guaiac test. Dose shown is what odor studies used, not a benefit threshold. Price: estimate ($12 to $20 a bottle lasting about a month).</t>
         </is>
       </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Where did chlorophyll water first show up for you?</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -22621,6 +22781,11 @@
       <c r="AJ138" s="3" t="inlineStr">
         <is>
           <t>Tier D (V3 D). PubMed search for microcurrent plus face/wrinkle returned no RCT of a NuFACE-type device. Bu 2024 (full text) says microcurrent research is relatively scarce; its only trial (Slendertone Face) is neuromuscular stimulation, not microcurrent. Other hits were combined RF-microcurrent devices run by contract labs or device teams (Nobile 2016, Kubik 2026), not the same technology, so not cited. Layne 2026 (abstract) is general about home devices. A 2026 Cutis letter (Kadam and Lipner) on adverse events from home microcurrent devices exists, but the full text was paywalled, so it is not cited; worth Ishan pulling. Price: NuFACE MINI+ $250, TRINITY+ $395 (opened), over 24 months plus conductive gel, about $20 (estimate for gel). Safety rows come from brand warnings via Space NK (opened).</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>How did the microcurrent device come into your routine?</t>
         </is>
       </c>
     </row>
@@ -22939,6 +23104,11 @@
           <t>Tier D for the doubled step (V3 C). Hamie 2024 (abstract) names the lack of trials on eye cream formulations as a key limitation; individual ingredients have small studies. No trial compares an eye cream with the same user's face moisturizer around the eyes. Messaraa 2020 (Oriflame-run, n=49, abstract) found a five-step routine incl. eye cream beat a two-step one over 4 weeks, but it tests the whole routine and is brand-funded. V3's claim that most eye creams are the brand's moisturizer in a smaller jar was NOT verified and is left out. AAD (opened) warns too many products can irritate and suggests the ring finger near the eyes; fits_instead leans on that. Keep if it carries a retinoid or caffeine the moisturizer lacks: the human_question surfaces that. Price $45/month is V3's estimate, not checked; drugstore eye creams cost far less. Moisturizer near the eyes being fine is a reasonable inference, not an explicit AAD statement.</t>
         </is>
       </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Who recommended an eye cream on top of your moisturizer?</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -23091,6 +23261,11 @@
       <c r="AJ141" s="3" t="inlineStr">
         <is>
           <t>Tier D (V3 N). Yuanxi 2016 (abstract, sample size not stated in abstract) is the only direct test found: cream alone matched toner plus cream on dry skin; toner alone ranked last; re-applying toner every 2 h did add hydration. Messaraa 2020 (brand-run) tests a whole routine. AAD rosacea page (existing source) says never use astringents or toners with rosacea; AAD order page and 2025 guide favor fewer products. V3's claim that modern cleansers do not leave skin needing rebalancing was not verified and is left out. Exfoliating (acid) toners are a different product and belong with the exfoliant rows. Damp-skin tip in fits_instead leans on the existing aad-2026-dry-skin source (Veer to confirm wording there). Price $25 is V3's estimate.</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Where did toner come into your routine from?</t>
         </is>
       </c>
     </row>
@@ -23243,6 +23418,11 @@
           <t>Tier D for the stack (V3 C). No study of combining facials, home LED and microcurrent was found; each part is graded in its own row (LED C, facials C, microcurrent D). TOO_MANY_STEPS fits: AAD warns many products and multiple anti-aging steps can irritate, though devices are not products, so this is a stretch Veer may want to drop. kind set to device because two of three parts are devices; there is no combo kind. Cost: Heyday ~$100 + LED ~$20 + microcurrent ~$20 = ~$140 (V3 had $200). Cadence weekly is a blend: facial monthly, devices most days. fits_instead rests on the sunscreen A row.</t>
         </is>
       </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>How did a facial, LED and microcurrent all end up in your routine?</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -23561,6 +23741,11 @@
       <c r="AJ144" s="3" t="inlineStr">
         <is>
           <t>Tier N for mass-market biotin gummies (V3 N). Patel 2017 (full text): every case of biotin helping hair had an underlying condition; no RCTs in healthy people. ConsumerLab (opened): SugarBearHair is 5,000 mcg biotin per 2 gummies, ~$30 for 60, no studies of the formula, and over-labeled vitamin amounts. Drake 2023 JAMA Derm review (abstract): some branded multi-ingredient products (Viviscal, Nutrafol, Lamdapil, Pantogar) showed potential benefit, mostly in company-run trials. If a user has one of those, a separate row may be warranted (likely C), so this row should not be matched to Nutrafol/Viviscal. These gummies also hold a multivitamin's worth of A, B, C, D, E: Veer may want this key added to the existing daily-multivitamin group (only new groups go in overlap_additions, so not done here). Lab-test interference from Li 2017 and FDA (opened) drives the safety note. Price $30/month from ConsumerLab (opened).</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Where did you first see the hair gummies?</t>
         </is>
       </c>
     </row>
@@ -25535,6 +25720,11 @@
       <c r="AJ156" s="3" t="inlineStr">
         <is>
           <t>V3 N kept. Ali 2009 (J Altern Complement Med, NCCAM-funded): 34 adults with fibromyalgia, 8 weekly Myers' infusions vs lactated Ringer's placebo; no between-group differences, strong placebo response. Merck Manual consumer page (Shane-McWhorter, reviewed Jul 2025): no data support energy, immunity or stress claims; few studies, small, no placebo, or no benefit over placebo; lists fluid overload, arrhythmia with magnesium or potassium shifts, fainting, thiamine anaphylaxis, B6 nerve damage, infections from poor sterilisation; advises avoiding in pregnancy, breastfeeding, kidney disease, high BP or heart conditions; FTC charged a company in 2018. Alangari 2025 (Cureus narrative review, no COI): benefit in healthy people uncertain, no head-to-head with oral. US Pharmacist (Feb 2022) summarises FDA's alert on compounding by IV hydration clinics, med spas and mobile IV services under insanitary conditions, including a 2021 septic shock case after an IV vitamin infusion; the FDA page itself returned 404. Price opened: AZ IV Medics Scottsdale Myers' Cocktail $215, fluids-only $94, hangover IV $270. cost 215 = one Myers' a month (V3 cadence).</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>How did you first hear about IV drips?</t>
         </is>
       </c>
     </row>

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -609,6 +609,18 @@
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>evidence_summary (40 words or fewer), human_question (under 12 words) and fits_instead never use the words on the Words sheet, never say they or their, and never end in an exclamation mark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Swaps</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>swap_title, swap_slot (morning, midday, evening or night) and swap_per_week (blank for every day) name the thing a person can add to their Ritual once they let this go. Only for a fits_instead that is something to do, never something to buy. swap_title is 6 words or fewer and follows the same word rules.</t>
         </is>
       </c>
     </row>
@@ -623,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK157"/>
+  <dimension ref="A1:AN157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -850,6 +862,21 @@
           <t>origin_question</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>swap_title</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>swap_slot</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>swap_per_week</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1855,6 +1882,19 @@
           <t>How did greens powder find its way into your mornings?</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Spinach and berry smoothie</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2531,6 +2571,16 @@
       <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>Tier A grades the sleep cost, so EVIDENCE_REGULAR is deliberately left out of keep_when: a strong tier on a cost item is not a reason to keep it. Same choice for energy drinks and evening alcohol. V3 was wrong on its headline number: in Drake 2013, 41 minutes was the self-reported (diary) loss at six hours, which did not reach significance (p = 0.08); the home EEG monitor measured more than an hour lost (1.1 to 1.2 h across the 0, 3 and 6 h conditions). Drake was funded by Zeo, the maker of the monitor, not a caffeine brand; n = 12. V3's '5 to 6 hour half-life' is narrower than Gardiner 2023's 2 to 10 h range across healthy adults. Gardiner's model puts a 107 mg cup's cut-off 8.8 h before bed (1:12pm for a 10pm bedtime), so '2pm' fits a bedtime around 11pm and is generous for earlier sleepers; black tea (47 mg) had no cut-off. Included studies were mostly low-to-moderate habitual users; tolerance in heavy users is unclear. dose_typical is caffeine per cup (Gardiner 107 mg per 250 mL; FDA 113 to 247 mg per 12 oz). cost_month_usd 40 is my estimate for a mix of cafe and home or office cups; moving the cup earlier saves nothing. Safety rows supported by EFSA and FDA (pregnancy, breastfeeding, medicines) and Gardiner 2023 (antidepressants, oral contraceptives).</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Decaf or black tea after 2pm</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>midday</t>
         </is>
       </c>
     </row>
@@ -4291,6 +4341,19 @@
           <t>V3 tier C kept. V3 said late work goes with lower HRV; I found no support: Kubo 2021 found no link with morning cortisol, and Wendsche 2017 found detachment unrelated to physiological stress markers, so the HRV claim is dropped. Evidence is observational (Wendsche: 91 samples, mostly self-report; Kubo: n = 58 with actigraphy, sleep quality but not duration). He 2020 tests phone restriction in general, not work email. Cause may run both ways: poor detachment can drive late email. Could not open the abstracts of Lanaj 2014 (late-night smartphone use, OBHDP) or Kushlev 2015 (email batching, CHB), so neither is cited. also_serves 'sleep' here means the habit touches sleep, not that it helps it.</t>
         </is>
       </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>One evening email check, then notifications off</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4448,6 +4511,19 @@
         <is>
           <t>V3 tier C kept, now sourced. Orthosomnia evidence: case series (Baron 2017), cross-sectional screening (Jahrami 2024: 3% to 14% of a 523-person sample depending on cut-off), survey (Lundekvam Berge 2026: negative effects higher with insomnia). Experiments: Gavriloff 2018 (insomnia, n = 63) fake low feedback left people less alert and more tired; Draganich 2014 (n = 164) assigned sleep quality predicted 2 of 4 cognitive tests; Robson 2022 (healthy, n = 54) one fake score changed neither arousal nor diary sleep. No trial compares daily checking with not checking. V3 said worry about the number makes sleep worse; the experiments show effects on next-day feelings, not on sleep itself, so that claim is softened. wearable_sees no: the effect is on how the day is judged, which device data cannot separate. Keep V3's offer to hide scores.</t>
         </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>A weekly look at sleep trends</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8619,6 +8695,16 @@
           <t>How did the phone become part of bedtime?</t>
         </is>
       </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Phone charging outside the bedroom</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -10510,6 +10596,16 @@
           <t>Where did you hear about EMF stickers?</t>
         </is>
       </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Phone across the room at night</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -12211,6 +12307,19 @@
           <t>Where did you come across grounding?</t>
         </is>
       </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Barefoot time on grass or sand</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>midday</t>
+        </is>
+      </c>
+      <c r="AN72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -12370,6 +12479,16 @@
           <t>How did the salt lamp end up in your room?</t>
         </is>
       </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>A warm, dim lamp in the evening</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -16974,6 +17093,16 @@
           <t>Where did mushroom coffee first catch your eye?</t>
         </is>
       </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Half-caf morning coffee</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>morning</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -19756,6 +19885,16 @@
           <t>Did apigenin come from a podcast sleep stack, or somewhere else?</t>
         </is>
       </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>Chamomile tea</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -20091,6 +20230,16 @@
       <c r="AK121" t="inlineStr">
         <is>
           <t>Who suggested 5-HTP to you?</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>A short worry list before bed</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>night</t>
         </is>
       </c>
     </row>
@@ -20423,6 +20572,19 @@
           <t>Where did you pick up the magnesium spray?</t>
         </is>
       </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>A warm bath</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="AN123" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -20901,6 +21063,16 @@
           <t>Framed as a cost habit (sleep), so UNLOVED_HABIT and no EVIDENCE_REGULAR. Tier B, not A: the caffeine-sleep meta-analysis (Gardiner 2023, 24 studies, TST -45 min, coffee 107 mg needs &gt;=8.8 h before bed) is strong for caffeine, but matcha itself was not tested and its dose is lower. Caffeine content from Unno 2026 review tables: 31 to 40 mg caffeine per g of matcha; I assumed a 2 g serving (common cafe/ceremonial serving; not from a source). Theanine + caffeine improved attention in small human studies cited by Unno; whether theanine softens the sleep cost is untested, so I did not claim it. Drake 2013: 400 mg even 6 h before bed disrupted sleep (higher dose than matcha). Whether the cost applies depends on bedtime: a 1pm matcha with an 11pm bed is outside the window, so the engine should pair this with a bedtime when it has one. Cost $30: estimate for a home matcha tin (cafe matcha would be far more).</t>
         </is>
       </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>A caffeine-free afternoon tea</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>midday</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -21067,6 +21239,19 @@
         <is>
           <t>What got bone broth into your day?</t>
         </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>A mug of miso or homemade stock</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="AN127" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -21538,6 +21723,16 @@
           <t>Cost habit, so UNLOVED_HABIT and no EVIDENCE_REGULAR. Tier A describes the cost of late caffeine: Gardiner 2023 meta-analysis (24 studies): TST -45 min, sleep efficiency -7%, SOL +9 min, WASO +12 min, less deep sleep; coffee (107 mg/250 mL) &gt;=8.8 h before bed to avoid TST loss. Drake 2013 RCT: 400 mg at 0, 3 or 6 h before bed all disrupted sleep. FDA consumer page: 400 mg/day (about two to three 12 oz cups) generally not linked to negative effects in most adults; 12 oz brewed coffee is 113 to 247 mg. So a second cup at 10am is usually fine; the cost is timing or a total well past 400 mg. V3's HRV claim was not checked here and is left out. Cost $40 is an estimate (mix of home brew and some cafe cups); timing rows otherwise have no product cost. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>Half-caf for the later cup</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>midday</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -21988,6 +22183,16 @@
           <t>Cost habit: UNLOVED_HABIT, no EVIDENCE_REGULAR. Tier C because the evidence is mostly observational: Iao 2022 (American Time Use Survey, nationally representative): eating/drinking &lt;1 h before bed linked to longer sleep but about 2 to 2.6x the odds of WASO &gt;30 min; causality unclear. St-Onge 2016 (26 adults, inpatient crossover; diet-sleep link analysed by regression on one ad-libitum day): higher % energy from sugar associated with more arousals; low fibre/high sat fat with lighter sleep. Kesgin 2025 (16 healthy 18 to 35 y, 1-week crossover): eating &gt;=25% of calories after 9:30pm raised AHI and lowered melatonin; that's heavy late eating, not a small dessert, so I used it as support only. No trial isolates a bedtime dessert. Cost 0: part of groceries. A loved evening ritual stays (THEIRS, LOVED).</t>
         </is>
       </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>Dessert right after dinner</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -22786,6 +22991,16 @@
       <c r="AK138" t="inlineStr">
         <is>
           <t>How did the microcurrent device come into your routine?</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>Two-minute face massage</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>evening</t>
         </is>
       </c>
     </row>

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>A smaller can before 2pm, or a cold sparkling water when it's mostly the fizz.</t>
+          <t>A smaller can before 2pm, and an earlier wind-down, so the afternoon dip asks for less caffeine.</t>
         </is>
       </c>
       <c r="AC12" s="3" t="n"/>

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -621,6 +621,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>swap_title, swap_slot (morning, midday, evening or night) and swap_per_week (blank for every day) name the thing a person can add to their Ritual once they let this go. Only for a fits_instead that is something to do, never something to buy. swap_title is 6 words or fewer and follows the same word rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>builds</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>yes when the benefit builds with daily use (creatine, vitamin D, sunscreen, morning light), so doing it now and then mostly misses it. Distill then offers to anchor it to something they already do every day. no for things that work on the day (pre-workout, an eye mask).</t>
         </is>
       </c>
     </row>
@@ -635,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN157"/>
+  <dimension ref="A1:AO157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -877,6 +889,11 @@
           <t>swap_per_week</t>
         </is>
       </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>builds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1049,6 +1066,11 @@
           <t>Dose floor settled at 3 g/day. The ISSN 2017 position stand gives 3 g/day for 28 days as the low-dose route and says smaller amounts (e.g. 3-5 g/day) saturate muscle over 3-4 weeks; it never gives a 2 g human dose (it notes a normal diet already supplies 1-2 g/day). V3's ruleText cut-off of 2 g was wrong; the factCheck 3 g was right. Loading (~0.3 g/kg/day for 5-7 days, then 3-5 g/day) is optional; ISSN notes larger athletes may take 5-10 g/day. Female evidence is thin (Wang 2024: only 2 female-only trials, gains not significant). Wang co-author Candow advises creatine makers and most ISSN/Antonio authors disclose industry ties; Wang itself had no external funding and the strength effect is consistent (I2 = 0%), so A stands. FORM_NOT_ABSORBED: ISSN and Antonio find no form better than monohydrate and ISSN does not mention HCl, so for HCl or buffered the verdict should say monohydrate is the studied form, not that the other form fails; ethyl ester has the weakest case. tier_otherwise C: without training, gains are small and inconsistent (Antonio 2021, mostly older-adult data). V3's claim about thinking during sleep loss was not checked and is left out of person-facing text. Effect on sleep or HRV is not visible to wearables. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1221,6 +1243,11 @@
           <t>Tier A holds for people who lift, but the effect is modest (Morton 2018: +0.3 kg lean mass, +2.5 kg 1RM) and plateaus near 1.6 g/kg/day of total protein (CI 1.03-2.20; authors suggest ~2.2 g/kg/day may be prudent). A lifter already eating that much from food gets little extra; the brief allows only one evidence_requires value, so intake is a second condition the engine could ask about. Supplement dose was not a moderator in Morton (4-106 g/day used, 5-44 g post-exercise), so DOSE_BELOW_MIN is left out; dose_min 20 g mirrors the ISSN per-serving guidance (20-40 g or ~0.25 g/kg), not a proven floor. tier_otherwise C: Nunes 2022 found no significant lean-mass gain without resistance exercise (6 trials, low certainty). Phillips (author of both meta-analyses) discloses dairy and beef industry honoraria; Nunes 2022 was ILSI Europe funded with industry co-authors. Lead: the 2025 Consumer Reports testing is cited through an NPR/OPB news report, not a peer-reviewed paper; flagged for reviewer. Kind kept as supplement although V3 treated it as plain food (V3 had no tier rule at all). Proposed a show-together group with collagen for combined protein grams.</t>
         </is>
       </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1389,6 +1416,11 @@
           <t>V3 graded B and said most positive trials were in people who don't eat fish; that is overstated. Only VITAL's prespecified fish-intake subgroup hinted at benefit in low fish eaters, and the authors call it hypothesis-generating (exact subgroup HRs sit in the NEJM supplement, which I did not open; vitalstudy.org returned 403). Hu 2019 could not test fish intake. Pooled RCTs show about 8% fewer heart attacks and coronary deaths in mostly older, higher-risk adults; Cochrane 2020 rates CV events as little or no effect (high certainty) and coronary events as a slight drop (low certainty). Hence C for low fish eaters. tier_otherwise D means no trial shows added benefit for people already eating oily fish weekly (the VITAL subgroup saw none); the scale has no 'tested and found little' grade, so D is the closest fit. Dose: V3 used both 500 mg and 1 g; set 840 mg EPA+DHA (VITAL dose; most trials ~850 mg; Hu range 376-4,000 mg). Count EPA+DHA from the label, not total fish oil weight (a 1,000 mg capsule often holds ~300 mg). New safety row: AF risk rises with dose (Gencer 2021, steeper above 1 g/day). V3's mood claim was not graded. Wearable set to no; small resting-heart-rate effects reported elsewhere were not checked here. No studies in 22-35-year-olds; all evidence extrapolated from older adults.</t>
         </is>
       </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1557,6 +1589,11 @@
           <t>Outcome chosen: bone density and levels when low, the one area where benefit clearly depends on baseline (Macdonald 2018: bone density rose only when starting 25(OH)D was at or below 30 nmol/L; the IOM found evidence for bone health only). Most 22-35 buyers want immunity, mood or energy, and those grade lower: colds C at best (Martineau 2017 showed a strong effect below 25 nmol/L, but Jolliffe 2021 and 2025 found no modification by baseline status and the 2025 overall effect is no longer significant); mood null (VITAL-DEP). tier_otherwise D means trials in people with normal levels found no bone, fracture or mood benefit (VITAL); the scale has no 'tested and found little' grade. B rather than A because the deficiency evidence comes from subgroup analyses of a few trials plus the IOM consensus. V3 nudged a ~$30 blood test: the Endocrine Society 2024 guideline suggests against routine 25(OH)D testing in healthy adults and against doses above the DRI for ages 19-74, and the IOM notes many labs use cut-offs that overstate deficiency (20 ng/mL, 50 nmol/L, is adequate for nearly everyone). Drop the testing nudge; ask whether a clinician already said it runs low. V3 put harm above 10,000 IU: the upper limit is 4,000 IU/day; above 10,000 IU/day is where kidney and tissue damage is documented. If clinician-prescribed (e.g. weekly high-dose), treat as clinician-led and protect. dose_min 600 IU is the RDA; DOSE_BELOW_MIN left out because correcting a deficiency is a clinician call. AG1 Next Gen reportedly has no vitamin D, so D plus AG1 is not an overlap (see overlap proposals). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1715,6 +1752,11 @@
           <t>C because the trials disagree slightly: the USPSTF evidence review pooled a small drop in cancer incidence (OR 0.93, 4 RCTs, limitations noted) while COSMOS found no effect on cancer, CV events or mortality; USPSTF grade is I (insufficient). V3 said there was no effect on cancer, which is not quite right. The cognitive benefit is confirmed only in adults 60+ (COSMOS, about 2 years of cognitive aging slowed). No trials in 22-35-year-olds. V3 also said it does no harm: USPSTF recommends against beta-carotene, which raises lung cancer risk in people at high risk (e.g. smokers), and some multis contain it. The safety list has no smoking condition, so this needs a reviewer decision. Targeted needs (B12 for vegans, iron, folate before pregnancy) are separate items and often clinician-led. COSMOS funders include Pfizer per the record; whether pills were donated was not confirmed. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1895,6 +1937,11 @@
       <c r="AN7" t="n">
         <v>3</v>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2063,6 +2110,11 @@
           <t>V3 graded B; the independent evidence does not back that. Myung 2025 (23 RCTs) found the pooled effect positive, but trials without company funding and high-quality trials showed no effect on hydration, elasticity or wrinkles. Graded C (studies disagree, split by funding). A stricter reading could give N, since the positive results come only from company-funded trials; reviewer call. Myung is abstract-only (full text paywalled), so subgroup sizes are unknown. De Miranda 2021 (19 RCTs, positive) did not assess funding in its abstract. V3's dose floors (5 g and 10 g) are unsupported: a positive RCT used 2.5 g/day (Proksch 2014; funding not stated in the record). The upper end of dose_typical (10 g) comes from typical products and V3, not from a trial opened in this session. Joint and hair outcomes were not graded. fits_instead rests on the Hughes 2013 sunscreen RCT. No safety rows: no interaction found in the sources opened.</t>
         </is>
       </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2235,6 +2287,11 @@
           <t>22 Oct: EVIDENCE_REGULAR and TRAINS removed from keep_when. The engine reads 'trains' as anyone with a gym or training habit, but the B here holds only for sessions over about an hour or heavy sweating, so LMNT was being praised as 'real work for your training' for ordinary gym-goers. Now it is neither protected nor cleared for them (their call), and the human question asks which it is. Earlier notes: Dose fields are mg of sodium per litre during sessions over about an hour (ACSM 1996 stand, 0.5 to 0.7 g/L); one LMNT stick holds 1,000 mg. Both hydration-index trials were beverage-industry funded, so the B rests on the ACSM stands. No consistent link with cramps (Costa 2026). LMNT's page claims 4 to 6 g sodium a day, well above the NKF's 2,300 mg ceiling.</t>
         </is>
       </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2407,6 +2464,11 @@
           <t>Tier A rests on the caffeine (ISSN 2021 stand; Grgic 2020 umbrella review of 21 meta-analyses, moderate-quality evidence, mostly young men), not on the blend: I found no meta-analysis of multi-ingredient pre-workouts, product trials are small and often brand-linked, and 44% of listed ingredients sit in proprietary blends with beta-alanine below its effective dose (Jagim 2019). 89% of regular users take it for energy and focus (Jagim 2019 survey), which is why evidence_for names energy as well as performance. V3 graded B and said the sleep cost starts 'after 2pm'; Gardiner 2023 modelled a standard 217.5 mg pre-workout needing about 13.2 h before bed to avoid lost sleep (before 8:50am for a 10pm bedtime), so afternoon and evening scoops cost more than V3 implied. dose_min 140 mg = 2 mg/kg at 70 kg, the ISSN 'may be as low as' figure; 3 to 6 mg/kg (about 200 to 400 mg) is the consistently effective range, so a stim-free tub fails DOSE_BELOW_MIN. tier_otherwise N: no studies of pre-workouts outside training; for alertness alone, coffee carries the same caffeine. Coffee as a substitute is my inference from caffeine being the shared active ingredient, not a head-to-head trial. Safety rows: pregnancy and breastfeeding from EFSA and FDA plus Jagim 2019's 254 mg average serving; heart from Bella 2025, Jagim 2019 (self-reported heart abnormalities) and the energy-drink ECG trials; under-18 extends AAP 2011's energy-drink guidance to stimulant pre-workouts; medicines from FDA and Gardiner 2023 (antidepressants and oral contraceptives change caffeine half-life). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2583,6 +2645,11 @@
           <t>midday</t>
         </is>
       </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2749,6 +2816,11 @@
           <t>V3 was wrong that energy drinks have 'more effect on resting heart rate': the meta-analysis found no significant heart-rate change (+0.8 bpm, Shah 2016), and with caffeine matched at 320 mg an energy drink raised QTc and systolic pressure more than caffeine alone while heart rate did not differ (Fletcher 2017). V3 graded B; the sleep tier A comes from the caffeine meta-analysis (Gardiner 2023), since a can is a caffeine dose. Energy-drink-specific sleep evidence is cross-sectional (Kaldenbach 2024: 53,266 Norwegian students aged 18 to 35, a good age match), so it supports but does not carry the A. EVIDENCE_REGULAR left out because the tier grades a cost. dose_typical uses FDA's 54 to 328 mg per 16 oz range; the engine should read the actual can. Sugar, taurine and other ingredients were not graded here. Safety rows supported by AAP 2011 (under-18), Shah 2019 and Fletcher 2017 (QTc in healthy young adults), Shah 2016 (blood pressure), FDA and EFSA (pregnancy, breastfeeding, medicines).</t>
         </is>
       </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2911,6 +2983,11 @@
           <t>V3's 'HRV down 10 to 25 percent' misread Pietila 2018: the 9.3 and 24.0 figures are percentage-point drops in Firstbeat's HRV-derived 'recovery' score at low and moderate intake; RMSSD itself fell 2.0 and 5.7 ms, and heart rate in the first three hours of sleep rose 1.4 and 4.0 bpm (8.7 at high intake). That study is observational (within-person, 4,098 Finnish employees, mean age 45, effects stronger in younger people) and two authors worked for Firstbeat. V3's 'fall asleep faster' at one or two drinks is not supported by the meta-analysis: Gardiner 2025 saw faster sleep onset only at about five drinks, and total sleep, efficiency and night waking were too uncertain to call. The older qualitative review (Ebrahim 2013) reported faster onset and second-half disruption at all doses, so the two disagree on those points while agreeing on REM; the A applies to REM. V3's 'shows up the same night on every wearable' has no source. EVIDENCE_REGULAR left out because the tier grades a cost. dose_typical is grams of pure alcohol for one to two US standard drinks (14 g each). Frame as what a drink costs, never as stopping; social drinking is often LOVED and kept. Safety rows supported by the US container health warning (27 CFR 16.21), CDC breastfeeding guidance, NIAAA pages (medicine interactions, liver, mental health, legal age 21) and ADA 2026 recommendation 5.19 (delayed lows with insulin or secretagogues).</t>
         </is>
       </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3071,6 +3148,11 @@
       <c r="AJ14" s="3" t="inlineStr">
         <is>
           <t>V3 graded B and said eating late raises overnight heart rate and body temperature. I found no source for body temperature. For heart rate, the only trial I found runs the other way round and in an older group: finishing eating at least 3 h before sleep lowered nighttime heart rate and raised HRV as secondary outcomes in 39 adults aged 36 to 75 with overweight (Grimaldi 2026). For sleep, the one polysomnography RCT (Gu 2020, 10pm vs 6pm dinner, healthy adults around 26) found no change in sleep stages; surveys link eating close to bed with more night waking (Chung 2020, ages 18 to 29; Iao 2022, US time-use data); a one-week crossover in 16 adults aged 18 to 35 found lower melatonin and more breathing events with heavy late eating (Kesgin 2025); a heavy 10pm protein-and-fat meal disturbed self-rated sleep in young men (Ucar 2021). Disagreement plus small trials gives C. The reflux link (Fujiwara 2005) is a case-control association in reflux patients. dose_typical is the gap between finishing dinner and bed, in minutes. Several sleep-cost items (this, evening alcohol, late caffeine) share the same nights; worth testing one at a time so wearable effects don't blur. Safety row supported by ADA 2026 recommendation 5.28 (consistent carbohydrate timing with fixed insulin doses).</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3223,6 +3305,11 @@
           <t>V3 graded B ('works if the food gets eaten') with no source. The weight-loss RCTs of prepared meals I found were company-linked: Rock 2016 was funded by Nestle, maker of the entrees (confirmed in the paper's full text); Rock 2010 is reported in press coverage of its disclosure as funded by Jenny Craig, whose program it tested (not verified in the paper itself). Both were in adults with overweight and included counselling. By the brief's rule brand-funded studies count as none. Independent evidence: one pilot RCT (Hollis-Hansen 2023: 70 food-pantry clients, free meals for two weeks, self-rated outcomes, no no-meal control group) and a 2025 scoping review that found only nutrient-calculation studies of meal kits, no intervention studies. Graded C on the small, short pilot; honestly close to D for paying 22-to-35-year-olds. The real clear code is UNUSED (food that goes uneaten). how_common 3 from Boyar 2025 (18% of US adults used a meal kit in the past week, more among younger, higher-income, health-minded people). cost_month_usd 350 blends meal kits (about $300) and ready-meal plans (about $450); my estimate, not sourced. fits_instead batch-cook idea leans on Ducrot 2017 (meal planning tied to better diet quality, cross-sectional). No safety rows: none found.</t>
         </is>
       </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3383,6 +3470,11 @@
       <c r="AJ16" s="3" t="inlineStr">
         <is>
           <t>V3 fact-check target confirmed: Wright 2013 (8 campers; clock about 2 h earlier after a week of natural light only; read in full text). Tier B is for clock timing only: lab bright-light experiments in healthy adults agree (Dautovich 2019 review, 32 experimental + 13 observational studies, no meta-analysis), but no trial tested 10 minutes outdoors, and everyday wrist-measured light shows weak or conflicting links (Bohmer 2021). Mood or energy claims would be tier C. V3 dayOne line ('about half of one night's normal swing') had no source and is dropped. clear_when empty: free, B tier, and the wake-up light rule keeps the free option. Area set to sleep (V3 batch was mind); reviewer may move it back. Never tell anyone to look at the sun. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -3547,6 +3639,11 @@
           <t>V3 tier B kept. A is arguable (Linardon 2024: 45 RCTs, effects held in lower-bias trials), but effects are small (g 0.24 to 0.28), measured only at post-test (10 days to 8 weeks), not better than active therapies, and the authors flag possible conflicts of interest in Headspace trials (k = 15; Calm k = 5). Gal 2021 stress effect (g 0.46) was heterogeneous (I2 68%). V3 line about sleep ('people say they sleep better; measured change smaller') was not checked here and is removed. Baumel 2019 backs the UNUSED path (median 30-day retention about 3%, meditation apps about 5%). V3 cost 15 reflects monthly billing; annual plans run about $70 a year, so 7 is a blended estimate (prices from third-party pages, not sourced). Safety note from Farias 2020. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3715,6 +3812,11 @@
           <t>V3 tier B lowered to C: one single-night PSG study (Scullin 2018, n = 57, healthy 18 to 30, d = 0.63) plus small mixed trials (Harvey 2003 pilot: shorter self-reported latency; Mooney 2009 in insomnia: no latency change). V3's '9 minutes faster' appears in Baylor University's own write-up (opened), not in the paper's text, which reports the effect size and shows means in a figure I did not read; keep the number out of person-facing copy unless verified. The tested form is a specific to-do list; a feelings journal is a different practice with weaker sleep evidence. BORROWED_WEAK listed because it is C tier, but it is free; the engine may want cost to weigh in. Area set to sleep (V3 batch was mind).</t>
         </is>
       </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3875,6 +3977,11 @@
       <c r="AJ19" s="3" t="inlineStr">
         <is>
           <t>V3 tier B raised to A: Choi 2025 (PNAS, preregistered, 145 papers, 24,804 people, g = 0.19, robust to publication bias). The effect is small and not specific to gratitude: Davis 2016 and Choi 2025 both find it matches other positive activities, and Davis found no effect on anxiety. Number of sessions did not moderate the effect (Choi), which supports the weekly fits_instead. Awe 'moral' is a judgment call: it fits when the practice dwells on other people's kindness (Keltner's moral beauty), much less for lists of pleasant things; blank it if the reviewer prefers. clear_when empty: free and A tier. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4144,11 @@
           <t>V3 tier B confirmed. Fincham 2023: 12 RCTs, 785 adults, g = -0.35 for stress, moderate risk of bias, effect significant in nonclinical samples; first author trained as a breath teacher. Balban 2023 (n = 108, remote, WHOOP-measured; senior author advises WHOOP): breathwork beat mindfulness on positive affect only; anxiety and negative affect fell equally in both, so V3's 'beat mindfulness for mood' holds for positive mood only. HRV rises acutely with slow breathing (Laborde 2022, 223 studies), confirming V3; V3's 'less carries into the night' had no source and is dropped. 4-7-8 and box breathing have little direct evidence: in one session, 6 breaths a minute raised HRV more than either (Marchant 2025, n = 84). Hyperventilation-style breathwork (for example Wim Hof) is a different item with fainting risk and is not covered here. wearable_sees partial: heart data shifts during a session; overnight carry-over unproven.</t>
         </is>
       </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4185,6 +4297,11 @@
       <c r="AJ21" s="3" t="inlineStr">
         <is>
           <t>Protected: never_clear yes and clear_when empty by design; no fits_instead offered for clinician-led care. Evidence population is people with depression or anxiety disorders, not healthy adults; no evidence_requires code fits, so it is set to none and the population sits in evidence_for. Keep the V3 behaviour of letting the person hide it from the cost total (hence the human_question). Cost: about $143 to $174 a session self-pay versus about $23 in-network copay (third-party 2026 figures, not sourced); 300 a month is a blended estimate for weekly sessions (V3 said 400). The safety row is a protection rule rather than a sourced interaction. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4354,6 +4471,11 @@
       <c r="AN22" t="n">
         <v>5</v>
       </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4525,6 +4647,11 @@
       <c r="AN23" t="n">
         <v>1</v>
       </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4688,6 +4815,11 @@
           <t>What got you wearing a second tracker?</t>
         </is>
       </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4854,6 +4986,11 @@
           <t>V3 tier A lowered to B. Sleep: small placebo-controlled patch trials in healthy non-smokers agree (Jaehne 2014, n = 66; Choi 2017, n = 16; also opened Gillin 1994 and Davila 1994, not cited), backed by actigraphy cohort data (Spadola 2019: nicotine within 4 h of bed, lower efficiency, about 6 more minutes awake) and a cross-sectional meta-analysis of vape-only users (Gulati 2026, OR 1.38). No sleep trial used pouches or vapes directly. Heart rate: dose-dependent; the pouch study (n = 15 smokers) found 20 to 30 mg pouches raise it 12 to 25 bpm but 6 mg only slightly; vaping about +2 bpm in a meta-analysis of mostly non-randomized studies. V3's 'lowers HRV' is not confirmed (Choi 2017: no overnight HRV difference). Withdrawal can upset sleep for a while (Jaehne 2009), so an evening-off test may look worse at first. If the pouch or vape replaced cigarettes, Distill should not propose letting it go; no safety condition code fits this, so it is flagged here and asked in human_question. The engine still needs V3's timing question (daytime only, some after 6pm, mostly evening). EVIDENCE_REGULAR left out of keep_when because the tier grades harm, not benefit. kind 'food-drink' is the nearest allowed value (no substance kind). Keep V3's stance: test evening timing, never a quit programme. Cost: ZYN about $5.50 to $6.25 a can retail, several pouches a day, about $80 a month (third-party pricing, not sourced; V3 said 60). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5014,6 +5151,11 @@
           <t>V3 tier A confirmed (Currier 2023 network meta-analysis, full text). V3 gave no dose: pooled trials show 2+ sessions a week with 2+ sets reliably build both strength and muscle; one multi-set session a week still built strength, but once-weekly single-set arms had credible intervals crossing zero. The longer-life link (Momma 2022) is cohort data with a J-shaped curve, best near 30 to 60 min a week. also_serves 'mind' rests on Noetel 2024, which studied people with clinical depression (very low certainty), so it stays internal and out of person-facing text. clear_when is empty on purpose: training itself is never proposed for letting go. Safety: Riebe 2015 abstract names the ACSM screening factors (current activity, known disease or symptoms, planned intensity); the clearance rule itself is the well-known ACSM algorithm, full text paywalled. Pregnancy note rests on WHO 2020 and the NHS page. wearable 'partial': sessions log, but strength gains barely show in heart data (Reimers 2018 found strength training's resting heart rate drop less consistent across sexes than endurance training's).</t>
         </is>
       </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5176,6 +5318,11 @@
           <t>V3 tier A kept for the outcome actually studied: aerobic fitness and resting heart rate from steady endurance training (Milanovic 2015, healthy adults 18 to 45; Reimers 2018). Not graded: 'zone 2 specifically'. Storoschuk 2025 (abstract) finds no evidence that zone 2 is the best intensity and says the enthusiasm draws on elite endurance athletes. V3's HRV claim and its 'Sandercock 2005' pointer were not opened, so HRV is dropped from the claim. dose_typical is MINUTES PER WEEK (WHO 150 to 300), not per session; 3+ hours a week sits inside that range. clear_when is empty on purpose: the cardio is never proposed for letting go; the lighter version lives in fits_instead. also_serves 'mind' rests on Noetel 2024 (walking or jogging, clinical depression, low certainty), internal only. awe 'nature' assumes outdoor runs, rides or hikes.</t>
         </is>
       </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5332,6 +5479,11 @@
       <c r="AJ28" s="3" t="inlineStr">
         <is>
           <t>V3 tier A kept but re-pointed: V3 named sleep and mood with no source; the graded outcome is fitness and blood pressure from walking RCTs in inactive adults (Murtagh 2015; lipids did not change). Steps and a longer life is cohort evidence: Ding 2025 curves bend around 5,000 to 7,000; Paluch 2022 finds mortality levelling at 8,000 to 10,000 for adults under 60, the age group this app serves. So fits_instead says 'much of', not 'all of', the benefit. dose_unit is blank because the allowed units have no steps option; proposing 'steps/day' as a unit. V3's 'one day's walk changes that night's sleep a little' was not checked and is dropped. also_serves 'mind' rests on Noetel 2024 (clinical depression) and Ding 2025 (fewer depressive symptoms at 7,000 steps, cohort), internal only. clear_when empty on purpose.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -5496,6 +5648,11 @@
           <t>V3 graded the membership itself A. Now the A belongs to the training it makes possible and holds only for people who use it (evidence_requires 'trains', tier_otherwise N). The main clear codes are UNUSED and OVERLAP. Usage evidence: DellaVigna and Malmendier 2006 (7,752 members of three US clubs; monthly members averaged about 4.3 visits, over $17 a visit, when a 10-visit pass cost $10 a visit). V3's visit thresholds (8+ a month keep; under 4 for two months running) are unsourced but line up with WHO's 2+ strength days a week, roughly 8 visits a month. cost_month_usd 50 is my estimate (budget gyms roughly $10 to $25, mid-tier $40 to $70), not sourced. wearable 'partial': workouts show up, the membership does not. Proposed 'gym floor access' group for two gyms doing the same job. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -5658,6 +5815,11 @@
           <t>No study found that compares outcomes by gym price, so the tier is the training's, applied only when the club gets used (otherwise N). Main clear codes: UNUSED and OVERLAP. V3's 'twice a week or more is worth almost any price' is opinion and is removed; V3's '$83 a visit' day-one copy is fine as arithmetic but not evidence. Premium clubs usually include a sauna or steam room, so proposed 'spa amenities' (with bathhouse or recovery-studio memberships) and 'gym floor access' (with a standard gym) groups. cost_month_usd 250 is my estimate (Equinox roughly $200 to $300+, Life Time roughly $100 to $250+), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -5824,6 +5986,11 @@
           <t>V3 said 'class formats have better attendance than open gyms, which is the honest case for paying more'. Not supported by what I opened: Burke 2006 found standard exercise classes did no better than home programs with some contact, while cohesion-building 'true groups' did best; Kritz 2026 (71 studies) found small, non-significant group edges for activity and health, and a significant edge for physical function only after removing outliers. Tier A is for the interval training itself (Milanovic 2015, healthy adults 18 to 45); no independent studies of the branded formats were looked for or found. Main clear codes: UNUSED and OVERLAP. Unflagged safety signal: spinning-induced rhabdomyolysis in healthy first-timers (Kim 2015, 11 cases); no schema condition fits, so suggest an item-level note such as 'ease into a first spin class'. awe 'collective' is for synchronized group classes; the row itself is a service. dose_typical 2 to 3 follows WHO-style weekly training, not a figure from the opened abstracts. cost_month_usd 200 is my estimate, not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -5992,6 +6159,11 @@
       <c r="AJ32" s="3" t="inlineStr">
         <is>
           <t>V3 tier B kept, outcome narrowed to stress and mood. V3 also claimed sleep benefits; not checked, so dropped. Support: Pascoe 2017 (42 RCTs against active controls, physiological stress markers, mixed populations), Pascoe and Bauer 2015 (25 RCTs, authors call it preliminary), Fleming and Herring 2018 (8 small pilates trials, inactive controls). Noetel 2024 ranks yoga among the stronger exercise types for clinical depression (very low certainty), internal only. Main clear codes: UNUSED and OVERLAP. The hot-yoga caution in pregnancy is in ACOG 804's full text, which I could not open (paywalled); the safety note rests on the NHS page (keep cool, stop if too hot, avoid lying flat on the back later). dose_typical 1 to 3 is common trial practice, not pulled from an opened abstract. awe 'collective' is for synchronized group practice; the row itself is a service. cost_month_usd 180 is my estimate (reformer pilates usually costs more), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6156,6 +6328,11 @@
           <t>V3 graded A with 'strong evidence that this works, if you'd otherwise skip'. The supervision-specific evidence is small: Fisher 2022 (exploratory, 12 studies; strength SMD 0.40 with a wide CI; trivial body-composition effect) and Mazzetti 2000 (about 20 trained men, 12 weeks). Tier A is the training's; the coach adds a modest, uncertain extra. Nothing I opened shows that a trainer improves attendance; that V3 premise is untested here. V3 had no overlap group and treated low use as cost-per-session only; now UNUSED (unused or expiring session packs) is the main clear code, plus a proposed 'coaching' overlap with paid coaching apps. never_clear 'no': a trainer is not clinician-led care (a physical therapist would be a different row). cost_month_usd 400 assumes roughly $60 to $100 a session, 1 to 2 a week; not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -6326,6 +6503,11 @@
           <t>V3 tier C changed: B for soreness in people who train (Machado 2016: small edge over passive rest, best near 10 to 15 C for 10 to 15 min; Moore 2022: soreness, perceived recovery and power better at 24 h after high-intensity work), C for everyone else (Cain 2025: 11 RCTs in healthy adults; stress lower only at 12 h; no mood change in the one mood study; sleep and quality of life each rest on a single study; inflammation up right after). Well supported: a small soreness benefit. Popular but thin: mood, dopamine, immunity, resilience. The dopamine figure that circulates traces to Sramek 2000, a one-hour head-out immersion at 14 C, not a 3-minute plunge. Buijze 2016: cold showers cut sick-leave days but not illness days. V3's 'an evening plunge can make it harder to fall asleep' is NOT supported: Robey 2013 and Chauvineau 2021 (small, trained men, lab sleep tests) found no change in sleep onset, and Chauvineau found fewer night arousals. V3's blunted-growth point is confirmed (Roberts 2015; Pinero 2024 applies to cold water within about 15 min after lifting). Popular 2 to 5 minute plunges are shorter than the 10 to 15 minutes best studied for soreness. Key mismatch: the overlap file lists 'cold-plunge-ice-bath-tub-owned', but the V3 row key is 'cold-plunge-ice-bath' and had no overlap group; see overlap_proposals. Safety: Shattock and Tipton 2012 for heart rhythm; the pregnancy, diabetes, blood pressure and medication rows rest on standard tub label warnings (read in a combined hot and cold tub manual, CSC Chill1000), which also flag alcohol and drowning risk. The schema has no alcohol or plunging-alone condition, so suggest an item-level caution: ease in, never alone, never after drinking. kind 'device' assumes an owned tub; a DIY ice bath would be 'practice'. cost_month_usd 100 is my estimate (tub amortized over a few years plus power), not sourced. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -6492,6 +6674,11 @@
           <t>V3 tier B changed to C. The longer-life and heart link is one observational cohort of 2,315 Finnish men aged 42 to 60 (Laukkanen 2015; 4 to 7 sessions a week had a sudden cardiac death HR of 0.37 versus once a week, while the 2 to 3 sessions CI crossed 1; sessions over 19 min also linked lower). Trials are few and small: Lee 2022 (47 inactive adults with risk factors, 8 weeks, systolic 8 mmHg lower than exercise alone) and Hussain and Cohen 2018 (40 studies, only 13 RCTs, mostly under 40 people). A search turned up no meta-analysis of RCTs showing a consistent blood pressure effect. Well supported: very little beyond short-term blood pressure dips; popular: longevity, recovery, sleep. V3's 'an evening sauna helps many people fall asleep faster' has no controlled sauna trial behind it that I could find; the warm-bath meta-analysis (Haghayegh 2019) backs the fits_instead instead. V3 safety 'not with alcohol' is confirmed (Hannuksela 2001), but the schema has no alcohol condition; suggest a cross-item note with 'alcohol-in-the-evening'. Hussain and Cohen report one small study (n=10) with a reversible drop in sperm production; no schema condition, internal only. cost_month_usd 0 because the gym or bathhouse rows carry the cost. dose_typical 2 to 7 spans the cohort's categories; the clearest links were at 4 to 7 sessions a week. Blood pressure and on-medication safety rows also lean on standard spa label warnings (high or low blood pressure, medication: consult a physician).</t>
         </is>
       </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -6646,6 +6833,11 @@
           <t>Tier A rests on one large independent RCT (Hughes 2013: n=903, 4.5 years, government-funded) plus a systematic review (Ronsch &amp; Bauer 2021) in which both photoaging trials favored sunscreen. That review calls the overall evidence base limited and notes guidelines put shade and clothing first, so a strict reading of 'several RCTs' could argue B. Both A and B keep it via EVIDENCE_REGULAR. The trial abstract gives no SPF; SPF 30+ and 1 teaspoon for the face are AAD advice. Skin-cancer outcomes are left out of person-facing text because they would be a medical claim. V3 overstated two things: 'nothing else on the shelf comes close' (retinoids have more photoaging RCTs) and 'the evidence is as strong as evidence gets'. kind=practice because the kind list has no topical-product option; propose adding one. UNUSED is included per its definition (a bottle can sit unused); drop it if sunscreen should never be proposed for letting go. No overlap group: if the table has an SPF moisturizer, SPF makeup or oral sun pills, propose a 'sun protection' group with keep-best-evidence. dose_unit is blank because the unit list has no % or teaspoon. how_common and cost are estimates. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -6804,6 +6996,11 @@
           <t>Tier A is for the class. Tretinoin has two systematic reviews (Sitohang 2022: 7 RCTs; Siddiqui 2024: 25 comparison studies), and both tretinoin and retinol were significant for fine wrinkles in a 23-RCT network meta-analysis (Lin 2025, which has internal inconsistencies and one co-author company affiliation). Over-the-counter retinol alone is closer to B (Kafi 2007: n=36, mean age 87, up to 3 times a week). The 2005 Cochrane photodamage review was withdrawn in 2015 over a sponsorship conflict, so it is not cited. Adapalene was not significant for fine wrinkles in Lin 2025 (very wide CI), so fits_instead points to drugstore retinol, not adapalene. never_clear=no because the row mixes OTC and prescription products; prescribed use is caught by the on-medication safety row, but splitting it into 'OTC retinol' and 'prescription retinoid' (never_clear yes) would be cleaner. V3 contradicted itself: goalNotes named overlap 'exfoliants' but overlapGroups was empty. A retinoid is not an exfoliant and should never be the step dropped, hence the proposed 'retinoid nights' group (keep-best-evidence). Pregnancy: the data show no clear harm but are underpowered (Kaplan 2015). The AAD says stop tazarotene, and most experts stop tretinoin and adapalene; the AAD does not address retinol, which is treated the same way as a precaution. The breastfeeding row rests on e-lactancia (APILAM, updated 2023-02-09, opened this session); LactMed was blocked by a captcha, so it is not cited. Concentrations need a % unit, which the list lacks. Lowest studied doses that worked: tretinoin 0.025% (Griffiths 1995), retinol 0.4% (Kafi 2007). Cost $25 (V3 had $40) is an estimate: drugstore retinol is about $10 a month, telehealth tretinoin $20 to 40, premium serums $30 to 45. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -6956,6 +7153,11 @@
       <c r="AJ38" s="3" t="inlineStr">
         <is>
           <t>Tier C (V3 had B). The only RCT-only review found 7 trials with 139 people in total (Correia 2023). A 2026 review of 44 studies says many were small, short, open-label or industry-sponsored. Reported effects: objective lightening and smoother skin; hydration was no better than placebo. V3 had stability backwards: L-ascorbic acid is the unstable form, while derivatives are stable but less studied, and in pig skin magnesium ascorbyl phosphate, ascorbyl palmitate and dehydroascorbic acid did not raise skin vitamin C (Pinnell 2001). FORM_NOT_ABSORBED therefore fits derivative-only or oxidized products. Derivatives do have small newer trials (Boghosian 2026), so present that code gently. V3's 'turned orange' check and 'opaque, airtight packaging' are common advice, but I found no independent source this session, so both stay out of person-facing text. Concentration needs a % unit: if one is added, set dose_min 10 (studied L-ascorbic acid serums ran 10 to 15%; Al-Niaimi 2017 says above 8% is needed and above 20% adds nothing) and add DOSE_BELOW_MIN. kind=practice because there is no topical-product kind; if the engine only applies FORM_NOT_ABSORBED to kind=supplement, this row needs an exception. Cost $30 (V3 had $60) is an estimate: budget serums are about $15 a month, premium ones $60 to 90. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7113,6 +7315,11 @@
           <t>Who suggested a retinoid and an acid on the same nights?</t>
         </is>
       </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -7268,6 +7475,11 @@
           <t>Where did the idea of two exfoliants come from?</t>
         </is>
       </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -7423,6 +7635,11 @@
           <t>How did a second hyaluronic serum end up on your shelf?</t>
         </is>
       </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -7591,6 +7808,11 @@
           <t>V3 graded B; regraded C. The only pooled data are 3 small trials in older adults with insomnia, moderate-to-high risk of bias, GRADE low to very low (Mah 2021). The one independent trial in younger adults (Schuster 2025, university-funded) found a small effect (d 0.2, p 0.049) with null secondary outcomes, and its capsules also carried about 1.5 g glycine. Arab 2023 calls the trial evidence inconsistent. V3's rule 'oxide = form not absorbed' is contradicted: two of the three pooled trials used magnesium oxide (500 and 729 mg elemental) and drove the positive result. Apply FORM_NOT_ABSORBED to sprays, oils and bath flakes only (Grober 2017). The threonate sleep trial is brand-funded (AIDP authors; Magtein supplied by Threotech) and 1 g of threonate gives only about 75 mg elemental, below dose_min. dose_min 250 mg elemental = lowest dose with a positive result (Schuster, bisglycinate before bed); Rawji 2024 notes the two negative trials used 100 to 250 mg. The 'low intake responds best' idea is exploratory only, so evidence_requires stays none. Cramps not graded here. NIH ODS magnesium fact sheet returned HTTP 403, so the kidney and medication safety rows rest on well-known label warnings. Cost is an estimate.</t>
         </is>
       </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -7755,6 +7977,11 @@
           <t>V3's 7 and 8 minute figures confirmed (Ferracioli-Oda 2013: 19 RCTs, 1,683 people). V3's line 'more than 1 mg adds grogginess, not effect' is not supported: pooled effects rise with dose up to about 4 mg (Cruz-Sanabria 2024) and higher doses gave larger total-sleep gains (Ferracioli-Oda). The defensible 'less is more' line is that over 5 mg adds nothing measurable (Cochrane jet lag review; Cruz-Sanabria). AASM 2017 suggests clinicians not use melatonin for chronic insomnia (weak, very low quality, based on 2 mg prolonged-release in over-55s); the summary reflects this. Tier B because the effect is consistent but small and mostly measured in people with sleep disorders; the jet lag evidence in healthy travellers is stronger. dose_min 0.1 mg = lowest dose that improved sleep (Zhdanova 2001, insomniacs over 50; 0.3 mg restored normal night levels; normal sleepers unaffected); 0.5 mg works for jet lag. UNUSED left off because occasional travel use is a normal pattern. Cadence set to daily, though many people use it only some nights. Erland 2017 (supplement content survey) not opened; NCCIH page summarizes it. Cost is an estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -7915,6 +8142,11 @@
       <c r="AJ44" s="3" t="inlineStr">
         <is>
           <t>V3 graded B; regraded C, which reflects indirect evidence. No independent trials of blended sleep gummies were found. The working ingredient is melatonin (tier B on its own), but gummy doses are unreliable (Cohen 2023: 22 of 25 mislabeled, 74% to 347% of label, one product with no melatonin but 31 mg CBD). Valerian, common in blends, got a weak recommendation against for insomnia from AASM 2017; the other herbs were not graded here. The router could lift this to melatonin's tier only when a melatonin dose is confirmed; a melatonin-free gummy should route with herb blends (C or D). The 'third of the price' line rests on my cost estimates (about 18 vs 5 USD a month), not a source. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8079,6 +8311,11 @@
       <c r="AJ45" s="3" t="inlineStr">
         <is>
           <t>Area kept as sleep for this batch, but stress is at least as common a reason to buy it (also_serves mind). If a reviewer moves it to mind, the stress evidence grades similarly (Akhgarjand 2022: 12 RCTs, 1,002 adults, low certainty). Tier B with caveats: all five pooled sleep trials ran in India; in the two KSM-66 trials I checked (Langade 2019, Salve 2019) the extract was supplied by its maker (Ixoreal) with no funding statement, the other two KSM-66 trials (Kelgane 2020, Langade 2021) were not checked, and the Shoden trial was sponsored by its maker (Arjuna). No trial declared brand funding outright, so it is not N, but independent replication outside India is missing. Cheah 2021 rated the overall sleep evidence moderate certainty. Sensoril has no trial in the sleep meta-analysis. dose_min 250 mg applies to KSM-66 (Salve 2019); Shoden worked at 120 mg, so the floor depends on the extract; plain root powder was not studied. V3's 6 to 8 week framing was roughly right; its liver and thyroid flags are confirmed. Safety sources: LiverTox (captcha) and NIH ODS (HTTP 403) could not be opened, so the liver rows rest on Bjornsson 2020 and Philips 2023, the thyroid row on Sharma 2018, and the pregnancy row on standard label warnings. Regulatory context, not cited as evidence: Denmark banned it in supplements in 2023 and the Dutch RIVM advised against it in 2024 (NutraIngredients timeline, July 2026). Cost is an estimate.</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -8232,6 +8469,11 @@
           <t>Where did you first hear about mouth tape?</t>
         </is>
       </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -8384,6 +8626,11 @@
       <c r="AJ47" s="3" t="inlineStr">
         <is>
           <t>Product-specific evidence is brand-funded only (Moyen 2024: nine of ten authors are Eight Sleep staff, fixed off-on-off order, no randomization, deep and REM gains only in sex and time-of-night subgroups), which alone would be N. The C rests on Herberger 2024 (randomized, blinded crossover, one night per mattress, +7.5 min deep sleep, about 2 bpm lower heart rate), whose co-author is affiliated with Technogel, the mattress material maker, plus a solid temperature mechanism (Okamoto-Mizuno 2012). A reviewer could fairly choose N. No independent trial of an active cooling pad was found; the Sleepme hot-flash result is a company press release. V3 said the only studies were company-run; that holds for the product. V3's 50 USD a month is too low: Pod 5 hardware runs about 2,849 to 2,999 USD plus Autopilot at 199 to 399 USD a year (third-party pricing pages, searched 2026-10-20), about 135 USD a month over 24 months. Simpler pads cost much less.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8536,6 +8783,11 @@
           <t>V3 graded A from one cohort; regraded B, since the brief's A needs meta-analyses or several RCTs in healthy adults. Evidence: large observational cohorts (Windred 2024: 60,977 people, mean age 63, so not the 22 to 35 group; it measured overall sleep regularity, not wake time alone), a systematic review of mostly observational studies (Chaput 2020, very low to moderate certainty), an expert consensus (Sletten 2023, National Sleep Foundation), one small controlled trial in students (Manber 1996; the abstract does not say whether groups were randomized), and stimulus control, which includes waking at the same time daily, for chronic insomnia (Edinger 2021, conditional, low-quality evidence). No trial isolates wake time alone in healthy adults. V3's '60,000 people' figure is confirmed (60,977). V3's 'single strongest sleep habit we know of' is not something these sources establish. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -8705,6 +8957,11 @@
           <t>night</t>
         </is>
       </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -8865,6 +9122,11 @@
       <c r="AJ50" s="3" t="inlineStr">
         <is>
           <t>V3 graded C ('small trials versus screens favour paper'); regraded B because two randomized studies agree, though both are short. Finucane 2021 is large (991 randomized) but one week long, unblinded, with a single-item self-reported outcome and more dropouts among readers; e-readers were not excluded and paper was not required. Its secondary sleep-disturbance gain was small. Chang 2015 (12 people, inpatient) compared a printed book with a tablet at full brightness for 4 hours, not with no reading. So the support is for reading in general and for print over bright screens; paper versus e-ink has not been tested. Cost set to 0 because the habit is free; books are optional. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9017,6 +9279,11 @@
           <t>V3 framed it only as harmful (B, social jet lag) and left the goal blank. The evidence conflicts, so C: catch-up looked protective in a Swedish cohort (Akerstedt 2019, self-reported sleep, under-65s only) and in observational studies pooled by Chaput 2020, and the National Sleep Foundation panel endorsed catch-up when weekday sleep is short (Sletten 2023). Against that, device-measured UK Biobank data found no link with mortality or cardiovascular disease (Chaput 2024; per the Gao 2024 editorial, one sensitivity analysis hinted at higher mortality at 2 h or more), and a randomized lab study found weekend recovery delayed the body clock and did not reverse metabolic effects (Depner 2019). Taylor 2008 and Wittmann 2006 could not be opened (no abstract available), so V3's Sunday-night circadian claim rests on Depner here.</t>
         </is>
       </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -9171,6 +9438,11 @@
           <t>Tier C, not B. Wang 2020 (BMC Psychiatry, 19 RCTs, 1832 women with sleep problems): pooled SMD -0.33 overall, PSQI SMD -0.54 across 16 RCTs, but ISI (insomnia) null in 3 RCTs and null in breast-cancer and peri/postmenopausal subgroups. Only women, mostly clinical subgroups, and these were yoga programmes, not specifically bedtime stretching. I found no trial of bedtime stretching in healthy young adults. Free, so no UNUSED. Possible future overlap with wind-down-practices (not added; existing groups can't take new members in this file). V3 note matched roughly.</t>
         </is>
       </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -9331,6 +9603,11 @@
       <c r="AJ53" s="3" t="inlineStr">
         <is>
           <t>Tier C: a single pragmatic RCT (Buijze 2016, PLoS One, n=3018 Dutch workers, opened full text): sickness absence IRR 0.71 at 90 days, illness days unchanged, no difference between 30, 60 and 90 s. Unblinded, all self-report, 20% attrition. Energy was not measured formally; authors only report it as the most common perceived benefit. Cain 2025 meta-analysis (11 studies, mostly baths, only 1 shower) found stress lower at 12 h and an acute inflammation spike, and cites the Buijze sick-day result narratively. Safety row: Buijze excluded people with serious cardiac comorbidity; cold shock is better described for immersion (Shattock 2012) than for showers, so I set clinician-first rather than never-suggest. Free, so no UNUSED. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9497,6 +9774,11 @@
       <c r="AJ54" s="3" t="inlineStr">
         <is>
           <t>Structured like a training row: A for the exercise when it happens (WHO 2020 guidelines, Bull et al., opened abstract: 150-300 min/week moderate plus muscle strengthening), requires trains. tier_otherwise C from Romeo 2019 JMIR (9 RCTs, 1740 adults, objective activity): apps produced a nonsignificant +477 steps/day (P=.19); short programmes under 3 months did better. dose_min 150 min is per week (WHO), not per day; the unit list has no min/week. Price: Apple Fitness+ $9.99/month or $79.99/year (apple.com, opened). Peloton's pricing page rendered $0 (display error), and Ladder wasn't opened, so 15 is an estimate across the three. V3 said B; the 'outlive the habit' line isn't tested for fitness apps specifically (DellaVigna 2006 is gyms). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9645,6 +9927,11 @@
           <t>Tier B: Villinger 2019 Obes Rev meta-analysis (41 studies, 27 RCTs, 6348 people): g=0.19 for nutrition behaviours, g=0.30 for obesity indices; commercial vs research app made no difference. Effects are small and the premium tier specifically isn't tested; I wrote the free-tier line from my own knowledge that MyFitnessPal's free tier logs food (not from an opened source) so Veer may want to check. Kept clear_when to UNUSED only so a used app is protected. Safety: Simpson &amp; Mazzeo 2017 (n=493 students, cross-sectional) linked calorie trackers with more eating concern and restraint; Hahn 2021 RCT (200 low-risk undergraduate women, 1 month MyFitnessPal) found no change in eating disorder risk. So the risk sits with people with an eating disorder history; clinician-first. Price: MyFitnessPal Premium $19.99/month or $79.99/year (myfitnesspal.com/premium, opened); annual works out near $7/month. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -9808,6 +10095,11 @@
           <t>What got you a second meditation or sleep app?</t>
         </is>
       </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -9968,6 +10260,11 @@
       <c r="AJ57" s="3" t="inlineStr">
         <is>
           <t>Tier C: Ferreira 2023 J Funct Morphol Kinesiol systematic review (opened full text, no funding, no COI): 11 studies, 281 mostly young active men, 10 of 11 at moderate risk of bias. Short-term ROM and stiffness gains; no change in lactate or perceived exertion; power, agility and balance null or worse. Long-term effects unknown, and soreness results weren't pooled. Safety row from the review's caution list (DVT, clotting disorders); it also lists pregnancy, pacemakers, recent fractures, which I didn't add as rows. Price: Theragun Prime lists about $299 (TechRadar via search, Therabody page 404'd), spread over 24 months = about $12. Foam-roller swap is my suggestion; not tested head to head here.</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10128,6 +10425,11 @@
           <t>Tier C: Maia 2024 Biol Sport meta-analysis (opened full text, public grant funding, no COI): 17 studies, 319 athletes and healthy adults. Soreness g=0.49 at 0-2 h and 0.37 at 96 h, nonsignificant at 24-72 h; muscle function trivial and nonsignificant; creatine kinase unclear; lactate and heart rate unaffected. Authors call the evidence preliminary. No safety row added: pneumatic compression is usually avoided with a suspected clot, but neither the review nor the Hyperice page I opened says so, so I left it out; worth Veer adding with a source. Price: Normatec 3 Legs $899 (hyperice.com, opened), /24 = about $37; Normatec Go $379, Elite Legs $1,099. Legs-up swap is my suggestion, untested. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -10284,6 +10586,11 @@
       <c r="AJ59" s="3" t="inlineStr">
         <is>
           <t>Tier C for the outcome 22-35s buy it for. Rubio-Arias 2021 Arch Phys Med Rehabil (23 studies, 884 overweight or obese, mostly women; abstract): fat mass -1.07 kg, called not clinically significant; also lower systolic BP (-7 mmHg) and better leg strength, which is a real but separate effect. Reis-Silva 2023 Front Physiol (8 RCTs, over-60s; abstract): no body-composition change. Chen 2026 BMC Musculoskelet Disord (14 RCTs, 1447 adults 60-93, 96% women; opened full text): small BMD gains at hip sub-sites, high GRADE; doesn't carry to young adults. Chen notes high-intensity vibration may cause dizziness and falls; no safety row added. Price is an estimate: home plates sell for roughly $100 to $300, spread over 24 months.</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10437,6 +10744,11 @@
           <t>Where did you first see the jaw exerciser?</t>
         </is>
       </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -10604,6 +10916,11 @@
       <c r="AM61" t="inlineStr">
         <is>
           <t>night</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10753,6 +11070,11 @@
           <t>Do you remember how this subscription started?</t>
         </is>
       </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -10899,6 +11221,11 @@
           <t>Tier B, not A: Greco 2023 (Sleep, ERC-funded, no conflicts) ran two counterbalanced within-subject experiments in 18-35s (n=89 and 33); mask vs no/holed mask gave small gains in word-pair learning (d about 0.19) and PVT reaction time (d 0.16), but self-rated sleepiness and Dreem-measured sleep stages did not differ, and allocation was counterbalanced, not described as randomised. Karimi 2021 meta (35 studies, mostly ICU patients) found masks and/or earplugs improved sleep quality; eye-mask-only studies mostly positive but heterogeneous, no GRADE. Hu 2010: 14 healthy volunteers in recorded ICU noise and 100 lux light; masks plus earplugs gave more REM and fewer arousals (combined, so mask effect not isolated). Consistent direction, small and narrow samples, hence B. Price: estimate, a $10-20 mask lasting about a year. wearable_sees partial: wearables can see sleep but not the mask.</t>
         </is>
       </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -11049,6 +11376,11 @@
           <t>Tier B kept from V3 but scoped to noisy rooms. Hu 2010 (Crit Care, n=14 healthy volunteers, randomised night order, about 66 dB(A) playback): plugs plus mask raised REM 9.3% to 12.9%, cut arousal index 15.1 to 12.2, better perceived sleep; total sleep time and sleep latency not significant; plugs and mask combined. Karimi 2021 meta: earplug-only ICU studies mixed (Litton 2017, Baghaie Lakeh 2018 null). No good trial in quiet bedrooms or of healthy people at home, so evidence_for is limited to noise. I did not find a review of earplugs in healthy adults at home. Price: estimate, foam plugs about $0.10-0.20 a pair, reusable silicone/Loop-style a one-off $25-35. In noise-masking group with white noise (show-together, not redundancy, so no OVERLAP clear code here). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -11203,6 +11535,11 @@
           <t>Riedy 2021 (Sleep Med Rev 55:101385, PROSPERO-registered, 38 studies): GRADE very low for continuous noise improving sleep; findings ranged from improved to disrupted; authors warn about possible harm to sleep and hearing and call for objective measures. Read abstract via Europe PMC only (PubMed blocked). C not D because there are many human studies, just inconsistent. The V3 line about masking real noise is plausible but I did not find a trial isolating it. Price: estimate, $30-60 machine over 24 months, apps often free. OVERLAP code is there for people who use both earplugs and a machine; Veer may prefer to drop it. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -11371,6 +11708,11 @@
       <c r="AJ66" s="3" t="inlineStr">
         <is>
           <t>Thompson 2014 (Eur J Appl Physiol 114:1049, n=8 people who find waking hard, random-order crossover): dawn light in last 30 min raised self-rated sleep quality and alertness, more additions and faster reaction time; cycling time trial not significant. Abstract only. Golden 2005 meta: dawn simulation for seasonal depression effect size 0.73 from 5 studies (abstract) - a different outcome, noted for context only. Search also surfaced Gabel 2013 (n=17, sleep restriction) which I did not open. Small and few, hence C. Price: hatch.co Restore 3 page lists $169.99 (opened 2026-10-22) = about $7/month over 24 months; Hatch+ subscription price not shown on page, so 8 is an estimate. moments includes night because Hatch-type devices also run wind-down sounds/light.</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11523,6 +11865,11 @@
           <t>Singh 2023 Cochrane CD013244 (17 trials total; 6 RCTs, 148 people, for sleep): 3 positive, 3 null, no meta-analysis possible, very low certainty. Cochrane full text returned 403; read abstract via Europe PMC. Reported adverse effects included headache, discomfort and lower mood. C (studies disagree) rather than D. Note the V3 claim that the review 'pooled all trials and found little effect' was inaccurate: it could not pool sleep data. The cheaper alternative leans on general evening-light evidence (existing chang-2015-ereader-sleep) rather than a glasses source. Price: estimate, $20-60 glasses over 24 months.</t>
         </is>
       </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -11669,6 +12016,11 @@
           <t>Camacho 2016 (Pulm Med, 14 studies, 294 patients, mostly small non-randomised, people with snoring/OSA): snore index change not significant (-2.5/hr overall; strips -3.1/hr), AHI unchanged, lowest O2 sat +1% (abstract and results disagree on significance). One included study found bed partners reported mildly less snoring. Improved nasal airflow is accepted. A consumer site claimed two GSK-sponsored RCTs found no sleep-quality benefit vs placebo strips; I could not verify, not used. C rather than D because human trials exist with mixed subjective vs objective results. Price: estimate, about $0.40-0.50 per strip nightly. Safety row added for sleep apnea. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -11828,6 +12180,11 @@
           <t>What first sold you on a silk pillowcase?</t>
         </is>
       </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -11982,6 +12339,11 @@
           <t>Downgraded V3 B to C; Veer may want B scoped to people with insomnia plus a mental health condition. Ekholm 2020 (JCSM, n=120 psychiatric outpatients with insomnia, 4 weeks, blinded raters, Region Stockholm funded, no COI): ISI response 59% vs 5%, remission 42% vs 4%; actigraphy total sleep time and WASO unchanged; blinding of participants weak (weight is obvious). Zhao 2024 meta (8 RCTs, 426 psychiatric patients, about half high risk of bias): pooled insomnia MD -1.92 ISI, p=0.06 (significant only after dropping one study); anxiety small benefit. No trial in healthy 22-35s found. Self-reported benefit outruns objective change. Price: estimate, $60-150 over 24 months. Safety row for babies/children (CPSC). dose_unit left blank because kg is not an allowed unit.</t>
         </is>
       </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -12146,6 +12508,11 @@
       <c r="AJ71" s="3" t="inlineStr">
         <is>
           <t>B: Pjrek 2020 (Psychother Psychosom, 19 RCTs vs dim light or sham ion generators): depression SMD -0.37, response RR 1.42, no publication bias, but moderate heterogeneity and moderate-high risk of bias (abstract). Golden 2005 meta: bright light ES 0.84 for seasonal depression, 0.53 non-seasonal (abstract). Not A: population is people with SAD, not healthy adults; evidence_requires has no 'seasonal low mood' option, so it is in evidence_for. For people without winter low mood the benefit is unproven; the engine may want a seasonal flag. Dose: 20-30 min at 10,000 lux each morning is the standard clinical protocol, but I did not open a dosing source, so dose_min is blank. Safety: Takeshima 2020 meta (6 RCTs, bipolar depression) found switch rate 4.7%, similar to control, mostly with mood stabilisers; authors suspect higher risk without one - kept clinician-first for bipolar. Price: estimate, $40-100 box over 24 months. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -12320,6 +12687,11 @@
       <c r="AN72" t="n">
         <v>2</v>
       </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -12489,6 +12861,11 @@
           <t>evening</t>
         </is>
       </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -12643,6 +13020,11 @@
           <t>Tier C, kept from V3. Khalesi 2019 (45 trials, healthy adults) found transient colonisation and some support for stool consistency, bowel movements and immune markers; no persistent microbiome change. Rauch 2022 found no improvement in gut symptoms or permeability in healthy or active adults. Strain-specific evidence (e.g. antibiotic-associated diarrhoea) does not transfer to a generic daily capsule; I could not open the AGA 2020 guideline full text (403), so it is not cited. If someone was prescribed a strain for a diagnosed condition, that falls outside this row. Price: $30/month is the V3 estimate, not checked against a pricing page. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -12805,6 +13187,11 @@
           <t>Tier C rather than D: Cochrane 2024 (34 RCTs) gives prevention RR 0.93 (0.85 to 1.01), low certainty, so a small effect is not ruled out. Treatment use (lozenges once a cold starts) may cut about 2.4 days, low certainty, high heterogeneity; Hemila has published critiques of this review arguing the lozenge effect is understated (not opened, titles only). V3's 'does nothing when not low' is roughly right for prevention. Upper limit 40 mg/day is set to avoid copper deficiency (LPI). Most daily multivitamins already carry zinc, hence the overlap. Price is the V3 estimate.</t>
         </is>
       </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -12967,6 +13354,11 @@
       <c r="AJ76" s="3" t="inlineStr">
         <is>
           <t>Tier A for the narrow claim only: Cochrane 2013, 31 comparisons, 9,745 episodes; duration down 8% (3 to 12%) in adults, 14% in children. Incidence RR 0.97 in the general community; RR 0.48 in marathon runners, skiers and soldiers under heavy physical stress (could justify a stronger keep for heavy endurance trainers). Starting vitamin C once a cold begins showed no consistent effect, so the benefit needs regular daily use. dose_min 200 mg is the review's inclusion floor. LPI: full absorption up to 200 mg per dose, plasma plateaus at 200 to 400 mg/day, so 1,000 mg adds little. The effect is small; the A is about how solid the evidence is, not its size. Price is the V3 estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -13129,6 +13521,11 @@
           <t>Tier A with deficiency: Houston 2018 BMJ Open, 18 RCTs, fatigue SMD -0.38 (4 trials, 714) in iron-deficient non-anaemic adults; no gain in measured VO2max. Treating iron-deficiency anaemia is standard care. tier_otherwise D: I found no trial benefit in iron-replete adults, and LPI advises against iron without evaluation for people not at risk and for haemochromatosis. dose_min 60 mg is taken from Stoffel 2017 (60 mg morning doses on alternate days absorbed best in iron-depleted women); real dosing belongs to the clinician, so I did not add DOSE_BELOW_MIN. LPI upper limit 45 mg/day applies to unsupervised use. At-risk groups per LPI: menstruating women, endurance athletes, vegetarians and vegans, frequent blood donors. Cadence is daily in the table but alternate-day is common. Price is the V3 estimate.</t>
         </is>
       </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -13297,6 +13694,11 @@
           <t>V3 graded N; that was wrong. For vegans the need is well established: Niklewicz 2024 meta-analysis shows lower B12 and higher homocysteine in vegans, with supplement users better on every marker; Del Bo 2019 RCT (40 vegans/vegetarians, marginal deficiency) restored levels with about 50 mcg/day. Graded B, not A, because the RCT evidence is small and status-based; correcting deficiency itself is standard care. I used low_intake (vegan/low animal food); people with a measured low level, metformin users and acid-reducer users are also at risk (LPI) and should also be protected; the engine may want deficiency too. tier_otherwise D: Markun 2021 (16 RCTs, 6,276) found no effect on cognition or depression without overt deficiency; fatigue was measured in only one trial, so 'no energy benefit' is inferred, not proven. LPI: only 1 to 2% of large oral doses absorbed, no upper limit. Price is the V3 estimate.</t>
         </is>
       </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -13459,6 +13861,11 @@
           <t>V3 graded B on knee arthritis. The arthritis evidence is real (Zeng 2021: 15 RCTs, 1,621; NCCIH calls it positive but needing higher quality), but it comes from older adults with osteoarthritis, not the 22 to 35 audience, and many trials carry bias risk. For what this audience buys it for (soreness, general inflammation), Fang 2021 pooled small trials with modest gains in soreness and CK; earlier trials were inconsistent. So C for evidence_for. If someone has diagnosed knee arthritis, B would fit; no evidence_requires code covers that. FORM_NOT_ABSORBED: Anand 2007 and LPI on low bioavailability; plain powder capsules are the target. Safety: DILIN 2023 liver-injury cases (often with piperine), NCCIH says highly bioavailable products have been linked to liver damage, LPI notes antiplatelet effects. V3's gallstone caution: LPI notes increased gallbladder contraction only; no gallstone source opened, so not added. Price is the V3 estimate.</t>
         </is>
       </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -13623,6 +14030,11 @@
           <t>Tier A: Jovanovski 2018 (28 RCTs, 1,924) LDL -0.33 mmol/L at a median 10.2 g/day, moderate-quality GRADE, in people with or without high cholesterol; van der Schoot 2022 (16 RCTs, 1,251, chronic constipation) responder rate 66% vs 41%, psyllium strongest, best above 10 g/day for 4+ weeks. evidence_requires low_intake as Veer asked, since the regularity benefit was shown in people with constipation. tier_otherwise B rather than lower because the LDL effect held regardless of baseline cholesterol, which suggests it does not depend on a low-fibre diet. dose_min 10 g comes from both reviews; many people take one teaspoon (about 5 g), which DOSE_BELOW_MIN would flag. The suggestion there should be 'a little more', not 'let it go'. More wind is the common side effect. No safety row: I did not open a source on spacing it from medicines. Price $12 is an estimate (V3 said $10).</t>
         </is>
       </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -13789,6 +14201,11 @@
       <c r="AJ81" s="3" t="inlineStr">
         <is>
           <t>V3 graded B; I matched the reviewed omega-3-fish-oil row (C, low_intake, otherwise D, dose_min 840 mg EPA+DHA from VITAL), since krill's benefit is its omega-3. Kim 2020 network meta-analysis (64 RCTs): no difference from fish oil on lipids; effect tracks n-3 dose. Laslett 2024 JAMA: 2 g/day krill oil did not help knee osteoarthritis pain. Label checked: NOW Neptune Krill 1000 mg = 120 EPA + 70 DHA (190 mg) per softgel, so one capsule is about a quarter of the VITAL dose; MegaRed's site did not show EPA/DHA in text. Krill bioavailability claims (e.g. Ramprasath 2013, omega-3 index) exist but co-authors appear industry-linked; not cited. No krill-specific safety row: fish oil's bleeding and blood-thinner rows likely apply, but I opened no krill source. Price $30 is the V3 estimate.</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13949,6 +14366,11 @@
           <t>Tier C. Energy: Tsai 2022 (13 RCTs, 1,126) found reduced fatigue including healthy participants, but Deng 2025 (24 trials, healthy adults) found small, unstable effects on performance, very low to low certainty, with fatigue only suggestive. So V3's 'does nothing for energy' overstates it; 'small and inconsistent' is fair. Statin myalgia: Qu 2018 positive (12 RCTs), Kennedy 2020 null (7 RCTs), Kovacic 2025 small positive (7 RCTs); NCCIH says overall evidence does not support it. Someone on a statin who feels it helps should be handled gently. Warfarin interaction per NCCIH (safety row). Price $25 is the V3 estimate.</t>
         </is>
       </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -14106,6 +14528,11 @@
       <c r="AK83" t="inlineStr">
         <is>
           <t>Who first suggested evening primrose oil?</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -14258,6 +14685,11 @@
           <t>Tier B for chronic pain only: Vickers 2018 IPD meta-analysis (39 high-quality trials, 20,827 patients) beat sham (~0.2 SD) and no acupuncture (~0.5 SD); NCCIH 2022 agrees, cites ACP 2017 and ACR 2019 guidelines. Effect over sham is small, so B not A. Area set to mind because most 22-35 users go for stress/calm; for stress, sleep or general wellness without pain I did not open trials and V3 called sleep trials weak, so treat non-pain use as C/D in conversation (human_question separates the two). B keep applies on paper to everyone; if the engine can key on purpose, only protect for pain. Safety: NCCIH says serious harms are rare and tied to non-sterile needles or untrained practitioners; no specific condition row sourced (bleeding-risk caution is common practice but I did not open a source, so no row). Cost: estimate, about $100-130 a session, roughly one a week or less; no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -14408,6 +14840,11 @@
           <t>Graded C on purpose. Rubinstein 2019 BMJ (47 RCTs, 9,211 adults): SMT similar to other recommended therapies for chronic LBP (moderate quality); two authors were chiropractors with chiropractic-association grants (flagged; brand_funded set no because not a product brand). Eklund 2018 PLoS One pragmatic RCT (n=328, no competing interests): maintenance care gave 12.8 fewer bothersome-pain days over a year vs symptom-guided care, but only in people with recurrent/persistent LBP who responded well to initial care, at ~1.7 more visits. For pain-free 'maintenance' I found no trials (effectively N). V3's claim that maintenance has no evidence was too strong for people with recurring pain, so I did not grade D/N; C lets their values decide and the question surfaces whether pain recurs. If Veer prefers, this could be B with an evidence_requires value for 'recurring back pain' if one is ever added. Cost: estimate ~$65 a visit, about monthly; no pricing page opened. No safety row: Rubinstein found mostly mild transient musculoskeletal events; I did not open sources on neck manipulation and artery injury.</t>
         </is>
       </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -14554,6 +14991,11 @@
           <t>never_clear yes per brief: prescribing care is the clinician's call, Distill only adds safety framing. Tier A applies to the GLP-1 part: Shi 2024 Lancet NMA (republished after 2022 retraction; 132 RCTs, 48,209 adults; independent funding) GLP-1 RAs ~5.8% extra weight loss, semaglutide ~11.4%; STEP 1 (Novo-funded) -14.9% vs -2.4%. TRT: Endocrine Society 2018 says diagnose only with symptoms plus repeatedly low morning T, and lists contraindications (planning fertility, prostate/breast cancer, high hematocrit, untreated severe OSA, uncontrolled heart failure, recent MI/stroke). Peptides (BPC-157, TB-500, CJC-1295, ipamorelin etc.): FDA compounding page (current 2026-04-22) lists them as withdrawn nominations or Category 2 with little or no human safety data: effectively tier N/D. FDA GLP-1 page (current 2026-10-01): compounded semaglutide/tirzepatide not FDA-reviewed, dosing-error hospitalisations, salt forms unlawful, counterfeit risk, 990+ and 730+ adverse event reports. Cadence weekly = typical weekly injection; moments any. Cost $300 is V3 estimate (telehealth GLP-1 programmes and TRT clinics vary roughly $150-1,300); no pricing page opened. area eat chosen since GLP-1 weight programmes dominate in this age group; TRT is move/energy. wearable_sees partial: resting HR and weight trends only. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -14702,6 +15144,11 @@
       <c r="AJ87" s="3" t="inlineStr">
         <is>
           <t>Tier A: Trauer 2015 Ann Intern Med meta-analysis (20 RCTs, 1,162 adults with chronic insomnia, no funding): SOL -19 min, WASO -26 min, SE +9.9%, sustained; TST only +7.6 min (CI crosses 0). AASM 2021 guideline: STRONG recommendation for multicomponent CBT-I. Population is people with chronic insomnia, not all healthy adults, but evidence_for names that group. never_clear yes because a trained CBT-I clinician is sleep care; caution: 'sleep coach' is unregulated and many coaches do not deliver CBT-I (stimulus control plus sleep restriction plus cognitive work). Name says 'trained coach' to signal that; if Veer wants untrained sleep coaching as a separate row it should be C/N and clearable. I left fits_instead empty to avoid steering people away from clinician care; a possible line is the free VA 'CBT-i Coach' app, but I did not open a source for it. dose_typical from common practice (Trauer required &gt;=3 components but I did not read session counts in the abstract), so dose_min left blank. Cost $200/month is V3 estimate; no pricing page opened. wearable_sees partial: bed and wake times are visible. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -14850,6 +15297,11 @@
           <t>Tier B: Mitchell 2017 J Acad Nutr Diet systematic review (26 RCTs, 5,500 adults) favoured dietitian consults for glycaemic control (4/4), dietary change (4/4) and anthropometry; not lipids or BP. Williams 2019 meta-analysis (5 RCTs, n=1,598): -1.03 kg extra weight, risk of bias unclear to high, so B not A. Evidence is for registered dietitians; 'nutritionist' is not a protected title in most US states, so a non-credentialed nutritionist or health coach is closer to C/N. Not never_clear (not prescribing care) but if it is for diabetes, kidney disease or an eating disorder it is part of medical care: the engine should not suggest letting go then (no safety row because I did not open a source specific to that). Cost: estimate ~$150 for a monthly follow-up visit (V3 had 200); no pricing page opened. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -15004,6 +15456,11 @@
           <t>Tier C (not D) because blood tests are real diagnostics: they do find low iron, B12 or vitamin D and the result can be acted on. But for population benefit: Krogsbøll 2019 Cochrane (17 trials, ~250,000 people) general health checks had little or no effect on total, cancer or CV mortality (high certainty). USPSTF 2021: insufficient evidence for vitamin D screening in adults without symptoms (I statement). No trials of 100+ marker subscription panels themselves; false positives and follow-up testing are a known downside of broad panels but I did not open a source quantifying it. Morning = fasting draw. Price: functionhealth.com/pricing opened: $365/year (shown as $1/day), 160+ tests, twice a year, so ~$30/month. New overlap group self-tests (with CGM and DNA test) added.</t>
         </is>
       </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -15158,6 +15615,11 @@
           <t>Tier C: Makkena 2026 Medicina systematic review (12 studies, PROSPERO-registered, no conflicts): two small RCTs showed some dietary changes when CGM was paired with low-GI education (e.g. -15 g carbs over 8 weeks); low certainty for diet, very low for activity and psychosocial outcomes; standalone benefit not established. Shah 2019 JCEM (153 healthy people, blinded Dexcom G6): median 96% of time in 70-140 mg/dL, mean ~98-99 mg/dL, so post-meal rises are normal (supports V3's 'turns normal rises into worry' point, though anxiety itself was not measured there). V3 graded D; I moved to C because two small RCTs exist. Price: stelo.com opened: $89/month subscription (was $99), 15-day sensors, labelled for adults not on insulin. wearable_sees partial: some wearable apps import CGM data. Safety row: Stelo is not for people on insulin or with problematic lows (from Stelo page).</t>
         </is>
       </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -15317,6 +15779,11 @@
           <t>What got you to order the DNA test?</t>
         </is>
       </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -15472,6 +15939,11 @@
           <t>How did you first hear about hyperbaric sessions?</t>
         </is>
       </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -15635,6 +16107,11 @@
           <t>Where did lymphatic drainage first come up for you?</t>
         </is>
       </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -15790,6 +16267,11 @@
           <t>Who first suggested a colon cleanse?</t>
         </is>
       </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -15956,6 +16438,11 @@
           <t>V3 graded N and said BCAAs 'add nothing' with enough protein. Muscle side holds: Wolfe 2017 (JISSN review; author discloses industry grants and shares in an amino-acid company) found no human evidence that BCAAs alone raise muscle protein synthesis; the two IV infusion studies saw it fall. ISSN 2017 protein stand (Jager) points to whole protein with all essential amino acids at 1.4 to 2.0 g/kg/day and does not recommend BCAAs. Plotkin 2021 (IJSNEM narrative review) is relevant but only its abstract without conclusions was reachable, so not cited. Soreness side is not 'nothing': Salem 2024 (Sports Med Open, 18 RCTs, healthy active people, no funding) pooled lower soreness at 24 to 96 h and lower CK at some time points, with high heterogeneity, publication bias, rare allocation concealment, and an internal participant-count mismatch (331 vs 399). Most trials did not equate total protein intake, so soreness may not beat simply eating more protein. Hence C, not N. Overlap: added to the existing protein-powders group (same job: amino acids for training). Price is my estimate for a 30-serving tub (about $25 to $35); no pricing page opened. NOT_TRAINING fits: sold for training only.</t>
         </is>
       </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -16123,6 +16610,11 @@
           <t>Who put glutamine on your list?</t>
         </is>
       </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -16292,6 +16784,11 @@
       <c r="AK97" t="inlineStr">
         <is>
           <t>Where did you first hear about ZMA?</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -16440,6 +16937,11 @@
           <t>V3 graded N and said fenugreek has 'none on testosterone'; that part is contradicted: Mansoori 2020 (Phytother Res meta-analysis, 4 RCTs) found a significant rise in total testosterone. I only read the abstract, which gives no effect size or funding; fenugreek trials are commonly run with branded extracts, so check before upgrading. Tribulus: Qureshi 2014 systematic review (11 studies) found it ineffective in humans except within combined supplements. D-AA: Willoughby &amp; Leutholtz 2013 (3 g, 28 days, trained men) and Melville 2017 (6 g, 12 weeks, 22 trained men aged 18 to 36) both found no change in testosterone or training outcomes. Clemesha 2020 (50 products): 61.5% of 109 components had no testosterone data, 10.1% had data showing a decrease, and 13 products exceeded the UL for zinc, B3 or magnesium. Tier C because the ingredients disagree (fenugreek positive, tribulus and D-AA null) and no blend has been tested. No dose fields: blends vary too much. fits_instead left empty: I found no source for a lifestyle swap that raises testosterone in healthy young men. Price: V3's $40, my estimate; no pricing page opened. Area move because the purchase is about training and physique. Name and short_name avoid 'booster' because 'boost' is on the banned word list. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -16598,6 +17100,11 @@
           <t>V3 graded N; I graded C because caffeine and green tea do have trial data, just small effects. Jeukendrup &amp; Randell 2011 (Obes Rev review): only caffeine and green tea have data backing fat-metabolism effects; evidence lacking for carnitine, CLA, forskolin, chromium and others. Tabrizi 2019 (13 RCTs, 606 people, I2 above 90%): caffeine might promote weight, BMI and fat reduction; very heterogeneous. Jurgens 2012 Cochrane: green tea outside Japan, -0.04 kg over 12 weeks, not meaningful. Batsis 2021 (Obesity, 315 RCTs of supplements and alternative therapies): only 52 low-risk and sufficient, of which 16 showed weight differences of 0.3 to 4.93 kg. Geller 2015 (NEJM, ED surveillance 2004 to 2013, HHS-funded): weight-loss or energy products caused 71.8% of supplement adverse events with palpitations, chest pain or tachycardia, 58% in people aged 20 to 34. V3 said they 'disturb your sleep': true by way of caffeine, but I did not open a fat-burner sleep study, so the summary leaves it out; added to the evening-stimulants overlap group instead. Coffee swap is my inference from shared caffeine. Under-18 safety row not added because I did not open a pediatric source this round (AAP 2011 exists in the table for energy drinks; Ishan may want it extended). Price: V3's $40, my estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -16756,6 +17263,11 @@
           <t>V3 C, kept. Pomeroy 2020 (Nutrients systematic review, 37 studies, healthy adults 18 to 35): 73% low quality; only tyrosine or caffeine supported, mainly under sleep loss. Camfield 2014 (Nutr Rev meta-analysis, 11 RCTs): caffeine plus L-theanine gave moderate gains in alertness and attention switching within 2 h, driven more by caffeine dose. Alpha-GPC: Marcus 2017 (JISSN, 48 college men, 7 days) found no change in psychomotor vigilance and a jump-power gain at 250 mg, not 500 mg; it lowered TSH at 500 mg. Lee 2021 (JAMA Netw Open, 12 million Koreans over 50, prescribed alpha-GPC): 43% higher 10-year stroke risk, dose-response; observational and older population, so used only for the heart safety row, not the tier. Cohen 2021 (Neurol Clin Pract): 10 cognitive supplements contained 5 unapproved drugs, some undeclared, 75% of quantities inaccurate. Stacks vary widely (some have caffeine; those would also belong in evening-stimulants, not added here since many don't). Price: V3's $60, my estimate; the Onnit page I opened showed no price.</t>
         </is>
       </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -16922,6 +17434,11 @@
           <t>NUANCE: the B holds only for sessions over about an hour or heavy sweating, not any training. The allowed evidence_requires values cannot say 'long or sweaty', so I used 'trains' as the closest and set tier_otherwise C. The engine should read TRAINS here narrowly: a 40-minute lift does not earn the keep, and for short sessions the C (and water) applies. Until the schema can express duration, the OVERLAP lever (electrolytes group, keep-one with electrolytes-lmnt-etc) is the main point of this row: two products doing one job. Sources: Sawka 2007 ACSM stand (abstract only; the numeric sodium advice is paywalled): electrolyte and carbohydrate drinks can beat water 'under certain circumstances', with customised plans because sweat rates vary. Stellingwerff &amp; Cox 2014 (61 RCTs, 679 people): 82% showed carbohydrate improved performance, with gains growing with exercise duration; under about an hour the effect is a mouth-sensing one. Kind is food-drink, so no dose_min; the sibling row electrolytes-lmnt-etc carries the sodium dose (500 to 700 mg/L, ACSM 1996). Safety rows mirror the sibling row's sourced ones (He 2013, NKF), which I did not reopen. Sugar in sports drinks (diabetes) not graded. Price is my estimate: about $45 for a month of an electrolyte mix plus about $15 of sports drinks; no pricing page opened. V3's 'two sources of the same salts and sugar' is fair (mixes like LMNT are sugar-free, so 'sugar' applies only to the sports drink).</t>
         </is>
       </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -17103,6 +17620,11 @@
           <t>morning</t>
         </is>
       </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -17264,6 +17786,11 @@
       <c r="AK103" t="inlineStr">
         <is>
           <t>Who got you onto sea moss?</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -17433,6 +17960,11 @@
           <t>What first put shilajit on your radar?</t>
         </is>
       </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -17593,6 +18125,11 @@
       <c r="AJ105" s="3" t="inlineStr">
         <is>
           <t>Tier C, kept from V3 but for a reason V3 didn't give: in healthy young adults there are now two small RCTs. Docherty 2023 (n=41, 1.8 g/day, product donated by Sempera Organics, no other funding, read full text) found one acute Stroop speed effect, recall slightly worse, no 28-day effect, stress only a trend (p=0.051). Surendran 2025 (n=18 crossover, 3 g extract) found no overall effect; I checked full text: two authors are employed by Three Spirit Drinks (lion's mane drinks), which paid publication fees, so I marked it brand_funded yes. Menon 2025 SR: MMSE +1.17 pooled from one RCT + one pilot in older/dementia groups. Also saw (not cited) Evans 2026 n=10 uncontrolled pilot, no significant change, and a 2026 preprint RCT. Could be argued down to D for healthy adults; I kept C because independent RCTs exist and disagree slightly. Price estimate.</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -17757,6 +18294,11 @@
           <t>Tier C. Shin 2010 SR (full text): 4 RCTs, 131 people, none reported allocation concealment; 3 of 4 showed a benefit on desire/function, cyclists none. Ho 2026 meta of herbal ED supplements (14 RCTs) says maca evidence remains insufficient. Morgado 2024 included 2 Lepidium meyenii testosterone studies and did not list maca among effective boosters (abstract only; I did not see maca-specific numbers, so the summary says 'isn't shown to raise' rather than 'doesn't'). Also saw a 2024 maca physical-performance meta (Huerta Ojeda, animals and humans) but did not open. Price estimate. Put in testosterone-boosters overlap because it's marketed on libido alongside tongkat and shilajit; Veer may prefer to leave it out.</t>
         </is>
       </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -17921,6 +18463,11 @@
           <t>Tier C for trainers, D otherwise. Jones 2016 meta (full text): 5 RCTs, 152 endurance-training adults, URS days rate ratio 0.56, URS episodes 0.62; 4 of 5 trials moderate/high risk of bias. Competing interests: lead author's PhD was partly supported via a project with The Golden Dairy Ltd (colostrum supplier for Neovite); trials used donated product. I marked the meta brand_funded no, but Veer may want to treat it as brand-linked, which would push this toward N. V3 said it helps athletes' gut problems: Aitkenhead 2025 meta of supplements for exercise gut damage found no pooled benefit and clinically trivial changes (abstract doesn't break out colostrum, so I don't claim colostrum failed specifically). Goluch 2026: body fat and lipid results inconsistent. tier_otherwise D because the feed claims (gut lining, skin, immunity in non-athletes) rest on mechanism. dose_min 10 g from the lowest trial dose; popular feed brands appear to serve much less per scoop (I could not open ARMRA's page, 404), so DOSE_BELOW_MIN may often fire; verify a serving size before relying on it. Price is an estimate based on premium feed brands (~$2 to $3 a serving).</t>
         </is>
       </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -18083,6 +18630,11 @@
           <t>Moved from V3 D to C: there are now ~28 randomized human trials, so 'mechanism/animal only' no longer fits; they mostly show target engagement with null or inconsistent outcomes. Yang 2026 NMN meta (15 RCTs): no effect on weight, BMI, fasting glucose, HbA1c, lipids, SBP; DBP slightly lower. Gallagher 2026 SR: 33 human studies, functional outcomes 'heterogeneous and often null'. Gao 2026 NMA: no precursor helps perceived fatigue or sleep; NMN linked to endurance (could be small-study effect). I didn't separately open Yoshino 2021 (V3 hint). Many NR trials are ChromaDex-supported; I didn't audit funding trial by trial, which could argue for a lower tier. 'Longer-life findings come from mice' rests on Gallagher's rodent findings; Gallagher's abstract says rodent improvements, not lifespan explicitly; Veer may soften to 'animal studies'. Price: Tru Niagen 300 mg/day lists $49 (from $39.20 subscribed) on truniagen.com, opened 2026-10-22; NMN products vary, so $45 is a midpoint.</t>
         </is>
       </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -18243,6 +18795,11 @@
           <t>Tier B, but read this: the evidence is in people with raised glucose, T2D, metabolic syndrome or PCOS (Zhao 2023: 20 RCTs n=1,761, FPG -0.52 mmol/L, larger in diabetes; Liu 2025: 12 RCTs n=889, 300 to 1,500 mg/day; Elahi Vahed 2026: 23 RCTs, weight -0.88 kg). For a healthy 25-year-old taking it as 'nature's Ozempic' the tier would be C at best. evidence_requires has no code for 'has a condition' (only none/trains/deficiency/low_intake), so I left it none and tier B, which means it is protected for everyone. Suggest Ishan adds a code like raised_glucose with tier_otherwise C. Interactions are real: Dumitru 2026 review (CYP3A4/2D6/2C9, P-gp, OCT/MATE, additive hypoglycaemia; cyclosporine +34.5% AUC in transplant patients). NCCIH goldenseal page: metformin levels fell ~25% in healthy adults; no pregnancy/breastfeeding. Mostly Chinese trials, quality uneven. dose_min 300 is the lowest dose in Liu's included trials; most trials used 900 to 1,500 mg/day. Price: Thorne Berberine-500, $44 for 30 servings (thorne.com, opened 2026-10-22).</t>
         </is>
       </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -18403,6 +18960,11 @@
       <c r="AJ110" s="3" t="inlineStr">
         <is>
           <t>Moved from V3 N to C: there are many independent RCTs, so N (no independent studies) was wrong. Sun 2026 umbrella (45 meta-analyses): only four high-certainty effects, all small and in narrower groups (waist -0.8 cm; TC in overweight; BP in T2D). Cochrane 2020 (T2D): 3 tiny RCTs, insufficient. Semba 2014 InCHIANTI cohort: dietary resveratrol not associated with mortality, CVD, cancer or inflammation; this is diet-level, not supplement dose. V3 cited a Cochrane review on CVD primary prevention and Berman 2017; I did not find/open either. The 'simpler organisms' line comes from Semba's background statement; no lifespan source opened beyond that. Dose range from Cochrane trials (10 to 1,000 mg) and typical labels; label range not sourced. Price estimate.</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -18567,6 +19129,11 @@
           <t>Tier C, borderline N. Leisegang 2022 meta (full text, no funding, no COI): 5 RCTs n=232, SMD 1.35; 7 of 9 included studies used Physta (Biotropics Malaysia), and Biotropics staff (A. George) co-author several (Chinnappan 2021, Ismail 2012, George 2013). If brand-authored Physta trials count as none, what's left in healthy men is small: Quin 2021 (n=21, not significant) and Chan 2021 (Physta, authorship unclear). In healthy men with normal T, Ismail 2012 and George 2013 found no significant change; Chinnappan 2021 (men 50 to 70 with low baseline T ~190 ng/dL) found a rise. Leitao 2021 (independent, men with androgen deficiency) positive. So 'mixed in healthy men' is accurate. Morgado 2024 rates it possibly effective for healthy and low-T men. No safety row: I did not open a liver or interaction source for tongkat. Price estimate.</t>
         </is>
       </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -18729,6 +19296,11 @@
           <t>Tier C, bordering D for this audience: RCTs exist but are in older adults and mostly null (Nair 2006 NEJM 2-year RCT; Elraiyah 2014 meta, libido p=0.06, low certainty). No trials found in 22 to 35 year olds. He 2025 meta confirms it is hormonally active (raises T and E2, more at &gt;=50 mg). Pregnenolone: search found RCTs only in alcohol and cocaine use disorder (Milivojevic/Sinha lab, titles seen, not opened), nothing in healthy adults, so no pregnenolone tier claim made. NCCIH DHEA page returned 404; MedlinePlus monograph withdrawn (TRC database unavailable since July 2025), so safety rows lean on Harvard Health (Jan 2025, physician-reviewed). If a clinician prescribed it (adrenal insufficiency, IVF), that's clinician-led care, not this row; the engine may want a never_clear path for that. Not marking never_clear here since the feed version is self-started. Price estimate (DHEA is cheap, ~$10 to $20).</t>
         </is>
       </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -18889,6 +19461,11 @@
       <c r="AJ113" s="3" t="inlineStr">
         <is>
           <t>Tier C on weight: Cochrane 2012 (Jurgens) found -0.04 kg outside Japan (6 RCTs, n=532), Japanese trials -0.2 to -3.5 kg but unpoolable; authors judge it not clinically important. Could be argued D-for-effect but trials exist and disagree by region, so C. Liver: EFSA 2018 says &gt;=800 mg EGCG/day as supplement raised transaminases in trials; USP 2020 review: liver injury case reports at 140 to ~1,000 mg EGCG/day, fasting bolus dosing raises EGCG bioavailability; USP label requires 'take with food, do not use with liver problems'. Brewed tea is generally safe per EFSA (rare idiosyncratic cases). V3 referenced Hu 2018 hepatotoxicity review; I used the USP 2020 review (Oketch-Rabah) instead, which I opened. Price estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -19053,6 +19630,11 @@
           <t>Tier C. Bulman/D'Cunha 2025 Sleep Med Rev meta-analysis (abstract via Bond portal): 19 RCTs, n=897, 18 pooled. Significant but small subjective effects: sleep onset latency SMD 0.15 (CI 0.01-0.29), daytime dysfunction 0.33, overall sleep quality 0.43 (CI 0.04-0.83). Authors flag few pure L-theanine studies and unsettled dose. No objective outcomes in abstract. Borderline B for self-rated sleep; kept C because effects are small, subjective, and confounded by blends. Dose 200-400 mg from V3 and Cotter 2025 review (search snippet only, not opened). Moment 'morning' added because many take it with coffee; caffeine-pairing evidence not reviewed here. Price is an estimate (~$12-18/month for 200 mg daily at mainstream brands); no pricing page opened. No safety row: nothing serious found in opened sources. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -19220,6 +19802,11 @@
           <t>Where did glycine at bedtime come from?</t>
         </is>
       </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -19382,6 +19969,11 @@
           <t>Tier C: studies disagree. Positives: Howatson 2012 (n=20 healthy, 7 days concentrate, more total sleep and efficiency, urinary melatonin up; funding not stated in record), Losso 2018 (8 completers &gt;50 with insomnia, 240 ml twice daily, ~84 min more PSG sleep; NIH-funded), Pigeon 2010 (n=15 older insomnia, only WASO improved; seen in listing, not cited). Nulls: Hillman 2022 (n=44 healthy, 30 days juice or capsules) and Tucker 2024 (n=34, 500 mg capsules) found no sleep effect, both funded by Cherry Marketing Institute (industry funding of null results). Barforoush 2025 review of 7 studies: limited and heterogeneous. A 2023 meta-analysis (Springer, objective efficiency ES 0.63) was seen in search only, not opened. also_serves 'move' because it's also used for exercise recovery (not reviewed here). Overlap: tart cherry is NOT yet a member of sleep-aids in existing-overlaps.json; Ishan needs to add it or drop OVERLAP. Sugar note: V3's ~25 g sugar per serving not verified on a label. Price estimate (~$25-45/month for concentrate twice daily, less for capsules).</t>
         </is>
       </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -19552,6 +20144,11 @@
           <t>Tier C. Suraev 2020 Sleep Med Rev systematic review: insufficient evidence for any sleep disorder, moderate-high risk of bias. Narayan 2024 JCSM RCT (n=30 insomnia, 150 mg nightly x2 weeks): no difference on ISI, self-reported SOL, SE, WASO; objective SE higher at 2 weeks; well-being higher. Wang 2025 JCSM (n=125, 300 mg CBD+terpenes, crossover) found a small rise in % deep+REM on a wrist tracker, no change in total sleep; funding not visible in the record, so not cited. Suraev CANSLEEP (200 mg CBD + 10 mg THC) cut total sleep and REM (conference abstract, not cited). dose_min 150 = lowest pure-CBD dose in an opened sleep RCT, used so DOSE_BELOW_MIN can flag 10-25 mg gummies; it is not a recommendation to take more. Bonn-Miller 2017 JAMA: 84 online products, 31% accurate within 10%, 43% under-labelled, 26% over-labelled, 21% had THC. Safety from NCCIH (interactions, liver injury) and FDA 2019 (avoid in pregnancy/breastfeeding). Price estimate (~$40-60/month for a 25 mg daily gummy). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -19718,6 +20315,11 @@
           <t>V3 had B; downgraded to C because studies now disagree. Pittler &amp; Ernst 2003 Cochrane (Europe PMC record; Cochrane site returned 403): 11 RCTs, n=645, HAM-A WMD 5.0 (CI 1.1-8.8) for kava, short-term use relatively safe; the review is old and Cochrane marks its CAM summaries outdated. Sarris 2013 (n=58 analysed, 120-240 mg, d=0.62) was positive, but the larger phase III Sarris 2020 (n=171 GAD, 240 mg/day, 16 weeks) found no benefit (placebo slightly better), with more liver-test abnormalities on kava. NCCIH 2025: may help anxiety, not GAD; rare serious liver injury; avoid with alcohol or sedatives; pregnancy/breastfeeding risks. Teschke 2008: of 26 suspected liver cases, 8 possible/probable, mostly with overdose, long use or co-medication. Sleep: found no solid kava sleep trials. Area set to mind (anxiety is the evidence outcome), also_serves sleep. Cadence 'occasional' and why_loved 'connection' reflect kava-bar culture; capsule users may be daily. Price estimate (~$25-35/month capsules; kava bar shells cost more). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -19895,6 +20497,11 @@
           <t>night</t>
         </is>
       </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -20061,6 +20668,11 @@
           <t>Tier C (V3 had D): human placebo-controlled trials exist but are small and disagree. Hepsomali 2020 Front Neurosci systematic review: 14 placebo-controlled trials, 'limited' evidence for stress and 'very limited' for sleep (first author's affiliation Unilever, not a GABA seller). Boonstra 2015 Front Psychol: blood-brain barrier crossing long assumed impossible, studies contradictory; much calming evidence from researchers with potential conflicts. FORM_NOT_ABSORBED not used because the barrier question is unresolved, not disproven. Could be argued N if every sleep trial is seller-funded; I did not verify funding trial by trial. Dose range from V3 plus common product labels (not opened). Overlap: gaba-oral is NOT yet in sleep-aids in existing-overlaps.json; needs adding or drop OVERLAP. Price estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -20242,6 +20854,11 @@
           <t>night</t>
         </is>
       </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -20411,6 +21028,11 @@
       <c r="AK122" t="inlineStr">
         <is>
           <t>What drew you to this form of magnesium?</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -20585,6 +21207,11 @@
       <c r="AN123" t="n">
         <v>2</v>
       </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -20743,6 +21370,11 @@
           <t>Tier C. Kazemi 2024 Complement Ther Med meta-analysis (abstract): 10 trials, n=772 adults (healthy or with conditions); PSQI WMD -1.88 (CI -3.46 to -0.31, I2 88%) from 5 studies; fewer awakenings, no clear change in duration, efficiency or daytime function. Hieu 2019 Phytother Res: sleep quality SMD -0.73; one insomnia trial null. NCCIH 2024: very little info on insomnia; likely safe as tea; ragweed-family allergy; warfarin interaction. 'Mostly extracts' is my inference from the MeSH 'Plant Extracts' tag and the trials I know of; abstract didn't split tea vs extract, so flag. Ritual role anchor: the cup itself can carry the evening moment. Cheap, so UNUSED rarely matters. Price estimate (~$5-8 for a month of bags).</t>
         </is>
       </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -20897,6 +21529,11 @@
           <t>Tier C, up from V3's D: Kapp &amp; Sumner 2019 systematic review (Ann Epidemiol) found only one human study as of 2018, but small RCTs have appeared since: Arce-Lopez 2025 (n=58 healthy, 6 wk, fiber-enriched kombucha; triglycerides and Bifidobacterium shifted vs unfermented tea), Bonifacio 2026 (n=90 healthy beginner runners, 12 wk; primary outcome FRAP unchanged, other changes exploratory after FDR), Bonifacio 2026 second trial (n=59 overweight on calorie restriction; no between-group differences overall). Small, short, mixed = C. No kombucha-company funding disclosed in these records (public Brazilian/Spanish funders). 'Probiotic drinks' with named strains (e.g. Yakult-type for antibiotic diarrhoea) were not assessed here; if Veer wants them separate, they need their own row. Price: estimate. Search-result listings (ShopRite) showed GT's Synergy 16 oz at $3.99 to $4.49 regular; about 3 bottles a week is roughly $50/month. Safety row from TTB page: kombucha can ferment in the bottle to 0.5% ABV or more. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -21073,6 +21710,11 @@
           <t>midday</t>
         </is>
       </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -21252,6 +21894,11 @@
       </c>
       <c r="AN127" t="n">
         <v>3</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -21403,6 +22050,11 @@
           <t>Tier C (V3 said D). Hydrogen: Dhillon 2024 systematic review (25 studies, mixed designs) calls results preliminary and asks for larger, rigorous trials; Ye 2026 meta-analysis (13 RCTs, n=757, adults with BMI &gt;=25, mostly cardiometabolic disease) found small TC/LDL drops below clinically meaningful thresholds and says it should not justify routine use. Small single trials in athletes (e.g. Chen 2026, n=13 crossover) report performance effects. That is small/short/mixed, so C rather than D. Alkaline: Alebrahim 2026 narrative review: some reflux (pepsin) and hydration-marker effects, mostly from mineral content; systemic alkalinization and anti-aging claims unsupported; caution in kidney disease. V3's claim that hydrogen trials are all seller-funded: I could not check funding statements from the abstracts, so I did not repeat it. The 'stomach acid neutralises it' line also isn't in what I opened, so it's left out. Price: estimate (bottled alkaline water or hydrogen tablets/cans run roughly $1 to $3 a day; generator bottles are a one-off $50 to $200).</t>
         </is>
       </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -21557,6 +22209,11 @@
           <t>Tier C for healthy 22 to 35 year olds. Shahmohammadi 2026 umbrella (10 meta-analyses, 38 RCTs): FBG -9.4 mg/dL, PPG -14.6, HbA1c -0.70%, weight -1.06 kg (rated high certainty), SBP -2.9; most trials in T2D/overweight, 8 in healthy people; over half poorly blinded. Arjmandfard 2025 (7 trials, T2D): FBS -21.9 mg/dL, HbA1c -1.53. Castagna 2025 (10 RCTs, n=789 overweight/T2D): SMD weight -0.39, BMI -0.65, trials 4 to 12 weeks. IMPORTANT: both Castagna and the umbrella's reference list include Abou-Khalil 2024 (BMJ Nutr Prev Health, Lebanese adolescents/young adults, n=120), which Europe PMC marks as a retracted publication (retraction 2025, doi 10.1136/bmjnph-2023-000823ret). That trial reported the largest weight effects and was the viral one, so the pooled weight estimates are inflated by an unknown amount. In people with T2D the glycaemic evidence is closer to B; there's no evidence_requires code for a diagnosis, so I kept C and put a diabetes safety row. Enamel: Willershausen 2014 in vitro, vinegars caused up to about 20% mineral loss in enamel at 4 h (raspberry vinegar); the umbrella authors also flag dental erosion, reflux, and caution with CKD and glucose/potassium-altering drugs. V3's 'Khezri 2018 n=39' is in Castagna's included list (not opened separately). Price: estimate; a 32 oz bottle of Bragg runs about $6 to $10 and lasts over a month at 1 tbsp/day; gummies cost more ($15 to $20).</t>
         </is>
       </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -21731,6 +22388,11 @@
       <c r="AM130" t="inlineStr">
         <is>
           <t>midday</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -21877,6 +22539,11 @@
       <c r="AJ131" s="3" t="inlineStr">
         <is>
           <t>Tier B for weight: Semnani-Azad 2025 BMJ network meta-analysis (99 RCTs, 6582 adults, only 720 healthy): every IF strategy and continuous calorie restriction beat ad-libitum eating for weight; vs calorie restriction only alternate-day fasting showed an edge (-1.29 kg, moderate certainty); time-restricted eating raised TC/LDL slightly vs whole-day fasting. B not A because most participants had health conditions and differences between strategies are small. It is a benefit row, so EVIDENCE_REGULAR; it's free, so nothing to clear. V3's claims about sleep/HRV effects and 'a week to adjust' were not checked and are left out of person-facing text. Safety rows (eating disorder history, diabetes medication, pregnancy) are standard clinical cautions, not from the BMJ paper; Veer may want a source for them.</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -22029,6 +22696,11 @@
           <t>Tier C, and deliberately no BORROWED_WEAK even though C allows it: whether a filter matters depends on the home's water (lead service lines, old buildings, private wells, PFAS), which Distill can't see, so a 'let it go' could be wrong in exactly the homes where it matters. Only UNUSED (a filter that isn't changed or used). Evidence: CDC 2024 page: test first; if water has no harmful germs/chemicals a filter may not be needed; pitcher filters are mainly for taste and smell, may remove lead; check NSF standard on label. Purchase 2025 field test: lead-certified faucet filters brought occupied-home lead below 1 ug/L; a disturbed lead line overwhelmed them; iron clogged them. Hazzazi 2025: nine popular pitchers varied widely in mineral changes; none fully removed fluoride despite three makers' claims. No health-outcome trials of filtering already-compliant water exist that I found. Price: brita.com lists Elite replacement $19.99 and Original 1-pack $7.99; filter life not shown on the page I opened, so $5/month is an estimate. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -22193,6 +22865,11 @@
           <t>evening</t>
         </is>
       </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -22358,6 +23035,11 @@
       <c r="AK134" t="inlineStr">
         <is>
           <t>Where did chlorophyll water first show up for you?</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -22514,6 +23196,11 @@
           <t>V3 graded N with a 'no detox to do' line; I've avoided that word in person-facing text. Tier C for gas/bloating because small human trials exist and mostly found nothing: Suarez 1999 (5 healthy volunteers, 0.52 g x4/day for 1 wk; no change in fecal sulfur gases, total gas or symptoms); Di Stefano 2000 RCT (34 functional patients; charcoal 400 mg bid did not lower breath H2 or symptoms, rifaximin did). A gastroenterologist quoted in a CU Anschutz news piece (search snippet only, not opened) says 1980s studies split. The popular 'cleanse' and hangover claims have no human studies I could find (effectively N). Juurlink 2016 (Br J Clin Pharmacol review): single-dose charcoal reduces absorption of many drugs; clinical overdose use. Elomaa 2001 (11 women, pill users): charcoal taken 3 h after and &gt;=12 h before the pill did not cause ovulation. That timing is the basis for the safety note. Price: estimate ($10 to $15 a bottle).</t>
         </is>
       </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -22672,6 +23359,11 @@
           <t>V3 graded B; downgraded to C for fine lines. The best wrinkle RCT (Lee 2007, n=76, sham, double-blind, abstract only) used clinic LEDs twice weekly for 4 weeks, not a home mask, and is single-centre; Wunsch 2014 (full text) was fully sponsor-funded with a non-randomized control group drawn mainly from sponsor staff. Bu 2024 and Grimes 2025 (both full text) call home-device evidence limited/mixed; only a third of LED studies had a control plus blinding. AAD (2024) says home devices are hard to judge. ACNE IS DIFFERENT: Ershadi 2025 JAMA Derm meta-analysis of 6 RCTs (216 people) found ~45% greater lesion reduction with home red/blue LED, 4 of 6 low risk of bias; that is B-level for mild to moderate acne. If Veer/Ishan want a split row (acne vs aging), acne would be B with EVIDENCE_REGULAR. The human_question asks which goal so the engine does not clear an acne user on the aging tier. Price: CurrentBody Series 3 $569.99 (opened); Omnilux and others are similar or lower; spread over 24 months about $20 to $24. Cadence daily approximates the 3 to 5 sessions a week on the label. fits_instead rests on existing A rows (sunscreen-daily-spf-30, retinol-retinoid-nightly). Layne 2026 abstract only; its author declares device-company honoraria.</t>
         </is>
       </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -22832,6 +23524,11 @@
       <c r="AJ137" s="3" t="inlineStr">
         <is>
           <t>Kept at C (V3 C), but it is a soft C: Ahn 2025 (n=34, abstract) compared gua sha against a roller with no untreated arm, so the 2 to 3 mm contour change cannot be separated from measurement drift or water retention changes. Miyaji 2018 (abstract) shows only a short blood-flow rise, and one author is from MTG Co., a roller maker (marked brand_funded yes). No study found on ice rollers or cold for cosmetic de-puffing; V3's "de-puffing lasts hours" claim was not verified and is not in the summary. Hamp 2023 (J Cosmet Dermatol, "Gua-sha, jade roller, and facial massage") exists but has no abstract and the full text was blocked (403), so it is not cited. A stricter reader could call this D. Cost: about $20 to $30 one-off, spread over 24 months (estimate, no pricing page opened). also_serves mind because the appeal is mostly the calm ritual. No safety rows: none found in sources opened.</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -23003,6 +23700,11 @@
           <t>evening</t>
         </is>
       </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -23163,6 +23865,11 @@
       <c r="AJ139" s="3" t="inlineStr">
         <is>
           <t>Tier C (V3 C). "Facial" covers many services; the only controlled study found was Freedman 2008 (n=20, abstract): six hydradermabrasion sessions 7 to 10 days apart beat hand-applied serum. That is weekly, not monthly, and a single plastic-surgery practice; funding not stated in the abstract (marked no, unverified). No trial of monthly spa facials found. V3's "no lasting change" was not tested directly. The calm/treat value is real and should carry it. Price: Heyday membership $95 to $105/month incl. one 50-minute facial (brand franchising page, opened); independent spas often charge more. UNUSED covers lapsed memberships. also_serves mind for the hour of calm.</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -23324,6 +24031,11 @@
           <t>Who recommended an eye cream on top of your moisturizer?</t>
         </is>
       </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -23481,6 +24193,11 @@
       <c r="AK141" t="inlineStr">
         <is>
           <t>Where did toner come into your routine from?</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -23638,6 +24355,11 @@
           <t>How did a facial, LED and microcurrent all end up in your routine?</t>
         </is>
       </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -23796,6 +24518,11 @@
           <t>Tier C for skin (V3 C). Wunsch 2014 (full text) is the closest match to a panel (full-body units) and found gains vs untreated controls, but was fully sponsor-funded with non-randomized, sponsor-employee controls and no sham. AAD 2024 (full text) supports subtle-to-noticeable results for aging skin but says home devices are hard to judge. Recovery: Dutra 2022 meta-analysis (abstract) found small gains in single-joint endurance and cycling time to exhaustion, none in strength or running; trials used lasers/LED clusters on muscles pre-exercise, not panels, so the move claim is C at best. Sleep: Zhao 2012 (abstract) is 20 athletes, not blinded; D for sleep. V3 testosterone claim rests on rat data; not searched further and left out. Price: Mito panels $249 to $749 for most home sizes (brand page, opened), over 24 months about $10 to $31; used $20. fits_instead points to morning-sunlight-10-min-outdoors (a different benefit, circadian, not skin); Veer may prefer "". Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -23963,6 +24690,11 @@
           <t>Where did you first see the hair gummies?</t>
         </is>
       </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -24129,6 +24861,11 @@
           <t>V3 N; here C with evidence_requires deficiency, tier_otherwise N. Patel 2017 (full text): 18 published cases, all with an underlying cause (inherited biotinidase or holocarboxylase deficiency, uncombable hair, brittle nails, valproate use), all improved; this is case-report evidence, so C, not B, even for the deficient. No RCT in healthy people. Adult AI is 30 mcg; Western diets give about 35 to 70 mcg (Patel). NIH ODS biotin fact sheets returned 403 to both WebFetch and curl, so not cited; worth re-checking (they also discuss lab interference and anticonvulsant-related low biotin). Lab interference: Li 2017 (abstract) 10 mg/day for a week skewed 9 of 23 biotin-based assays incl. thyroid; FDA troponin page (opened, current as of 2022) reports falsely low troponin. The FDA consumer safety communication URL 404d; not cited. Cost $8 is V3's, not checked. Area skin since the use is hair and nails; no hair area exists.</t>
         </is>
       </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -24293,6 +25030,11 @@
           <t>V3 graded B; set to C to match the reviewed collagen-peptides row (same evidence: Myung 2025, de Miranda 2021, Proksch 2014, all reused by id). V3's claim that gummies and drinks carry a fraction of the dose is only partly true: Vital Proteins gummies list 2.5 g VERISOL per serving at $16.99 for 30 servings (opened), which matches the Proksch dose. Other gummies list far less (a Walmart listing showed 120 mg, but the page was bot-blocked, so not cited); DOSE_BELOW_MIN handles those case by case. Cost $25 is an estimate between gummies (~$17) and ready-to-drink shots (not priced here). Area skin rather than eat because these are sold as beauty products; collagen-peptides sits in eat with also_serves skin.</t>
         </is>
       </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -24459,6 +25201,11 @@
           <t>V3 graded A off an unsourced claim that unused credits are the most common wellness purchase that does nothing; I found no study of class-pack or ClassPass breakage, so that claim is dropped. The A now belongs to the training (HIIT trials, WHO activity guidance), held only for people who use it (trains, otherwise N), matching gym-membership and boutique rows. Usage evidence is DellaVigna and Malmendier 2006 (gym memberships, not packs). Expiry matters: SoulCycle's opened series page (San Francisco) lists 5 classes $185 (45-day expiry), 10 for $365 (3 months), 20 for $710 (9 months). cost_month_usd 120 = a 10-pack spread over its 3-month expiry. ClassPass official pricing page returned 403; third-party summaries show $19 for 8 credits up to about $139 to $159, with rollover capped, so not used for the price. Clear codes follow the gym rows (UNUSED, OVERLAP), not BORROWED_WEAK. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -24625,6 +25372,11 @@
           <t>V3 B kept. Moyer, Rounds and Hannum 2004 (Psychol Bull, 37 randomised studies, mixed healthy and clinical samples): single sessions lowered state anxiety, BP and heart rate but not cortisol, negative mood or immediate pain; multiple sessions lowered delayed pain, trait anxiety and depression. Dupuy 2018 (Front Physiol meta-analysis, post-exercise recovery) found massage the most effective technique for DOMS and perceived fatigue, single sessions only. B not A because samples are mixed and old, and effects are mostly short-term. V3's 'HRV goes up' not verified, dropped. Prices opened: ThePricer (updated Aug 2026) puts Massage Envy membership at about $70 to $90 a month for one 60-min session, 12-month initial term; unused benefits accrue but are forfeited 60 days after cancelling. Squeeze (Fort Worth opening article, Mar 2024): $95 a month for 50 min, $125 for 80 min, credits roll over and never expire, cancel anytime. cost 90 is the midpoint. Massage Envy's own page returned empty.</t>
         </is>
       </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -24795,6 +25547,11 @@
           <t>V3 B changed to C to match the reviewed sauna row (sauna-post-workout-or-evening), which reused the same sources: one observational cohort of Finnish men (Laukkanen 2015) plus small trials. No new sources needed. Price opened: Bathhouse (abathhouse.com, NYC: Atlantic Ave, Flatiron, Williamsburg) Starter $145 a month for 3 day passes, Standard $225 for 5. Othership's membership page lists rollover of unused credits but showed no prices. Safety rows mirror the sauna row. V3 typical 2 to 4 visits a week kept as dose_typical; the cohort's clearest links were at 4 to 7.</t>
         </is>
       </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -24965,6 +25722,11 @@
           <t>V3 C restructured to match the cold-plunge row: B for soreness when the person trains (Dupuy 2018 meta-analysis: immersion, contrast water, compression and massage all cut DOMS; Machado 2016 and Moore 2022 for cold water), C otherwise (sauna heart evidence is a single cohort; mood claims thin). Add-ons: whole-body cryo insufficient per Cochrane (Costello 2015, 4 tiny RCTs); IV drips no evidence in healthy people (Merck Manual 2025). Prices opened: Athletech News (Sep 2024) Restore NYC tiers about $250 (8 services), $390 (14), $449 (31), 3-month minimum per directory listings (not opened); Boston Globe (Mar 2025) Remedy Place $450 to $3,250 a month; Time Out (2025) Remedy Place from $595. Othership pricing not shown on its pages. cost 250 = Restore entry tier; Remedy Place members sit far higher. Safety rows combine the sauna and cold-plunge rows.</t>
         </is>
       </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -25131,6 +25893,11 @@
           <t>V3 graded A off 'nobody needs two', which is not a research finding. As with gym-membership, the A belongs to the training and holds only with use (trains, otherwise N); OVERLAP via gym-floor-access (keep-most-used) is the real lever. DellaVigna and Malmendier 2006 is the usage evidence. Price is an estimate: a second membership is often a studio or climbing gym. Opened data points: Time Out (2025) VITAL Climbing Harlem $155 a month; SoulCycle 10-pack $365 over 3 months (about $120 a month). Budget gyms run far less (Planet Fitness page returned 403, not used). cost 120 sits between. Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -25297,6 +26064,11 @@
           <t>V3 B kept; same evidence as the massage membership row (Moyer 2004, Dupuy 2018). V3's 'HRV goes up for a while' and 'no lasting physical effect' not verified; Moyer found course effects on trait anxiety and depression, so 'no lasting effect' was dropped. NCCIH (2019) notes rare serious harms (blood clot, nerve injury, fracture), mostly with vigorous deep tissue work. Price opened: ThePricer (Aug 2026) non-member 60-min Massage Envy prices $125 (Mount Dora), $145 (Freehold), $155 (Concord), $160 (Gramercy NYC); Squeeze $129 for 50 min. cost 130 excludes tip. UNUSED included per the rule for paid items (a prepaid package or gift card). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
         </is>
       </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -25459,6 +26231,11 @@
           <t>V3 C ('about as well as stretching at home') changed to B, conditional on regular sessions. Konrad 2024 (J Sport Health Sci, 77 studies, 3,870 healthy people): stretch training moderately raised ROM (ES about 1.0); fully supervised ES 1.08 vs non-supervised 0.74, difference not significant (p = 0.17); frequency, volume and intensity not significant; PNF and static beat dynamic. Behm 2023: one bout gives small ROM gains, no difference by technique. No trial isolates one-on-one assisted studio stretching, hence B not A, and flexibility is the only outcome tested (no evidence found for injury, recovery or posture claims). Price: StretchLab's memberships page lists plans but no prices; ThePricer (Aug 2026) lists 4 x 25 min at $169 to $239 a month (3-month initial term), 4 x 50 min $329 (Burlingame). cost 189 is the middle 4 x 25 tier.</t>
         </is>
       </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -25621,6 +26398,11 @@
           <t>V3 C kept. Feinstein 2018 (PLoS One): open-label, no control, 50 adults with anxiety disorders, one 60-min float, large drop in state anxiety (d 2.15); float pool built with Floataway involvement, no float-centre funding. Jonsson and Kjellgren 2016 (BMC CAM): RCT pilot, 50 adults with self-reported GAD, 12 x 45-min floats vs waitlist, non-blinded; GAD symptoms, sleep and depression improved more than waitlist, worry (PSWQ) did not; a reported F-statistic does not match its p-value. No trials in calm healthy adults; I did not open the randomized crossover (Biol Psychiatry CNNI 2018) or the 2024 feasibility RCT. Price opened: True REST San Diego $89 single 60-min float; memberships $65 (1 float), $110 (2), $200 (4), unused floats roll over. cost 89 = one float a month.</t>
         </is>
       </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -25785,6 +26567,11 @@
       <c r="AJ155" s="3" t="inlineStr">
         <is>
           <t>V3 C kept. Costello 2015 Cochrane (CD010789): 4 lab RCTs, 64 active, mostly young men; very low-quality evidence, insufficient to say whether WBC reduces soreness or improves recovery vs rest; no adverse events reported. Dupuy 2018 pooled 'cryotherapy' broadly (not WBC alone) and found smaller DOMS drops than massage. Legrand 2023 consortium scoping review: 16 adverse events in 7 reports (4 serious: amnesia, brain bleed, moyamoya, aortic dissection); hypertension is an absolute contraindication in the Bad Voslau consensus. An FDA MAUDE report I opened states FDA has not cleared or approved any WBC device and describes a worker found dead in a chamber; the 2016 FDA consumer update URL now 404s, so not cited. Could argue D; kept C because RCTs exist, just tiny. Price opened: Cryo Lab (El Dorado Hills, CA) $45 a session, 2 to 3.5 minutes. cost 180 = 4 sessions a month; unlimited plans run about $59 to $249 elsewhere (search snippets, not opened). Validation 24 Oct: edited per the independent re-check (data/validation).</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -25942,6 +26729,11 @@
           <t>How did you first hear about IV drips?</t>
         </is>
       </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -26098,6 +26890,11 @@
       <c r="AJ157" s="3" t="inlineStr">
         <is>
           <t>V3 C kept; V3's 'specific modalities usually don't add to rest' is not tested anywhere I found, so dropped. Naidoo, Schembri and Cohen 2018 (BMC CAM): 23 studies (8 RCTs), 2,592 people, all reported benefits, but small samples, weak methods, little follow-up, no adverse-event data; strongest in people with chronic illness. de Bloom 2009 (J Occup Health): 7 vacation studies, small gain (d 0.43) that fades after return to work (d -0.38). Cohen's group also ran an uncontrolled one-week retreat study (n 37) at a retreat; not cited. Price opened: Kripalu R&amp;R from $99 a night plus lodging from $109 weekday / $129 weekend, 2-night weekend minimum: about $460 to $700 for a weekend. cost 50 assumes one such weekend a year, spread over 12 months (V3 spread over 24). UNUSED kept per the paid-item rule; it only applies to a prepaid, untaken booking.</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/data/Routing-Table_V4.xlsx
+++ b/data/Routing-Table_V4.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -633,6 +633,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>yes when the benefit builds with daily use (creatine, vitamin D, sunscreen, morning light), so doing it now and then mostly misses it. Distill then offers to anchor it to something they already do every day. no for things that work on the day (pre-workout, an eye mask).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>budget_option</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>For something expensive: the same activity for less, offered once unless they love it (the luxury, the people there). 30 words or fewer, the person-facing word rules apply. Never for therapy, clinical care or anything from a clinician.</t>
         </is>
       </c>
     </row>
@@ -647,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO157"/>
+  <dimension ref="A1:AP157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -894,6 +906,11 @@
           <t>builds</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>budget_option</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3310,6 +3327,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>A smaller plan for your busiest nights, with a simple Sunday cook for the rest.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -5820,6 +5842,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>A standard gym with the equipment you use, plus a class pass for the days you want the extras.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -5991,6 +6018,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>A class pack for your favourite days, with runs or home workouts between.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6164,6 +6196,11 @@
       <c r="AO32" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>A class pack for one or two favourite classes a week, and a mat at home between.</t>
         </is>
       </c>
     </row>
@@ -6331,6 +6368,11 @@
       <c r="AO33" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>A session every other week to check your form, with the program on your own between.</t>
         </is>
       </c>
     </row>
@@ -8633,6 +8675,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>A fan, lighter bedding and a cooler room do much of the same.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -23872,6 +23919,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>A facial each season, with a simple routine at home between.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -25552,6 +25604,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>A gym that has a sauna, or a day pass on the weeks you want it.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -25727,6 +25784,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>A pay-per-visit pass for the sauna and plunge you actually use.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -26069,6 +26131,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>A massage every other month, with a massage ball for sore spots between.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -26234,6 +26301,11 @@
       <c r="AO153" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>One assisted session a month, with a 10-minute stretch at home between.</t>
         </is>
       </c>
     </row>
